--- a/data/credit_bond_all_2026-08-28.xlsx
+++ b/data/credit_bond_all_2026-08-28.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-28" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-31" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-28</t>
+          <t>数据来源：DM    2026-08-31</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -719,8 +719,12 @@
           <t>1.70 ~ 2.40</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>76.0</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.99</t>
@@ -743,7 +747,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/1.9000</t>
+          <t>2.0100/1.9000</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -783,7 +787,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X3" s="3"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>1.91%~2.01%</t>
+        </is>
+      </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -857,7 +865,11 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP3" s="3"/>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ3" s="3" t="inlineStr">
         <is>
           <t>贸易零售</t>
@@ -913,7 +925,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>08-28 17:00</t>
+          <t>08-28 18:30</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -935,8 +947,12 @@
           <t>2.20 ~ 3.50</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>108.81</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -982,9 +998,21 @@
       </c>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>2.35%~2.45%</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -1109,7 +1137,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1131,8 +1159,12 @@
           <t>1.70 ~ 2.70</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>46.81</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1.90</t>
@@ -1150,12 +1182,12 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.8925</t>
+          <t>1.8940</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>2.0100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -1165,7 +1197,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C- 18.10</t>
+          <t>C- 18.44</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1195,7 +1227,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X5" s="3"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>1.92%~2.02%</t>
+        </is>
+      </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1336,7 +1372,11 @@
           <t>08-28 18:00</t>
         </is>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>012682172.IB</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>0.66Y</t>
@@ -1345,7 +1385,9 @@
       <c r="E6" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>1.37 ~ 1.67</t>
@@ -1415,7 +1457,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="X6" s="3"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>1.49%~1.53%</t>
+        </is>
+      </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1552,7 +1598,11 @@
           <t>08-28 18:00</t>
         </is>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>102690019.IB</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -1561,7 +1611,9 @@
       <c r="E7" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
           <t>1.60 ~ 2.60</t>
@@ -1631,7 +1683,11 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X7" s="3"/>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>1.85%~1.95%</t>
+        </is>
+      </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -1772,7 +1828,11 @@
           <t>08-28 18:00</t>
         </is>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>102683449.IB</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -1781,7 +1841,9 @@
       <c r="E8" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
           <t>1.10 ~ 2.10</t>
@@ -1811,7 +1873,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>--/1.7200</t>
+          <t>1.8000/1.7000</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1851,7 +1913,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X8" s="3"/>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.78%</t>
+        </is>
+      </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1992,7 +2058,11 @@
           <t>08-28 18:00</t>
         </is>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>012682171.IB</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -2001,7 +2071,9 @@
       <c r="E9" s="4" t="n">
         <v>4.0</v>
       </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>1.37 ~ 1.57</t>
@@ -2016,22 +2088,22 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26象屿SCP006</t>
+          <t>26中拓SCP009</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>245D</t>
+          <t>259D</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.5998</t>
+          <t>1.7014</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7500/--</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -2064,7 +2136,7 @@
       <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X9" s="3"/>
@@ -2141,7 +2213,11 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP9" s="3"/>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
           <t>贸易零售</t>
@@ -2187,7 +2263,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ9" s="3"/>
+      <c r="AZ9" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
@@ -2200,7 +2278,11 @@
           <t>08-28 18:00</t>
         </is>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>102683453.IB</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -2209,7 +2291,9 @@
       <c r="E10" s="4" t="n">
         <v>4.2</v>
       </c>
-      <c r="F10" s="3"/>
+      <c r="F10" s="4" t="n">
+        <v>4.2</v>
+      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
           <t>2.30 ~ 3.30</t>
@@ -2224,7 +2308,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>22蓝海债(柜台)</t>
+          <t>22蓝海债</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -2249,7 +2333,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.45</t>
+          <t>B- 35.82</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2279,7 +2363,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X10" s="3"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>2.20%~2.30%</t>
+        </is>
+      </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -2420,7 +2508,11 @@
           <t>08-28 18:00</t>
         </is>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>102683455.IB</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -2429,7 +2521,9 @@
       <c r="E11" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F11" s="3"/>
+      <c r="F11" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>1.60 ~ 2.60</t>
@@ -2469,7 +2563,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C 25.52</t>
+          <t>B- 35.56</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2499,7 +2593,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X11" s="3"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>2.23%~2.33%</t>
+        </is>
+      </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2579,7 +2677,7 @@
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
@@ -2640,7 +2738,11 @@
           <t>08-28 18:00</t>
         </is>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>102683452.IB</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -2649,7 +2751,9 @@
       <c r="E12" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
           <t>1.75 ~ 2.75</t>
@@ -2689,7 +2793,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>B- 36.97</t>
+          <t>B- 36.39</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2719,7 +2823,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X12" s="3"/>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>2.26%~2.36%</t>
+        </is>
+      </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2843,7 +2951,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ12" s="3"/>
+      <c r="AZ12" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
@@ -2856,7 +2966,11 @@
           <t>08-28 18:00</t>
         </is>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>132680091.IB</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -2865,7 +2979,9 @@
       <c r="E13" s="4" t="n">
         <v>7.0</v>
       </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="4" t="n">
+        <v>7.0</v>
+      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.00</t>
@@ -2890,7 +3006,7 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.7892</t>
+          <t>1.7951</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -2905,7 +3021,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C 25.47</t>
+          <t>C 27.84</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -2935,7 +3051,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X13" s="3"/>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>1.74%~1.84%</t>
+        </is>
+      </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3076,7 +3196,11 @@
           <t>08-28 18:00</t>
         </is>
       </c>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>102683450.IB</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>10Y</t>
@@ -3085,7 +3209,9 @@
       <c r="E14" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F14" s="3"/>
+      <c r="F14" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
           <t>1.90 ~ 2.29</t>
@@ -3115,7 +3241,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/1.7800</t>
+          <t>1.9000/1.7800</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -3155,7 +3281,11 @@
           <t>4-</t>
         </is>
       </c>
-      <c r="X14" s="3"/>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>2.10%~2.20%</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3283,7 +3413,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ14" s="3"/>
+      <c r="AZ14" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
@@ -3293,7 +3425,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -3315,8 +3447,12 @@
           <t>1.20 ~ 2.20</t>
         </is>
       </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="H15" s="4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>39.53</v>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
           <t>1.64</t>
@@ -3334,12 +3470,12 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.6523</t>
+          <t>1.6633</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.6500/1.6200</t>
+          <t>--/1.6200</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -3349,7 +3485,7 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.70</t>
+          <t>C+ 30.85</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3379,7 +3515,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X15" s="3"/>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>1.66%~1.76%</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3516,7 +3656,11 @@
           <t>08-28 18:00</t>
         </is>
       </c>
-      <c r="C16" s="3"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>102683444.IB</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -3525,7 +3669,9 @@
       <c r="E16" s="4" t="n">
         <v>6.0</v>
       </c>
-      <c r="F16" s="3"/>
+      <c r="F16" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.30</t>
@@ -3591,7 +3737,11 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>1.72%~1.82%</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3728,7 +3878,7 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26中荆05</t>
+          <t>26中荆05(取消发行)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3738,7 +3888,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>283810.SH</t>
+          <t>DY283810.SH</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3759,7 +3909,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -3779,7 +3929,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1.9300/1.8400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -3819,7 +3969,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X17" s="3"/>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>1.77%~1.87%</t>
+        </is>
+      </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -3863,7 +4017,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>中荆投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种一)</t>
+          <t>中荆投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -3928,7 +4082,7 @@
       </c>
       <c r="AU17" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t/>
         </is>
       </c>
       <c r="AV17" s="3" t="inlineStr">
@@ -3961,7 +4115,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -4002,12 +4156,12 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.9715</t>
+          <t>1.9777</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>2.0000/1.9700</t>
+          <t>--/1.9650</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -4017,7 +4171,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C 25.53</t>
+          <t>C- 18.62</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4047,7 +4201,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X18" s="3"/>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>1.94%~2.04%</t>
+        </is>
+      </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4203,8 +4361,12 @@
           <t>1.10 ~ 2.10</t>
         </is>
       </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="H19" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>32.0</v>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
           <t>1.63</t>
@@ -4222,12 +4384,12 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.6063</t>
+          <t>1.6100</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/1.6400</t>
+          <t>1.6500/1.6300</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -4267,7 +4429,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X19" s="3"/>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4343,7 +4509,7 @@
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
@@ -4396,7 +4562,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26宏桂02</t>
+          <t>26遂宁兴业PPN001</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4404,45 +4570,41 @@
           <t>08-28 18:00</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>524990.SZ</t>
-        </is>
-      </c>
+      <c r="C20" s="3"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.2</v>
+        <v>4.0</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26宏桂01</t>
+          <t>26伊犁财通PPN001</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.70Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.9455</t>
+          <t>2.0881</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4452,12 +4614,12 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>广西宏桂资本运营集团有限公司</t>
+          <t>遂宁兴业投资集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>D- 0.98</t>
+          <t>D 5.00</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4467,7 +4629,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 09:30</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -4484,10 +4646,14 @@
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X20" s="3"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>2.26%~2.36%</t>
+        </is>
+      </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -4496,23 +4662,23 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>四川省-遂宁市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,3.00亿元用于偿还有息债务,剩余部分用于补充流动资金。本期债券募集资金1.20亿元将用于补充公司贸易业务等日常生产经营所需流动资金,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出。[25宏桂资本SCP002]</t>
+          <t>本次定向债务融资工具注册规模为4亿元，本期定向债务融资工具基础发行规模0亿元，发行规模上限4亿元。根据发行人的资金需求，拟用于偿还公司存量债务融资工具本金【25遂宁兴业SCP002】、【26遂宁兴业SCP001】</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>申万宏源证券有限公司,天风证券股份有限公司</t>
+          <t>重庆银行股份有限公司,光大证券股份有限公司,天津银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4522,28 +4688,32 @@
       </c>
       <c r="AG20" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>广西宏桂资本运营集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>遂宁兴业投资集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
-        </is>
-      </c>
-      <c r="AK20" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK20" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL20" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM20" s="3" t="inlineStr">
@@ -4558,12 +4728,12 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
@@ -4573,17 +4743,17 @@
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4616,68 +4786,64 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26张高Y1</t>
+          <t>26宝鸡工发PPN002</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>08-28 17:30</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>283797.SH</t>
-        </is>
-      </c>
+          <t>08-28 18:00</t>
+        </is>
+      </c>
+      <c r="C21" s="3"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.90 ~ 3.00</t>
         </is>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>25张高Y1</t>
+          <t>26宝鸡工发PPN001</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>1.65Y+N</t>
+          <t>2.58Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.6816</t>
+          <t>2.1288</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>1.7200/1.6200</t>
+          <t>--/2.1400</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>张家港市高铁投资发展(集团)有限公司</t>
+          <t>宝鸡市工业发展集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 24.94</t>
+          <t>D- 3.00</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4687,7 +4853,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 14:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4697,42 +4863,46 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>2.54%~2.64%</t>
+        </is>
+      </c>
+      <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>陕西省-宝鸡市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金。[23张高Y2]</t>
+          <t>发行人本期定向债务融资工具基础发行规模0.00 亿元，发行金额上限5.00亿元，募集资金拟用于偿还公司有息负债、补充流动资金。其中，3亿元用于偿还公司有息负债，2亿元用于补充流动资金</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD21" s="3"/>
+          <t>光大证券股份有限公司,华夏银行股份有限公司,重庆银行股份有限公司,兴业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr">
+        <is>
+          <t>西安投融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -4742,12 +4912,12 @@
       </c>
       <c r="AG21" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)</t>
+          <t>宝鸡市工业发展集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4757,72 +4927,68 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>2031-08-31</t>
         </is>
       </c>
       <c r="AK21" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL21" s="3" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP21" s="3"/>
+      <c r="AQ21" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM21" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO21" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ21" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR21" s="3" t="inlineStr">
-        <is>
-          <t>综合基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS21" s="3" t="inlineStr">
-        <is>
-          <t>综合基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT21" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU21" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW21" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX21" s="3" t="inlineStr">
@@ -4835,73 +5001,71 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ21" s="3"/>
+      <c r="AZ21" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26张高Y2</t>
+          <t>26汤山建设PPN001</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>08-28 17:30</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>283798.SH</t>
-        </is>
-      </c>
+          <t>08-28 18:00</t>
+        </is>
+      </c>
+      <c r="C22" s="3"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.0</v>
+        <v>7.4</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>25张高Y1</t>
+          <t>24汤山04</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>1.65Y+N</t>
+          <t>3.22Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.6816</t>
+          <t>1.7594</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>1.7200/1.6200</t>
+          <t>--/1.7100</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>张家港市高铁投资发展(集团)有限公司</t>
+          <t>南京汤山建设投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C- 24.94</t>
+          <t>C- 11.97</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -4911,7 +5075,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -4921,14 +5085,14 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X22" s="3"/>
@@ -4940,23 +5104,23 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金。[23张高Y2]</t>
+          <t>发行人本次定向债务融资工具注册金额7.40亿元，本期发行金额7.40亿元，募集资金拟全部用于偿还发行人到期债务融资工具本金[25汤山建设SCP001]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
@@ -4966,12 +5130,12 @@
       </c>
       <c r="AG22" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
+          <t>南京汤山建设投资发展集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -4981,60 +5145,60 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2029-08-31</t>
         </is>
       </c>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM22" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO22" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ22" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR22" s="3" t="inlineStr">
-        <is>
-          <t>综合基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS22" s="3" t="inlineStr">
-        <is>
-          <t>综合基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT22" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU22" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -5042,7 +5206,7 @@
       </c>
       <c r="AW22" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX22" s="3" t="inlineStr">
@@ -5055,54 +5219,64 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ22" s="3"/>
+      <c r="AZ22" s="4" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26遂宁兴业PPN001</t>
+          <t>26宏桂02</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
-        </is>
-      </c>
-      <c r="C23" s="3"/>
+          <t>08-28 19:00</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>524990.SZ</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.0</v>
+        <v>4.2</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>66.0</v>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26伊犁财通PPN001</t>
+          <t>26宏桂01</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>2.70Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>2.0881</t>
+          <t>1.9386</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -5112,12 +5286,12 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>遂宁兴业投资集团有限公司</t>
+          <t>广西宏桂资本运营集团有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>D 5.00</t>
+          <t>D- 0.98</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5127,7 +5301,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:30</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -5144,10 +5318,14 @@
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X23" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>1.98%~2.08%</t>
+        </is>
+      </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -5156,23 +5334,23 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>四川省-遂宁市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具注册规模为4亿元，本期定向债务融资工具基础发行规模0亿元，发行规模上限4亿元。根据发行人的资金需求，拟用于偿还公司存量债务融资工具本金【25遂宁兴业SCP002】、【26遂宁兴业SCP001】</t>
+          <t>本期公司债券募集资金扣除发行费用后,3.00亿元用于偿还有息债务,剩余部分用于补充流动资金。本期债券募集资金1.20亿元将用于补充公司贸易业务等日常生产经营所需流动资金,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出。[25宏桂资本SCP002]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>重庆银行股份有限公司,光大证券股份有限公司,天津银行股份有限公司</t>
+          <t>申万宏源证券有限公司,天风证券股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5182,32 +5360,28 @@
       </c>
       <c r="AG23" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>遂宁兴业投资集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>广西宏桂资本运营集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK23" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-31</t>
+        </is>
+      </c>
+      <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t/>
         </is>
       </c>
       <c r="AM23" s="3" t="inlineStr">
@@ -5222,12 +5396,12 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
@@ -5237,17 +5411,17 @@
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5280,64 +5454,74 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26宝鸡工发PPN002</t>
+          <t>26苏州银行01</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
-        </is>
-      </c>
-      <c r="C24" s="3"/>
+          <t>08-28 16:00</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>2620007.IB</t>
+        </is>
+      </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>30.0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>30.0</v>
+      </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+          <t>1.30 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>31.0</v>
+      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26宝鸡工发PPN001</t>
+          <t>25苏州银行科创债01(柜台)</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2.58Y</t>
+          <t>4.04Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>2.1288</t>
+          <t>1.6308</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/2.1400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>宝鸡市工业发展集团有限公司</t>
+          <t>苏州银行股份有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>D- 3.00</t>
+          <t>A- 62.46</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5347,7 +5531,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>08-28 14:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -5357,47 +5541,55 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="3"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>1.58%~1.68%</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>陕西省-宝鸡市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具基础发行规模0.00 亿元，发行金额上限5.00亿元，募集资金拟用于偿还公司有息负债、补充流动资金。其中，3亿元用于偿还公司有息负债，2亿元用于补充流动资金</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,华夏银行股份有限公司,重庆银行股份有限公司,兴业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD24" s="3" t="inlineStr">
-        <is>
-          <t>西安投融资担保有限公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司,中国银行股份有限公司,中国邮政储蓄银行股份有限公司,中国工商银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国光大银行股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,国信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr">
@@ -5407,63 +5599,67 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>宝鸡市工业发展集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>苏州银行股份有限公司2026年第一期金融债券</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
+          <t>2029-09-01</t>
         </is>
       </c>
       <c r="AK24" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL24" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AM24" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP24" s="3"/>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5473,7 +5669,7 @@
       </c>
       <c r="AV24" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW24" s="3" t="inlineStr">
@@ -5496,64 +5692,72 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26汤山建设PPN001</t>
+          <t>26盛泽G1</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
-        </is>
-      </c>
-      <c r="C25" s="3"/>
+          <t>08-28 19:00</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>245734.SH</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>7.4</v>
+        <v>5.0</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>58.0</v>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>24汤山04</t>
+          <t>24盛泽G1</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>3.22Y</t>
+          <t>2.81Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.7455</t>
+          <t>1.7543</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/1.7100</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>南京汤山建设投资发展集团有限公司</t>
+          <t>江苏盛泽投资有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C- 11.97</t>
+          <t>C- 12.74</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5563,7 +5767,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5573,7 +5777,7 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U25" s="3"/>
@@ -5583,32 +5787,36 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X25" s="3"/>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>1.70%~1.80%</t>
+        </is>
+      </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>发行人本次定向债务融资工具注册金额7.40亿元，本期发行金额7.40亿元，募集资金拟全部用于偿还发行人到期债务融资工具本金[25汤山建设SCP001]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换到期公司债券本金的偿债资金[23盛泽G1]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司</t>
+          <t>华安证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
@@ -5618,63 +5826,67 @@
       </c>
       <c r="AG25" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>南京汤山建设投资发展集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>江苏盛泽投资有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
-        </is>
-      </c>
-      <c r="AK25" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK25" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL25" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AM25" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
@@ -5707,71 +5919,77 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ25" s="4" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="AZ25" s="3"/>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26长沙银行三农债</t>
+          <t>26张高Y2</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:30</t>
-        </is>
-      </c>
-      <c r="C26" s="3"/>
+          <t>08-28 19:00</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>283798.SH</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+          <t>1.90 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>71.81</v>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26长沙银行债02</t>
+          <t>25张高Y1</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>1.65Y+N</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.6023</t>
+          <t>1.6829</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>1.6050/1.5975</t>
+          <t>--/1.6200</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>长沙银行股份有限公司</t>
+          <t>张家港市高铁投资发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>A 73.26</t>
+          <t>C- 19.06</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -5781,7 +5999,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -5798,43 +6016,39 @@
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将依据适用法律和监管部门的批准,专项用于发放涉农贷款。</t>
+          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金。[23张高Y2]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,兴业银行股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,广发证券股份有限公司,中国建设银行股份有限公司</t>
+          <t>东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -5844,29 +6058,25 @@
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>长沙银行股份有限公司2026年"三农"专项金融债券</t>
+          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK26" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5874,7 +6084,7 @@
       </c>
       <c r="AM26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN26" s="3" t="inlineStr">
@@ -5884,32 +6094,32 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -5924,7 +6134,7 @@
       </c>
       <c r="AW26" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX26" s="3" t="inlineStr">
@@ -5942,68 +6152,72 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26盛泽G1</t>
+          <t>26金义03</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>245734.SH</t>
+          <t>283806.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+          <t>1.35 ~ 2.35</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>36.81</v>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>24盛泽G1</t>
+          <t>26金义02</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>2.81Y</t>
+          <t>2.79Y+2.00Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.7495</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7800/1.7600</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>江苏盛泽投资有限公司</t>
+          <t>浙江金义控股集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 10.62</t>
+          <t>B+ 57.22</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6013,7 +6227,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 16:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6035,28 +6249,28 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.70%~1.80%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换到期公司债券本金的偿债资金[23盛泽G1]</t>
+          <t>本期债券的募集资金扣除发行费用后,拟全部用于偿还到期的公司债券“23金义03”。[23金义03]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>华安证券股份有限公司,东吴证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,国金证券股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
@@ -6077,74 +6291,70 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>江苏盛泽投资有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>浙江金义控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="AK27" s="3"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
           <t>2029-09-01</t>
         </is>
       </c>
-      <c r="AK27" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
-      <c r="AL27" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM27" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO27" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ27" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR27" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS27" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT27" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU27" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV27" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -6152,7 +6362,7 @@
       </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX27" s="3" t="inlineStr">
@@ -6170,70 +6380,68 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26平安租赁CP003</t>
+          <t>26XCF14</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>042680303.IB</t>
+          <t>283838.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>0.97Y</t>
+          <t>5+2+2</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>4.0</v>
-      </c>
+        <v>6.5</v>
+      </c>
+      <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.51</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26平安租赁CP002</t>
+          <t>26XCF12</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>355D</t>
+          <t>4.98Y+4.00Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.5609</t>
+          <t>1.9001</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8900</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>平安国际融资租赁有限公司</t>
+          <t>成都兴城投资集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C- 20.76</t>
+          <t>C 28.72</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6243,7 +6451,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 16:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6260,12 +6468,12 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.55%~1.59%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6276,48 +6484,48 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行短期融资券拟募集资金4亿元，拟全部用于偿还发行人银行借款</t>
+          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途,具体用途根据发行人资金需求情况确定。</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司,招商银行股份有限公司</t>
+          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>平安国际融资租赁有限公司2026年度第三期短期融资券</t>
+          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行公司债券(第七期)(品种二)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2027-08-21</t>
+          <t>2035-09-01</t>
         </is>
       </c>
       <c r="AK28" s="3" t="inlineStr">
@@ -6327,12 +6535,12 @@
       </c>
       <c r="AL28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t/>
         </is>
       </c>
       <c r="AM28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN28" s="3" t="inlineStr">
@@ -6342,37 +6550,37 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AV28" s="3" t="inlineStr">
@@ -6382,7 +6590,7 @@
       </c>
       <c r="AW28" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX28" s="3" t="inlineStr">
@@ -6392,59 +6600,61 @@
       </c>
       <c r="AY28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AZ28" s="4" t="n">
-        <v>0.0</v>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AZ28" s="3"/>
     </row>
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26苏州银行01</t>
+          <t>26淮联07</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:00</t>
-        </is>
-      </c>
-      <c r="C29" s="3"/>
+          <t>08-28 19:00</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>283831.SH</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>30.0</v>
+        <v>2.5</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>25苏州银行科创债01(柜台)</t>
+          <t>25淮发03</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>4.04Y</t>
+          <t>3.94Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.6308</t>
+          <t>1.8585</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6454,12 +6664,12 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>苏州银行股份有限公司</t>
+          <t>淮安市国有联合投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>A- 60.29</t>
+          <t>C- 18.06</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6469,7 +6679,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6486,12 +6696,12 @@
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6499,62 +6709,54 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z29" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+          <t>本期债券募集资金扣除发行费用后,拟将全部用于偿还公司债券本金[23淮发V2]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国银行股份有限公司,中国邮政储蓄银行股份有限公司,中国工商银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国光大银行股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,国信证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,招商证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>苏州银行股份有限公司2026年第一期金融债券</t>
+          <t>淮安市国有联合投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种二)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK29" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6562,7 +6764,7 @@
       </c>
       <c r="AM29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN29" s="3" t="inlineStr">
@@ -6572,32 +6774,32 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6630,49 +6832,53 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26宜都国通MTN001</t>
+          <t>26淮联06</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
-        </is>
-      </c>
-      <c r="C30" s="3"/>
+          <t>08-28 19:00</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>283830.SH</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.0</v>
+        <v>2.5</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26宜都国通CP001</t>
+          <t>24淮安国联PPN003</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>203D</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.6759</t>
+          <t>1.7748</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -6682,12 +6888,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>宜都市国通投资开发有限责任公司</t>
+          <t>淮安市国有联合投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>D- 2.97</t>
+          <t>C- 18.06</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6697,7 +6903,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -6707,42 +6913,46 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X30" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>1.76%~1.86%</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>湖北省-宜昌市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期基础发行规模0.00亿元，发行金额上限4.00亿元，募集资金拟用于偿还接续“25宜都国通CP002”的专项过桥贷款；本期募集资金拟用于偿还“25宜都国通CP002”本金4.00亿元</t>
+          <t>本期债券募集资金扣除发行费用后,拟将全部用于偿还公司债券本金[23淮发V2]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,汉口银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,东吴证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
@@ -6752,44 +6962,44 @@
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>宜都市国通投资开发有限责任公司2026年度第一期中期票据</t>
+          <t>淮安市国有联合投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种一)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
+          <t>2029-09-01</t>
         </is>
       </c>
       <c r="AK30" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL30" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AM30" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
           <t>城投</t>
@@ -6797,7 +7007,7 @@
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
@@ -6845,71 +7055,73 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ30" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ30" s="3"/>
     </row>
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26海峡环保SCP002</t>
+          <t>26XCF13</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
-        </is>
-      </c>
-      <c r="C31" s="3"/>
+          <t>08-28 19:00</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>283837.SH</t>
+        </is>
+      </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3+2+2</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.0</v>
+        <v>6.5</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>26海峡环保SCP001</t>
+          <t>26XCF11</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>159D</t>
+          <t>2.98Y+4.00Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.5369</t>
+          <t>1.7657</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7300</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>福建海峡环保集团股份有限公司</t>
+          <t>成都兴城投资集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>D- 3.00</t>
+          <t>C 28.72</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -6919,7 +7131,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>08-28 10:00</t>
+          <t>08-28 16:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -6929,42 +7141,46 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X31" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>1.74%~1.84%</t>
+        </is>
+      </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额3.00亿元,拟用于偿还金融机构借款</t>
+          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途,具体用途根据发行人资金需求情况确定。</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,华泰联合证券有限责任公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -6974,40 +7190,40 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>福建海峡环保集团股份有限公司2026年度第二期超短期融资券</t>
+          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行公司债券(第七期)(品种一)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2027-05-28</t>
+          <t>2033-09-01</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AM31" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -7020,27 +7236,27 @@
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-01</t>
         </is>
       </c>
       <c r="AV31" s="3" t="inlineStr">
@@ -7050,7 +7266,7 @@
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
@@ -7068,49 +7284,57 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26传化MTN001(科创债)</t>
+          <t>26堰控01</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
-        </is>
-      </c>
-      <c r="C32" s="3"/>
+          <t>08-28 19:00</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>520442.SZ</t>
+        </is>
+      </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>66.81</v>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>25生产兵团MTN002</t>
+          <t>26十堰城控PPN001</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2.30Y</t>
+          <t>4.89Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.7048</t>
+          <t>2.0561</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -7120,10 +7344,14 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>传化智联股份有限公司</t>
-        </is>
-      </c>
-      <c r="P32" s="3"/>
+          <t>十堰市城市发展控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>C+ 30.21</t>
+        </is>
+      </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
@@ -7131,7 +7359,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7141,88 +7369,92 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X32" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>1.96%~2.06%</t>
+        </is>
+      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>湖北省-十堰市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>发行人本期科技创新债券发行规模为2亿元,其中1亿元用于偿还发行人有息负债,1亿元用于子公司浙江传化功能新材料有限公司纺织工业印染助剂、纺织品整理剂、化学试剂和助剂等功能化学品和新材料领域产品的研发和技术突破的投入</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还即将回售的公司债券本金[23堰控03]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>长江证券股份有限公司,华鑫证券有限责任公司,中国国际金融股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>传化智联股份有限公司2026年度第一期科技创新债券</t>
+          <t>十堰市城市发展控股集团有限公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2028-08-31</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AM32" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
@@ -7237,17 +7469,17 @@
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>物流</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7280,64 +7512,64 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26长安汇通MTN003(科创债)</t>
+          <t>26长沙银行三农债</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 16:30</t>
         </is>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.0</v>
+        <v>20.0</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.40</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26长安汇通MTN002</t>
+          <t>26长沙银行债02</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>4.82Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.9570</t>
+          <t>1.6023</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6050/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>长安汇通集团有限责任公司</t>
+          <t>长沙银行股份有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>B- 38.33</t>
+          <t>A 72.86</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7357,7 +7589,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U33" s="3"/>
@@ -7367,32 +7599,40 @@
           <t>4</t>
         </is>
       </c>
-      <c r="X33" s="3"/>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>1.56%~1.66%</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z33" s="3"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券发行规模为6亿元,募集资金拟全部用于置换本期债券发行之日起一年以内科技创新领域基金出资和科技创新领域股权投资[25长安汇通SCP002,23长安汇通PPN001,25长安汇通SCP003,23长安汇通PPN002]</t>
+          <t>本期债券募集资金将依据适用法律和监管部门的批准,专项用于发放涉农贷款。</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,兴业银行股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,广发证券股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7407,7 +7647,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>长安汇通集团有限责任公司2026年度第三期科技创新债券</t>
+          <t>长沙银行股份有限公司2026年"三农"专项金融债券</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7417,57 +7657,57 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
+          <t>2029-09-01</t>
         </is>
       </c>
       <c r="AK33" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7500,64 +7740,70 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26川高速MTN005</t>
+          <t>26平安租赁CP003</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
-        </is>
-      </c>
-      <c r="C34" s="3"/>
+          <t>08-31 18:00</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>042680303.IB</t>
+        </is>
+      </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.97Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F34" s="3"/>
+        <v>4.0</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.80</t>
+          <t>1.31 ~ 1.51</t>
         </is>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>24川高速MTN006</t>
+          <t>26平安租赁CP002</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2.64Y</t>
+          <t>355D</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.6868</t>
+          <t>1.5665</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司</t>
+          <t>平安国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 17.21</t>
+          <t>C- 20.62</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7577,17 +7823,21 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X34" s="3"/>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>1.55%~1.59%</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -7596,28 +7846,28 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具拟募集资金7亿元,拟全部用于偿付到期债务融资工具:【23川高速MTN006(革命老区)】。</t>
+          <t>发行人本次发行短期融资券拟募集资金4亿元，拟全部用于偿还发行人银行借款</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,中信银行股份有限公司</t>
+          <t>渤海银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr">
@@ -7627,7 +7877,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司2026年度第五期中期票据</t>
+          <t>平安国际融资租赁有限公司2026年度第三期短期融资券</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7637,86 +7887,92 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
-        </is>
-      </c>
-      <c r="AK34" s="3"/>
+          <t>2027-08-21</t>
+        </is>
+      </c>
+      <c r="AK34" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL34" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AM34" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN34" s="3" t="inlineStr">
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY34" s="3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AO34" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ34" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR34" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>高速公路</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV34" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW34" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX34" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY34" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AZ34" s="3"/>
+      <c r="AZ34" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26中建材集MTN004(科创债)</t>
+          <t>26宜都国通MTN001</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -7726,43 +7982,45 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>1100000256648.IB</t>
+          <t>102683456.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="F35" s="3"/>
+        <v>4.0</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.48 ~ 1.68</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>24中建材集MTN001A(科创票据)</t>
+          <t>26宜都国通CP001</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>2.95Y</t>
+          <t>203D</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.6800</t>
+          <t>1.6759</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -7772,12 +8030,12 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>中国建材集团有限公司</t>
+          <t>宜都市国通投资开发有限责任公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.33</t>
+          <t>D- 2.97</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -7804,29 +8062,33 @@
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X35" s="3"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>2.11%~2.21%</t>
+        </is>
+      </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>湖北省-宜昌市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模为11亿元,募集资金用于偿还有息债务；本期科技创新债券的募集资金穿透实际用于发行人科技创新业务及主营业务新材料核心板块,主要投向新材料领域项下玻璃纤维、石膏板、风电叶片等的研发设备购置、核心生产装备升级改造及核心物料采购等</t>
+          <t>本期基础发行规模0.00亿元，发行金额上限4.00亿元，募集资金拟用于偿还接续“25宜都国通CP002”的专项过桥贷款；本期募集资金拟用于偿还“25宜都国通CP002”本金4.00亿元</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>广发证券股份有限公司,汉口银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
@@ -7837,7 +8099,7 @@
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
@@ -7847,7 +8109,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>中国建材集团有限公司2026年度第四期科技创新债券</t>
+          <t>宜都市国通投资开发有限责任公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -7857,10 +8119,14 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
-        </is>
-      </c>
-      <c r="AK35" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK35" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL35" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -7878,32 +8144,32 @@
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -7931,12 +8197,14 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ35" s="3"/>
+      <c r="AZ35" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26南京交建SCP006</t>
+          <t>26海峡环保SCP002</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -7944,16 +8212,22 @@
           <t>08-28 18:00</t>
         </is>
       </c>
-      <c r="C36" s="3"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>012682173.IB</t>
+        </is>
+      </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 1.70</t>
@@ -7963,37 +8237,37 @@
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26南京交建SCP004</t>
+          <t>26海峡环保SCP001</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>255D</t>
+          <t>159D</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.5369</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>1.5300/1.4090</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司</t>
+          <t>福建海峡环保集团股份有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C- 24.83</t>
+          <t>D- 3.00</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8003,7 +8277,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 10:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8020,29 +8294,33 @@
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X36" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>1.56%~1.60%</t>
+        </is>
+      </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额3.5亿元,本期发行的募集资金扣除发行费用后用于偿还发行人本级及子公司有息债务</t>
+          <t>本期超短期融资券发行金额3.00亿元,拟用于偿还金融机构借款</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,南京银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
@@ -8063,7 +8341,7 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司2026年度第六期超短期融资券</t>
+          <t>福建海峡环保集团股份有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8094,32 +8372,32 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8147,14 +8425,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ36" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ36" s="3"/>
     </row>
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26海发国资MTN003</t>
+          <t>26传化MTN001(科创债)</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8162,58 +8438,60 @@
           <t>08-28 18:00</t>
         </is>
       </c>
-      <c r="C37" s="3"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>102683451.IB</t>
+        </is>
+      </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.80 ~ 2.50</t>
         </is>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>24海发国资MTN004</t>
+          <t>25生产兵团MTN002</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>2.30Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.9062</t>
+          <t>1.7048</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>--/1.8800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>青岛海发国有资本投资运营集团有限公司</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t>C+ 34.98</t>
-        </is>
-      </c>
+          <t>传化智联股份有限公司</t>
+        </is>
+      </c>
+      <c r="P37" s="3"/>
       <c r="Q37" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
@@ -8238,10 +8516,14 @@
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X37" s="3"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8250,17 +8532,17 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期发行规模为人民币10亿元，本期债务融资工具募集资金将用于偿还发行人合并范围内有息债务本金。[25海发国资SCP006,26海发国资SCP001,23海发国资MTN003]</t>
+          <t>发行人本期科技创新债券发行规模为2亿元,其中1亿元用于偿还发行人有息负债,1亿元用于子公司浙江传化功能新材料有限公司纺织工业印染助剂、纺织品整理剂、化学试剂和助剂等功能化学品和新材料领域产品的研发和技术突破的投入</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,渤海银行股份有限公司</t>
+          <t>浙商银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8271,7 +8553,7 @@
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
@@ -8281,7 +8563,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>青岛海发国有资本投资运营集团有限公司2026年度第三期中期票据</t>
+          <t>传化智联股份有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8291,7 +8573,7 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t>2028-08-31</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
@@ -8312,32 +8594,32 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>物流</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8370,7 +8652,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26靖滨01</t>
+          <t>26长安汇通MTN003(科创债)</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8380,7 +8662,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>283740.SH</t>
+          <t>102683454.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -8389,34 +8671,36 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.60 ~ 2.40</t>
         </is>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>24靖滨03</t>
+          <t>26长安汇通MTN002</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>4.82Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.7776</t>
+          <t>1.9570</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -8426,12 +8710,12 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司</t>
+          <t>长安汇通集团有限责任公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C- 15.41</t>
+          <t>B- 35.21</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8441,7 +8725,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8451,42 +8735,46 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X38" s="3"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>1.89%~1.99%</t>
+        </is>
+      </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还发行人即将到期的公司债券本金；本期债券募集资金中6.6亿元仅用于偿还发行人即将到期的公司债券本金；本期债券为5年期债券,募集资金拟全部用于偿还到期的公司债券本金[23靖滨02]</t>
+          <t>本期科技创新债券发行规模为6亿元,募集资金拟全部用于置换本期债券发行之日起一年以内科技创新领域基金出资和科技创新领域股权投资[25长安汇通SCP002,23长安汇通PPN001,25长安汇通SCP003,23长安汇通PPN002]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,中信证券股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -8496,28 +8784,32 @@
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>长安汇通集团有限责任公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK38" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK38" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL38" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM38" s="3" t="inlineStr">
@@ -8527,37 +8819,37 @@
       </c>
       <c r="AN38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -8590,7 +8882,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26XCF13</t>
+          <t>26川高速MTN005</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8600,58 +8892,60 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>283837.SH</t>
+          <t>102683446.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3+2+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F39" s="3"/>
+        <v>7.0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>7.0</v>
+      </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.50 ~ 1.80</t>
         </is>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26XCF11</t>
+          <t>24川高速MTN006</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>2.98Y+4.00Y</t>
+          <t>2.64Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.7472</t>
+          <t>1.6868</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>1.8200/1.7400</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司</t>
+          <t>四川高速公路建设开发集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C 28.87</t>
+          <t>C- 17.25</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -8661,7 +8955,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -8671,7 +8965,7 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U39" s="3"/>
@@ -8681,7 +8975,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X39" s="3"/>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>1.60%~1.70%</t>
+        </is>
+      </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8690,23 +8988,23 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途,具体用途根据发行人资金需求情况确定。</t>
+          <t>发行人本期债务融资工具拟募集资金7亿元,拟全部用于偿付到期债务融资工具:【23川高速MTN006(革命老区)】。</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,华泰联合证券有限责任公司,申万宏源证券有限公司</t>
+          <t>中国民生银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -8716,75 +9014,75 @@
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行公司债券(第七期)(品种一)</t>
+          <t>四川高速公路建设开发集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2033-09-01</t>
+          <t>2029-08-31</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>高速公路</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM39" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO39" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ39" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR39" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS39" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT39" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU39" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
       <c r="AV39" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -8792,7 +9090,7 @@
       </c>
       <c r="AW39" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX39" s="3" t="inlineStr">
@@ -8810,7 +9108,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26皖担Y1</t>
+          <t>26中建材集MTN004(科创债)</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -8820,43 +9118,45 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>245991.SH</t>
+          <t>102683447.IB</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="F40" s="3"/>
+        <v>11.0</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>11.0</v>
+      </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.48 ~ 1.68</t>
         </is>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>25安徽担保PPN001</t>
+          <t>24中建材集MTN001A(科创票据)</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>2.14Y</t>
+          <t>2.95Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.7477</t>
+          <t>1.6800</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -8866,12 +9166,12 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>安徽省信用融资担保集团有限公司</t>
+          <t>中国建材集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>C+ 33.13</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -8881,7 +9181,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -8898,10 +9198,14 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X40" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>1.62%~1.72%</t>
+        </is>
+      </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8910,38 +9214,38 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,发行人拟将15亿元用于置换2026年8月使用自有资金偿付到期的15亿元23皖担Y1[23皖担Y1]</t>
+          <t>本期债务融资工具发行规模为11亿元,募集资金用于偿还有息债务；本期科技创新债券的募集资金穿透实际用于发行人科技创新业务及主营业务新材料核心板块,主要投向新材料领域项下玻璃纤维、石膏板、风电叶片等的研发设备购置、核心生产装备升级改造及核心物料采购等</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国国际金融股份有限公司,国元证券股份有限公司,华安证券股份有限公司</t>
+          <t>江苏银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>安徽省信用融资担保集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
+          <t>中国建材集团有限公司2026年度第四期科技创新债券</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -8957,54 +9261,54 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr">
+        <is>
+          <t>建材制造</t>
+        </is>
+      </c>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>综合建材</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>综合建材</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>水泥制造</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM40" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AO40" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ40" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR40" s="3" t="inlineStr">
-        <is>
-          <t>担保</t>
-        </is>
-      </c>
-      <c r="AS40" s="3" t="inlineStr">
-        <is>
-          <t>再担保</t>
-        </is>
-      </c>
-      <c r="AT40" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU40" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV40" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -9012,7 +9316,7 @@
       </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX40" s="3" t="inlineStr">
@@ -9030,7 +9334,7 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26XCF14</t>
+          <t>26南京交建SCP006</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9040,58 +9344,60 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>283838.SH</t>
+          <t>012682174.IB</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>5+2+2</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F41" s="3"/>
+        <v>3.5</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>3.5</v>
+      </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26XCF12</t>
+          <t>26南京交建SCP004</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>4.98Y+4.00Y</t>
+          <t>255D</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.8941</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>1.9300/1.8900</t>
+          <t>--/1.4090</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司</t>
+          <t>南京市交通建设投资控股(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C 28.87</t>
+          <t>C 28.70</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9101,7 +9407,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9111,17 +9417,21 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X41" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>1.51%~1.55%</t>
+        </is>
+      </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -9130,23 +9440,23 @@
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途,具体用途根据发行人资金需求情况确定。</t>
+          <t>本期超短期融资券发行金额3.5亿元,本期发行的募集资金扣除发行费用后用于偿还发行人本级及子公司有息债务</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,申万宏源证券有限公司</t>
+          <t>中信银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
@@ -9156,79 +9466,75 @@
       </c>
       <c r="AG41" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行公司债券(第七期)(品种二)</t>
+          <t>南京市交通建设投资控股(集团)有限责任公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2035-09-01</t>
-        </is>
-      </c>
-      <c r="AK41" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-05-28</t>
+        </is>
+      </c>
+      <c r="AK41" s="3"/>
       <c r="AL41" s="3" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>高速公路</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM41" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO41" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ41" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR41" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS41" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT41" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU41" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
       <c r="AV41" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -9236,7 +9542,7 @@
       </c>
       <c r="AW41" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX41" s="3" t="inlineStr">
@@ -9249,12 +9555,14 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ41" s="3"/>
+      <c r="AZ41" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26堰控01</t>
+          <t>26海发国资MTN003</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9264,58 +9572,60 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>520442.SZ</t>
+          <t>102683445.IB</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F42" s="3"/>
+      <c r="F42" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>26十堰城控PPN001</t>
+          <t>24海发国资MTN004</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>4.89Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>2.0561</t>
+          <t>1.9062</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9200/1.8800</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>十堰市城市发展控股集团有限公司</t>
+          <t>青岛海发国有资本投资运营集团有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.21</t>
+          <t>B- 35.22</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9325,7 +9635,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9335,42 +9645,46 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X42" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>1.77%~1.87%</t>
+        </is>
+      </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>湖北省-十堰市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还即将回售的公司债券本金[23堰控03]</t>
+          <t>本期发行规模为人民币10亿元，本期债务融资工具募集资金将用于偿还发行人合并范围内有息债务本金。[25海发国资SCP006,26海发国资SCP001,23海发国资MTN003]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,华鑫证券有限责任公司,中国国际金融股份有限公司,招商证券股份有限公司</t>
+          <t>中信银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
@@ -9380,28 +9694,28 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>十堰市城市发展控股集团有限公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>青岛海发国有资本投资运营集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2029-08-31</t>
         </is>
       </c>
       <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM42" s="3" t="inlineStr">
@@ -9411,32 +9725,32 @@
       </c>
       <c r="AN42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
@@ -9474,53 +9788,57 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26淮联06</t>
+          <t>26靖滨01</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>283830.SH</t>
+          <t>283740.SH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>2.5</v>
+        <v>6.6</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>77.81</v>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>24淮安国联PPN003</t>
+          <t>24靖滨03</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.7748</t>
+          <t>1.7952</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -9530,12 +9848,12 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司</t>
+          <t>靖江市滨江新城投资开发有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 18.24</t>
+          <t>C- 14.49</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9562,29 +9880,33 @@
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X43" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>1.97%~2.07%</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将全部用于偿还公司债券本金[23淮发V2]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还发行人即将到期的公司债券本金；本期债券募集资金中6.6亿元仅用于偿还发行人即将到期的公司债券本金；本期债券为5年期债券,募集资金拟全部用于偿还到期的公司债券本金[23靖滨02]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,东吴证券股份有限公司,招商证券股份有限公司</t>
+          <t>天风证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
@@ -9605,7 +9927,7 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种一)</t>
+          <t>靖江市滨江新城投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
@@ -9615,14 +9937,10 @@
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK43" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="AK43" s="3"/>
       <c r="AL43" s="3" t="inlineStr">
         <is>
           <t/>
@@ -9640,12 +9958,12 @@
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
@@ -9698,17 +10016,17 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26淮联07</t>
+          <t>26蓉西01</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>283831.SH</t>
+          <t>283832.SH</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -9717,7 +10035,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>2.5</v>
+        <v>10.0</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="inlineStr">
@@ -9725,41 +10043,45 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
+      <c r="H44" s="4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>51.81</v>
+      </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>25淮发03</t>
+          <t>25蓉西01</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>3.94Y</t>
+          <t>3.96Y+2.00Y</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.8547</t>
+          <t>1.9319</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>--/1.7500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司</t>
+          <t>成都温江兴蓉西城市运营集团有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C- 18.24</t>
+          <t>C- 15.65</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -9779,36 +10101,40 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X44" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>1.95%~2.05%</t>
+        </is>
+      </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将全部用于偿还公司债券本金[23淮发V2]</t>
+          <t>本期公司债券募集资金扣除发行费用后,4亿元用于置换发行人偿还“23蓉西01”公司债券本金的自有资金,6亿元用于偿还即将回售的“23蓉西02”公司债券本金[23蓉西01,23蓉西02]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,招商证券股份有限公司,东吴证券股份有限公司</t>
+          <t>广发证券股份有限公司,国投证券股份有限公司,中天证券股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
@@ -9829,7 +10155,7 @@
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种二)</t>
+          <t>成都温江兴蓉西城市运营集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -9839,10 +10165,14 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK44" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK44" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL44" s="3" t="inlineStr">
         <is>
           <t/>
@@ -9855,7 +10185,7 @@
       </c>
       <c r="AN44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO44" s="3" t="inlineStr">
@@ -9865,22 +10195,22 @@
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
@@ -9918,7 +10248,7 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26蓉西01</t>
+          <t>26南京交建SCP005</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -9928,58 +10258,60 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>283832.SH</t>
+          <t>012682175.IB</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F45" s="3"/>
+        <v>4.5</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>4.5</v>
+      </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>25蓉西01</t>
+          <t>26南京交建SCP004</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>3.96Y+2.00Y</t>
+          <t>255D</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.9282</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4090</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>成都温江兴蓉西城市运营集团有限公司</t>
+          <t>南京市交通建设投资控股(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C- 20.74</t>
+          <t>C 28.70</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -9989,7 +10321,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10006,35 +10338,39 @@
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X45" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>1.51%~1.55%</t>
+        </is>
+      </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,4亿元用于置换发行人偿还“23蓉西01”公司债券本金的自有资金,6亿元用于偿还即将回售的“23蓉西02”公司债券本金[23蓉西01,23蓉西02]</t>
+          <t>本期超短期融资券发行金额4.5亿元,本期发行的募集资金拟用于偿还发行人有息债务[26南京交建SCP002]</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,国投证券股份有限公司,中天证券股份有限公司</t>
+          <t>南京银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
@@ -10044,79 +10380,75 @@
       </c>
       <c r="AG45" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>成都温江兴蓉西城市运营集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>南京市交通建设投资控股(集团)有限责任公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK45" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-05-28</t>
+        </is>
+      </c>
+      <c r="AK45" s="3"/>
       <c r="AL45" s="3" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>高速公路</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM45" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AO45" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ45" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR45" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS45" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT45" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU45" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV45" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -10137,12 +10469,14 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ45" s="3"/>
+      <c r="AZ45" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26金义03</t>
+          <t>26中荆06</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10152,58 +10486,62 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>283806.SH</t>
+          <t>283811.SH</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>10.0</v>
+        <v>0.7</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 2.35</t>
-        </is>
-      </c>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>57.81</v>
+      </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>26金义02</t>
+          <t>24中荆投资PPN002</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>2.79Y+2.00Y</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.7589</t>
+          <t>1.9247</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>1.7800/1.7600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>浙江金义控股集团有限公司</t>
+          <t>中荆投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>B+ 57.22</t>
+          <t>C- 19.54</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10213,7 +10551,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -10223,39 +10561,47 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X46" s="3"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>1.81%~1.91%</t>
+        </is>
+      </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>湖北省-荆门市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除发行费用后,拟全部用于偿还到期的公司债券“23金义03”。[23金义03]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券本金。[G23中荆3]</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,国金证券股份有限公司,光大证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD46" s="3"/>
+          <t>国泰海通证券股份有限公司,长江证券股份有限公司,东方证券股份有限公司,国金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr">
+        <is>
+          <t>长江产业投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE46" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -10273,7 +10619,7 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>浙江金义控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>中荆投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10283,10 +10629,14 @@
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK46" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK46" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL46" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10299,32 +10649,32 @@
       </c>
       <c r="AN46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
@@ -10334,17 +10684,17 @@
       </c>
       <c r="AU46" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t/>
         </is>
       </c>
       <c r="AV46" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW46" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX46" s="3" t="inlineStr">
@@ -10362,64 +10712,72 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26南京交建SCP005</t>
+          <t>26皖担Y1</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
-        </is>
-      </c>
-      <c r="C47" s="3"/>
+          <t>08-28 19:00</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>245991.SH</t>
+        </is>
+      </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>4.5</v>
+        <v>15.0</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
-        </is>
-      </c>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>54.0</v>
+      </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>26南京交建SCP004</t>
+          <t>25安徽担保PPN001</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>255D</t>
+          <t>2.14Y</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.7477</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>1.5300/1.4090</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司</t>
+          <t>安徽省信用融资担保集团有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C- 24.83</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10429,7 +10787,7 @@
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 16:00</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
@@ -10446,10 +10804,14 @@
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X47" s="3"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>1.74%~1.84%</t>
+        </is>
+      </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -10458,23 +10820,23 @@
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额4.5亿元,本期发行的募集资金拟用于偿还发行人有息债务[26南京交建SCP002]</t>
+          <t>本期公司债券募集资金扣除发行费用后,发行人拟将15亿元用于置换2026年8月使用自有资金偿付到期的15亿元23皖担Y1[23皖担Y1]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,江苏银行股份有限公司</t>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,国元证券股份有限公司,华安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
       <c r="AE47" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF47" s="3" t="inlineStr">
@@ -10484,12 +10846,12 @@
       </c>
       <c r="AG47" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司2026年度第五期超短期融资券</t>
+          <t>安徽省信用融资担保集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -10499,13 +10861,13 @@
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2027-05-28</t>
+          <t>2029-08-31</t>
         </is>
       </c>
       <c r="AK47" s="3"/>
       <c r="AL47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t/>
         </is>
       </c>
       <c r="AM47" s="3" t="inlineStr">
@@ -10520,32 +10882,32 @@
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP47" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ47" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>担保</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>再担保</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
@@ -10560,7 +10922,7 @@
       </c>
       <c r="AW47" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX47" s="3" t="inlineStr">
@@ -10573,75 +10935,73 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ47" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ47" s="3"/>
     </row>
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26中荆06</t>
+          <t>26张高Y1(取消发行)</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>283811.SH</t>
+          <t>DY283797.SH</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.7</v>
+        <v>3.0</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>24中荆投资PPN002</t>
+          <t>25张高Y1</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>1.65Y+N</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.9247</t>
+          <t>1.6829</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>1.9300/1.8400</t>
+          <t>--/1.6200</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>中荆投资控股集团有限公司</t>
+          <t>张家港市高铁投资发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>C- 19.54</t>
+          <t>C- 19.06</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -10661,17 +11021,21 @@
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X48" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -10680,24 +11044,20 @@
       <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>湖北省-荆门市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券本金。[G23中荆3]</t>
+          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金。[23张高Y2]</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,长江证券股份有限公司,东方证券股份有限公司,国金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD48" s="3" t="inlineStr">
-        <is>
-          <t>长江产业投资集团有限公司</t>
-        </is>
-      </c>
+          <t>东吴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -10715,7 +11075,7 @@
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>中荆投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)</t>
+          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
@@ -10725,12 +11085,12 @@
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
+          <t>2029-09-01</t>
         </is>
       </c>
       <c r="AK48" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL48" s="3" t="inlineStr">
@@ -10745,12 +11105,12 @@
       </c>
       <c r="AN48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP48" s="3" t="inlineStr">
@@ -10760,22 +11120,22 @@
       </c>
       <c r="AQ48" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT48" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU48" s="3" t="inlineStr">
@@ -10785,12 +11145,12 @@
       </c>
       <c r="AV48" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW48" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX48" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-28.xlsx
+++ b/data/credit_bond_all_2026-08-28.xlsx
@@ -1220,7 +1220,9 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U5" s="3"/>
+      <c r="U5" s="4" t="n">
+        <v>4.31</v>
+      </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
@@ -1393,8 +1395,12 @@
           <t>1.37 ~ 1.67</t>
         </is>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>22.07</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>1.53</t>
@@ -1450,8 +1456,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
+      <c r="U6" s="4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -1619,7 +1629,9 @@
           <t>1.60 ~ 2.60</t>
         </is>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="4" t="n">
+        <v>2.05</v>
+      </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1676,8 +1688,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
+      <c r="U7" s="4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
           <t>7+</t>
@@ -1849,7 +1865,9 @@
           <t>1.10 ~ 2.10</t>
         </is>
       </c>
-      <c r="H8" s="3"/>
+      <c r="H8" s="4" t="n">
+        <v>1.55</v>
+      </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1906,8 +1924,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
+      <c r="U8" s="4" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>1.16</v>
+      </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -2079,7 +2101,9 @@
           <t>1.37 ~ 1.57</t>
         </is>
       </c>
-      <c r="H9" s="3"/>
+      <c r="H9" s="4" t="n">
+        <v>1.43</v>
+      </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -2132,7 +2156,9 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U9" s="3"/>
+      <c r="U9" s="4" t="n">
+        <v>1.6</v>
+      </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
@@ -2263,9 +2289,7 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ9" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ9" s="3"/>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
@@ -2299,7 +2323,9 @@
           <t>2.30 ~ 3.30</t>
         </is>
       </c>
-      <c r="H10" s="3"/>
+      <c r="H10" s="4" t="n">
+        <v>2.44</v>
+      </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -2356,8 +2382,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
+      <c r="U10" s="4" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -2529,8 +2559,12 @@
           <t>1.60 ~ 2.60</t>
         </is>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="H11" s="4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>73.81</v>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
           <t>2.21</t>
@@ -2586,8 +2620,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
+      <c r="U11" s="4" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>1.34</v>
+      </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -2759,8 +2797,12 @@
           <t>1.75 ~ 2.75</t>
         </is>
       </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="H12" s="4" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>111.0</v>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>2.34</t>
@@ -2816,8 +2858,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
+      <c r="U12" s="4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>1.57</v>
+      </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
           <t>6+</t>
@@ -2951,9 +2997,7 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ12" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ12" s="3"/>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
@@ -3217,7 +3261,9 @@
           <t>1.90 ~ 2.29</t>
         </is>
       </c>
-      <c r="H14" s="3"/>
+      <c r="H14" s="4" t="n">
+        <v>2.29</v>
+      </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -3274,8 +3320,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
+      <c r="U14" s="4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>1.1</v>
+      </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
           <t>4-</t>
@@ -3413,9 +3463,7 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ14" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ14" s="3"/>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
@@ -3677,7 +3725,9 @@
           <t>1.50 ~ 2.30</t>
         </is>
       </c>
-      <c r="H16" s="3"/>
+      <c r="H16" s="4" t="n">
+        <v>1.72</v>
+      </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -3734,8 +3784,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
+      <c r="U16" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>3.4</v>
+      </c>
       <c r="W16" s="3"/>
       <c r="X16" s="3" t="inlineStr">
         <is>
@@ -4137,8 +4191,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="H18" s="4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>24.51</v>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
           <t>1.98</t>
@@ -4194,7 +4252,9 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U18" s="3"/>
+      <c r="U18" s="4" t="n">
+        <v>4.66</v>
+      </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
@@ -4422,7 +4482,9 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U19" s="3"/>
+      <c r="U19" s="4" t="n">
+        <v>4.13</v>
+      </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
@@ -4585,8 +4647,12 @@
           <t>1.80 ~ 2.80</t>
         </is>
       </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="H20" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>83.81</v>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
           <t>2.11</t>
@@ -4642,8 +4708,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
+      <c r="U20" s="4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>1.4</v>
+      </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -4809,8 +4879,12 @@
           <t>1.90 ~ 3.00</t>
         </is>
       </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+      <c r="H21" s="4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>96.81</v>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
           <t>2.53</t>
@@ -4866,8 +4940,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
+      <c r="U21" s="4" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>3.33</v>
+      </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
           <t>7-</t>
@@ -5001,9 +5079,7 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ21" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ21" s="3"/>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
@@ -5031,8 +5107,12 @@
           <t>1.60 ~ 2.20</t>
         </is>
       </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="H22" s="4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>53.0</v>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
           <t>1.76</t>
@@ -5088,8 +5168,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
+      <c r="U22" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
           <t>6+</t>
@@ -5219,9 +5303,7 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ22" s="4" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="AZ22" s="3"/>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
@@ -6380,7 +6462,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26XCF14</t>
+          <t>26淮联07</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6390,58 +6472,62 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>283838.SH</t>
+          <t>283831.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>5+2+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>57.81</v>
+      </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26XCF12</t>
+          <t>25淮发03</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>4.98Y+4.00Y</t>
+          <t>3.94Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.9001</t>
+          <t>1.8585</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/1.8900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司</t>
+          <t>淮安市国有联合投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C 28.72</t>
+          <t>C- 18.06</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6451,7 +6537,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6468,7 +6554,7 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
@@ -6484,17 +6570,17 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途,具体用途根据发行人资金需求情况确定。</t>
+          <t>本期债券募集资金扣除发行费用后,拟将全部用于偿还公司债券本金[23淮发V2]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,申万宏源证券有限公司</t>
+          <t>华泰联合证券有限责任公司,招商证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6515,7 +6601,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行公司债券(第七期)(品种二)</t>
+          <t>淮安市国有联合投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种二)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6525,14 +6611,10 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2035-09-01</t>
-        </is>
-      </c>
-      <c r="AK28" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6550,7 +6632,7 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
@@ -6560,17 +6642,17 @@
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
@@ -6580,7 +6662,7 @@
       </c>
       <c r="AU28" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t/>
         </is>
       </c>
       <c r="AV28" s="3" t="inlineStr">
@@ -6590,7 +6672,7 @@
       </c>
       <c r="AW28" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX28" s="3" t="inlineStr">
@@ -6608,7 +6690,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26淮联07</t>
+          <t>26淮联06(取消发行)</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6618,12 +6700,12 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>283831.SH</t>
+          <t>DY283830.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
@@ -6632,29 +6714,29 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>25淮发03</t>
+          <t>24淮安国联PPN003</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>3.94Y</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.8585</t>
+          <t>1.7748</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6701,7 +6783,7 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6722,7 +6804,7 @@
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,招商证券股份有限公司,东吴证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,东吴证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6743,7 +6825,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种二)</t>
+          <t>淮安市国有联合投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6753,10 +6835,14 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK29" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL29" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6832,7 +6918,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26淮联06</t>
+          <t>26XCF13</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6842,58 +6928,62 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>283830.SH</t>
+          <t>283837.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2+2</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>21.46</v>
+      </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>24淮安国联PPN003</t>
+          <t>26XCF11</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>2.98Y+4.00Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.7748</t>
+          <t>1.7657</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7300</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司</t>
+          <t>成都兴城投资集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 18.06</t>
+          <t>C 28.72</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6903,7 +6993,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 16:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -6916,16 +7006,18 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U30" s="3"/>
+      <c r="U30" s="4" t="n">
+        <v>4.05</v>
+      </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -6936,17 +7028,17 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将全部用于偿还公司债券本金[23淮发V2]</t>
+          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途,具体用途根据发行人资金需求情况确定。</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,东吴证券股份有限公司,招商证券股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,华泰联合证券有限责任公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -6967,7 +7059,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种一)</t>
+          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行公司债券(第七期)(品种一)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -6977,64 +7069,60 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
+          <t>2033-09-01</t>
+        </is>
+      </c>
+      <c r="AK30" s="3"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
           <t>2029-09-01</t>
         </is>
       </c>
-      <c r="AK30" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
-      <c r="AL30" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM30" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO30" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ30" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR30" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS30" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT30" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU30" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV30" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7042,7 +7130,7 @@
       </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX30" s="3" t="inlineStr">
@@ -7060,7 +7148,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26XCF13</t>
+          <t>26堰控01</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7070,58 +7158,62 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>283837.SH</t>
+          <t>520442.SZ</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3+2+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>6.5</v>
+        <v>10.0</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>66.81</v>
+      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>26XCF11</t>
+          <t>26十堰城控PPN001</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>2.98Y+4.00Y</t>
+          <t>4.89Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.7657</t>
+          <t>2.0561</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/1.7300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司</t>
+          <t>十堰市城市发展控股集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C 28.72</t>
+          <t>C+ 30.21</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7131,7 +7223,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -7148,33 +7240,33 @@
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.96%~2.06%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>湖北省-十堰市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途,具体用途根据发行人资金需求情况确定。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还即将回售的公司债券本金[23堰控03]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,华泰联合证券有限责任公司,申万宏源证券有限公司</t>
+          <t>长江证券股份有限公司,华鑫证券有限责任公司,中国国际金融股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
@@ -7190,12 +7282,12 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行公司债券(第七期)(品种一)</t>
+          <t>十堰市城市发展控股集团有限公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7205,7 +7297,7 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2033-09-01</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
@@ -7226,12 +7318,12 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
@@ -7256,7 +7348,7 @@
       </c>
       <c r="AU31" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t/>
         </is>
       </c>
       <c r="AV31" s="3" t="inlineStr">
@@ -7266,7 +7358,7 @@
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
@@ -7284,131 +7376,135 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26堰控01</t>
+          <t>26海发国资MTN003</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>08-28 19:00</t>
+          <t>08-28 18:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>520442.SZ</t>
+          <t>102683445.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F32" s="3"/>
+      <c r="F32" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>66.81</v>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="I32" s="3"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>24海发国资MTN004</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>2.94Y</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>1.9062</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>青岛海发国有资本投资运营集团有限公司</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>B- 35.22</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>08-28 09:00</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>26十堰城控PPN001</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>4.89Y</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>2.0561</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>十堰市城市发展控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t>C+ 30.21</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t>08-28 15:00</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>3.3</v>
+      </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.96%~2.06%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>湖北省-十堰市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还即将回售的公司债券本金[23堰控03]</t>
+          <t>本期发行规模为人民币10亿元，本期债务融资工具募集资金将用于偿还发行人合并范围内有息债务本金。[25海发国资SCP006,26海发国资SCP001,23海发国资MTN003]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,华鑫证券有限责任公司,中国国际金融股份有限公司,招商证券股份有限公司</t>
+          <t>中信银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
@@ -7418,28 +7514,28 @@
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>十堰市城市发展控股集团有限公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>青岛海发国有资本投资运营集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2029-08-31</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM32" s="3" t="inlineStr">
@@ -7449,32 +7545,32 @@
       </c>
       <c r="AN32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
@@ -7793,7 +7889,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5600</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -8001,8 +8097,12 @@
           <t>1.80 ~ 2.80</t>
         </is>
       </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="H35" s="4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>81.81</v>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
           <t>1.95</t>
@@ -8058,8 +8158,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
+      <c r="U35" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>1.15</v>
+      </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -8197,9 +8301,7 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ35" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ35" s="3"/>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
@@ -8459,7 +8561,9 @@
           <t>1.80 ~ 2.50</t>
         </is>
       </c>
-      <c r="H37" s="3"/>
+      <c r="H37" s="4" t="n">
+        <v>2.05</v>
+      </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -8512,8 +8616,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
+      <c r="U37" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>1.33</v>
+      </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -8681,8 +8789,12 @@
           <t>1.60 ~ 2.40</t>
         </is>
       </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+      <c r="H38" s="4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>45.81</v>
+      </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
           <t>1.93</t>
@@ -8738,8 +8850,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U38" s="3"/>
-      <c r="V38" s="3"/>
+      <c r="U38" s="4" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>1.79</v>
+      </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -8911,8 +9027,12 @@
           <t>1.50 ~ 1.80</t>
         </is>
       </c>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
+      <c r="H39" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>34.0</v>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
           <t>1.70</t>
@@ -8968,8 +9088,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
+      <c r="U39" s="4" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>1.11</v>
+      </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
           <t>4+</t>
@@ -9137,7 +9261,9 @@
           <t>1.48 ~ 1.68</t>
         </is>
       </c>
-      <c r="H40" s="3"/>
+      <c r="H40" s="4" t="n">
+        <v>1.58</v>
+      </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -9363,8 +9489,12 @@
           <t>1.30 ~ 1.70</t>
         </is>
       </c>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
+      <c r="H41" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>23.07</v>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
           <t>1.48</t>
@@ -9420,8 +9550,12 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
+      <c r="U41" s="4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>1.01</v>
+      </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -9555,77 +9689,77 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ41" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ41" s="3"/>
     </row>
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26海发国资MTN003</t>
+          <t>26靖滨01</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>102683445.IB</t>
+          <t>283740.SH</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>6.6</v>
+      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>77.81</v>
+      </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>24海发国资MTN004</t>
+          <t>24靖滨03</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.9062</t>
+          <t>1.7952</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>1.9200/1.8800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>青岛海发国有资本投资运营集团有限公司</t>
+          <t>靖江市滨江新城投资开发有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>B- 35.22</t>
+          <t>C- 14.49</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9635,7 +9769,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9645,46 +9779,46 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.97%~2.07%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期发行规模为人民币10亿元，本期债务融资工具募集资金将用于偿还发行人合并范围内有息债务本金。[25海发国资SCP006,26海发国资SCP001,23海发国资MTN003]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还发行人即将到期的公司债券本金；本期债券募集资金中6.6亿元仅用于偿还发行人即将到期的公司债券本金；本期债券为5年期债券,募集资金拟全部用于偿还到期的公司债券本金[23靖滨02]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,渤海银行股份有限公司</t>
+          <t>天风证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
@@ -9694,40 +9828,40 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>青岛海发国有资本投资运营集团有限公司2026年度第三期中期票据</t>
+          <t>靖江市滨江新城投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AM42" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>类城投</t>
@@ -9735,7 +9869,7 @@
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
@@ -9788,7 +9922,7 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26靖滨01</t>
+          <t>26蓉西01</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -9798,7 +9932,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>283740.SH</t>
+          <t>283832.SH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -9807,38 +9941,38 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>6.6</v>
+        <v>10.0</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>77.81</v>
+        <v>51.81</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>24靖滨03</t>
+          <t>25蓉西01</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>3.96Y+2.00Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.7952</t>
+          <t>1.9319</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -9848,12 +9982,12 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司</t>
+          <t>成都温江兴蓉西城市运营集团有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 14.49</t>
+          <t>C- 15.65</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9873,7 +10007,7 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U43" s="3"/>
@@ -9885,28 +10019,28 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>1.97%~2.07%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还发行人即将到期的公司债券本金；本期债券募集资金中6.6亿元仅用于偿还发行人即将到期的公司债券本金；本期债券为5年期债券,募集资金拟全部用于偿还到期的公司债券本金[23靖滨02]</t>
+          <t>本期公司债券募集资金扣除发行费用后,4亿元用于置换发行人偿还“23蓉西01”公司债券本金的自有资金,6亿元用于偿还即将回售的“23蓉西02”公司债券本金[23蓉西01,23蓉西02]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,中信证券股份有限公司</t>
+          <t>广发证券股份有限公司,国投证券股份有限公司,中天证券股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
@@ -9927,7 +10061,7 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>成都温江兴蓉西城市运营集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
@@ -9937,10 +10071,14 @@
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK43" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK43" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL43" s="3" t="inlineStr">
         <is>
           <t/>
@@ -9953,12 +10091,12 @@
       </c>
       <c r="AN43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
@@ -9968,17 +10106,17 @@
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
@@ -10016,72 +10154,74 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26蓉西01</t>
+          <t>26南京交建SCP005</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>08-28 19:00</t>
+          <t>08-28 18:00</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>283832.SH</t>
+          <t>012682175.IB</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F44" s="3"/>
+        <v>4.5</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>4.5</v>
+      </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1.93</v>
+        <v>1.4</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>51.81</v>
+        <v>23.07</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>25蓉西01</t>
+          <t>26南京交建SCP004</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>3.96Y+2.00Y</t>
+          <t>255D</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.9319</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4090</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>成都温江兴蓉西城市运营集团有限公司</t>
+          <t>南京市交通建设投资控股(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C- 15.65</t>
+          <t>C 28.70</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10091,7 +10231,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -10104,43 +10244,47 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U44" s="3"/>
-      <c r="V44" s="3"/>
+      <c r="U44" s="4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="V44" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,4亿元用于置换发行人偿还“23蓉西01”公司债券本金的自有资金,6亿元用于偿还即将回售的“23蓉西02”公司债券本金[23蓉西01,23蓉西02]</t>
+          <t>本期超短期融资券发行金额4.5亿元,本期发行的募集资金拟用于偿还发行人有息债务[26南京交建SCP002]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,国投证券股份有限公司,中天证券股份有限公司</t>
+          <t>南京银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF44" s="3" t="inlineStr">
@@ -10150,32 +10294,28 @@
       </c>
       <c r="AG44" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>成都温江兴蓉西城市运营集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>南京市交通建设投资控股(集团)有限责任公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK44" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-05-28</t>
+        </is>
+      </c>
+      <c r="AK44" s="3"/>
       <c r="AL44" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM44" s="3" t="inlineStr">
@@ -10190,32 +10330,32 @@
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
@@ -10248,7 +10388,7 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26南京交建SCP005</t>
+          <t>26中荆06</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10258,60 +10398,62 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>012682175.IB</t>
+          <t>283811.SH</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>4.5</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="F45" s="3"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
-        </is>
-      </c>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>57.81</v>
+      </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26南京交建SCP004</t>
+          <t>24中荆投资PPN002</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>255D</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.9247</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>--/1.4090</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司</t>
+          <t>中荆投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C 28.70</t>
+          <t>C- 19.54</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10321,7 +10463,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10338,39 +10480,43 @@
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>1.81%~1.91%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>湖北省-荆门市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额4.5亿元,本期发行的募集资金拟用于偿还发行人有息债务[26南京交建SCP002]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券本金。[G23中荆3]</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,江苏银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD45" s="3"/>
+          <t>国泰海通证券股份有限公司,长江证券股份有限公司,东方证券股份有限公司,国金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr">
+        <is>
+          <t>长江产业投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
@@ -10380,28 +10526,32 @@
       </c>
       <c r="AG45" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司2026年度第五期超短期融资券</t>
+          <t>中荆投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2027-05-28</t>
-        </is>
-      </c>
-      <c r="AK45" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK45" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t/>
         </is>
       </c>
       <c r="AM45" s="3" t="inlineStr">
@@ -10416,32 +10566,32 @@
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
@@ -10451,7 +10601,7 @@
       </c>
       <c r="AV45" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW45" s="3" t="inlineStr">
@@ -10469,64 +10619,62 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ45" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ45" s="3"/>
     </row>
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26中荆06</t>
+          <t>26皖担Y1</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>283811.SH</t>
+          <t>245991.SH</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.7</v>
+        <v>15.0</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>57.81</v>
+        <v>54.0</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>24中荆投资PPN002</t>
+          <t>25安徽担保PPN001</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>2.14Y</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.9247</t>
+          <t>1.7477</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -10536,12 +10684,12 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>中荆投资控股集团有限公司</t>
+          <t>安徽省信用融资担保集团有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>C- 19.54</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10551,7 +10699,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 16:00</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -10568,40 +10716,36 @@
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>1.81%~1.91%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>湖北省-荆门市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券本金。[G23中荆3]</t>
+          <t>本期公司债券募集资金扣除发行费用后,发行人拟将15亿元用于置换2026年8月使用自有资金偿付到期的15亿元23皖担Y1[23皖担Y1]</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,长江证券股份有限公司,东方证券股份有限公司,国金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD46" s="3" t="inlineStr">
-        <is>
-          <t>长江产业投资集团有限公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,国元证券股份有限公司,华安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -10619,24 +10763,20 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>中荆投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)</t>
+          <t>安徽省信用融资担保集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK46" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-31</t>
+        </is>
+      </c>
+      <c r="AK46" s="3"/>
       <c r="AL46" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10654,32 +10794,32 @@
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>担保</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>再担保</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
@@ -10689,12 +10829,12 @@
       </c>
       <c r="AV46" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW46" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX46" s="3" t="inlineStr">
@@ -10712,7 +10852,7 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26皖担Y1</t>
+          <t>26张高Y1(取消发行)</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10722,7 +10862,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>245991.SH</t>
+          <t>DY283797.SH</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -10731,53 +10871,49 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>15.0</v>
+        <v>3.0</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I47" s="4" t="n">
-        <v>54.0</v>
-      </c>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>25安徽担保PPN001</t>
+          <t>25张高Y1</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>2.14Y</t>
+          <t>1.65Y+N</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.7477</t>
+          <t>1.6829</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6200</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>安徽省信用融资担保集团有限公司</t>
+          <t>张家港市高铁投资发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>C- 19.06</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10787,7 +10923,7 @@
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
@@ -10797,40 +10933,40 @@
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,发行人拟将15亿元用于置换2026年8月使用自有资金偿付到期的15亿元23皖担Y1[23皖担Y1]</t>
+          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金。[23张高Y2]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国国际金融股份有限公司,国元证券股份有限公司,华安证券股份有限公司</t>
+          <t>东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
@@ -10851,20 +10987,24 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>安徽省信用融资担保集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
+          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
-        </is>
-      </c>
-      <c r="AK47" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK47" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL47" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10877,37 +11017,37 @@
       </c>
       <c r="AN47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP47" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ47" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>担保</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>再担保</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
@@ -10922,7 +11062,7 @@
       </c>
       <c r="AW47" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX47" s="3" t="inlineStr">
@@ -10940,7 +11080,7 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26张高Y1(取消发行)</t>
+          <t>26XCF14</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -10950,111 +11090,117 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>DY283797.SH</t>
+          <t>283838.SH</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5+2+2</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>3.0</v>
+        <v>6.5</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>25.7</v>
+      </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>26XCF12</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>4.98Y+4.00Y</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>1.9001</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>成都兴城投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>C 28.72</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>08-28 16:00</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
-          <t>25张高Y1</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>1.65Y+N</t>
-        </is>
-      </c>
-      <c r="M48" s="3" t="inlineStr">
-        <is>
-          <t>1.6829</t>
-        </is>
-      </c>
-      <c r="N48" s="3" t="inlineStr">
-        <is>
-          <t>--/1.6200</t>
-        </is>
-      </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>张家港市高铁投资发展(集团)有限公司</t>
-        </is>
-      </c>
-      <c r="P48" s="3" t="inlineStr">
-        <is>
-          <t>C- 19.06</t>
-        </is>
-      </c>
-      <c r="Q48" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="R48" s="3" t="inlineStr">
-        <is>
-          <t>08-28 15:00</t>
-        </is>
-      </c>
-      <c r="S48" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U48" s="3"/>
+      <c r="U48" s="4" t="n">
+        <v>2.17</v>
+      </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金。[23张高Y2]</t>
+          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途,具体用途根据发行人资金需求情况确定。</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
@@ -11075,7 +11221,7 @@
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)(取消发行)</t>
+          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行公司债券(第七期)(品种二)</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
@@ -11085,7 +11231,7 @@
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>2035-09-01</t>
         </is>
       </c>
       <c r="AK48" s="3" t="inlineStr">
@@ -11110,27 +11256,27 @@
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP48" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ48" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT48" s="3" t="inlineStr">
@@ -11140,7 +11286,7 @@
       </c>
       <c r="AU48" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AV48" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-28.xlsx
+++ b/data/credit_bond_all_2026-08-28.xlsx
@@ -4334,7 +4334,7 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26南京交建SCP005</t>
+          <t>26南京交建SCP006</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>012682175.IB</t>
+          <t>012682174.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>4.26</v>
+        <v>4.1</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.0</v>
+        <v>1.01</v>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
@@ -4451,12 +4451,12 @@
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额4.5亿元,本期发行的募集资金拟用于偿还发行人有息债务[26南京交建SCP002]</t>
+          <t>本期超短期融资券发行金额3.5亿元,本期发行的募集资金扣除发行费用后用于偿还发行人本级及子公司有息债务</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,江苏银行股份有限公司</t>
+          <t>中信银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司2026年度第五期超短期融资券</t>
+          <t>南京市交通建设投资控股(集团)有限责任公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4566,7 +4566,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26南京交建SCP006</t>
+          <t>26西安高新MTN009</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4576,62 +4576,62 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>012682174.IB</t>
+          <t>102683452.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.5</v>
+        <v>10.0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.5</v>
+        <v>10.0</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.75 ~ 2.75</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.4</v>
+        <v>2.37</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26南京交建SCP004</t>
+          <t>24西安高新MTN015</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>255D</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>2.3383</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/1.4090</t>
+          <t>2.3500/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司</t>
+          <t>西安高新控股有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C 26.67</t>
+          <t>B- 35.73</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4655,19 +4655,19 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>2.26%~2.36%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4678,23 +4678,23 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额3.5亿元,本期发行的募集资金扣除发行费用后用于偿还发行人本级及子公司有息债务</t>
+          <t>发行人本期中期票据基础发行金额人民币0亿元，发行金额上限人民币10亿元，募集资金全部拟用于偿还发行人到期债务[25西安高新CP010,25西安高新CP011]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,南京银行股份有限公司</t>
+          <t>中信银行股份有限公司,西安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司2026年度第六期超短期融资券</t>
+          <t>西安高新控股有限公司2026年度第九期中期票据</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2027-05-28</t>
+          <t>2029-08-31</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
@@ -4755,17 +4755,17 @@
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26西安高新MTN009</t>
+          <t>26海发国资MTN003</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>102683452.IB</t>
+          <t>102683445.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -4824,41 +4824,41 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.75 ~ 2.75</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.37</v>
+        <v>1.8</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>24西安高新MTN015</t>
+          <t>24海发国资MTN004</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>2.3383</t>
+          <t>1.9062</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>2.3500/--</t>
+          <t>1.9200/1.8800</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>西安高新控股有限公司</t>
+          <t>青岛海发国有资本投资运营集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -4887,19 +4887,19 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.57</v>
+        <v>3.3</v>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>2.26%~2.36%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -4910,17 +4910,17 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行金额人民币0亿元，发行金额上限人民币10亿元，募集资金全部拟用于偿还发行人到期债务[25西安高新CP010,25西安高新CP011]</t>
+          <t>本期发行规模为人民币10亿元，本期债务融资工具募集资金将用于偿还发行人合并范围内有息债务本金。[25海发国资SCP006,26海发国资SCP001,23海发国资MTN003]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,西安银行股份有限公司</t>
+          <t>中信银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>西安高新控股有限公司2026年度第九期中期票据</t>
+          <t>青岛海发国有资本投资运营集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
@@ -5030,7 +5030,7 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26海发国资MTN003</t>
+          <t>26宜都国通MTN001</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5040,62 +5040,62 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>102683445.IB</t>
+          <t>102683456.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>24海发国资MTN004</t>
+          <t>26宜都国通CP001</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>203D</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.9062</t>
+          <t>1.6759</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>1.9200/1.8800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>青岛海发国有资本投资运营集团有限公司</t>
+          <t>宜都市国通投资开发有限责任公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B- 35.73</t>
+          <t>D- 2.66</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5119,40 +5119,40 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>3.3</v>
+        <v>1.15</v>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>2.11%~2.21%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>湖北省-宜昌市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期发行规模为人民币10亿元，本期债务融资工具募集资金将用于偿还发行人合并范围内有息债务本金。[25海发国资SCP006,26海发国资SCP001,23海发国资MTN003]</t>
+          <t>本期基础发行规模0.00亿元，发行金额上限4.00亿元，募集资金拟用于偿还接续“25宜都国通CP002”的专项过桥贷款；本期募集资金拟用于偿还“25宜都国通CP002”本金4.00亿元</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,渤海银行股份有限公司</t>
+          <t>广发证券股份有限公司,汉口银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>青岛海发国有资本投资运营集团有限公司2026年度第三期中期票据</t>
+          <t>宜都市国通投资开发有限责任公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5183,10 +5183,14 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
-        </is>
-      </c>
-      <c r="AK22" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK22" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL22" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -5204,7 +5208,7 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
@@ -5262,7 +5266,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26宜都国通MTN001</t>
+          <t>26金川MTN002</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5272,62 +5276,62 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>102683456.IB</t>
+          <t>102683450.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.90 ~ 2.29</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26宜都国通CP001</t>
+          <t>26金川MTN001</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>203D</t>
+          <t>4.83Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.6759</t>
+          <t>1.8772</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9000/1.7800</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>宜都市国通投资开发有限责任公司</t>
+          <t>金川集团股份有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>D- 2.66</t>
+          <t>C 29.77</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5351,40 +5355,40 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>3.1</v>
+        <v>1.08</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>2.11%~2.21%</t>
+          <t>2.10%~2.20%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>湖北省-宜昌市</t>
+          <t>甘肃省-金昌市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期基础发行规模0.00亿元，发行金额上限4.00亿元，募集资金拟用于偿还接续“25宜都国通CP002”的专项过桥贷款；本期募集资金拟用于偿还“25宜都国通CP002”本金4.00亿元</t>
+          <t>发行人本期拟发行5亿元中期票据,拟全部用于偿还发行人有息负债。</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,汉口银行股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
@@ -5405,7 +5409,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>宜都市国通投资开发有限责任公司2026年度第一期中期票据</t>
+          <t>金川集团股份有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5415,7 +5419,7 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
+          <t>2036-08-31</t>
         </is>
       </c>
       <c r="AK23" s="3" t="inlineStr">
@@ -5440,32 +5444,32 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他有色金属</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5498,7 +5502,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26金川MTN002</t>
+          <t>26盛裕投资MTN001</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5508,12 +5512,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>102683450.IB</t>
+          <t>102690019.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
@@ -5524,46 +5528,46 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.29</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26金川MTN001</t>
+          <t>25盛裕投资MTN003</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>4.83Y</t>
+          <t>1.58Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.8772</t>
+          <t>1.7538</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>1.9000/1.7800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>金川集团股份有限公司</t>
+          <t>扬州盛裕投资发展有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C 29.77</t>
+          <t>C- 17.70</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5573,7 +5577,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 14:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -5587,40 +5591,40 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.08</v>
+        <v>2.86</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.1</v>
+        <v>1.0</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>2.10%~2.20%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>甘肃省-金昌市</t>
+          <t>江苏省-扬州市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>发行人本期拟发行5亿元中期票据,拟全部用于偿还发行人有息负债。</t>
+          <t>发行人承诺本期中期票据5.00亿元用于偿还含回售选择权的中期票据“23盛裕投资MTN001”回售本金部分,金额5.00亿元[23盛裕投资MTN001]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>中国银河证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
@@ -5641,7 +5645,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>金川集团股份有限公司2026年度第二期中期票据</t>
+          <t>扬州盛裕投资发展有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5651,7 +5655,7 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2036-08-31</t>
+          <t>2031-08-31</t>
         </is>
       </c>
       <c r="AK24" s="3" t="inlineStr">
@@ -5676,32 +5680,32 @@
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5*无效</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>其他有色金属</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>金属非金属新材料</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5734,7 +5738,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26盛裕投资MTN001</t>
+          <t>26川高速MTN005</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5744,62 +5748,62 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>102690019.IB</t>
+          <t>102683446.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 1.80</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>25盛裕投资MTN003</t>
+          <t>24川高速MTN006</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>1.58Y</t>
+          <t>2.64Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.7538</t>
+          <t>1.6868</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>扬州盛裕投资发展有限公司</t>
+          <t>四川高速公路建设开发集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C- 17.70</t>
+          <t>C- 17.69</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5809,7 +5813,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>08-28 14:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5823,40 +5827,40 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.86</v>
+        <v>4.84</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.0</v>
+        <v>1.11</v>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>江苏省-扬州市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>发行人承诺本期中期票据5.00亿元用于偿还含回售选择权的中期票据“23盛裕投资MTN001”回售本金部分,金额5.00亿元[23盛裕投资MTN001]</t>
+          <t>发行人本期债务融资工具拟募集资金7亿元,拟全部用于偿付到期债务融资工具:【23川高速MTN006(革命老区)】。</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>中国民生银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
@@ -5877,7 +5881,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>扬州盛裕投资发展有限公司2026年度第一期中期票据</t>
+          <t>四川高速公路建设开发集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5887,14 +5891,10 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK25" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-31</t>
+        </is>
+      </c>
+      <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -5912,12 +5912,12 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>6.5*无效</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
@@ -5927,17 +5927,17 @@
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -5970,7 +5970,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26川高速MTN005</t>
+          <t>26先进制造MTN002(科创债)</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5980,62 +5980,62 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>102683446.IB</t>
+          <t>102683449.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.80</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>24川高速MTN006</t>
+          <t>26先进制造MTN001(科创债)</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>2.64Y</t>
+          <t>2.92Y+2.00Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.6868</t>
+          <t>1.6979</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>1.8000/1.7000</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司</t>
+          <t>成都先进制造产业投资有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 17.69</t>
+          <t>C- 19.13</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 11:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -6059,19 +6059,19 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>4.84</v>
+        <v>3.76</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -6079,20 +6079,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z26" s="3"/>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具拟募集资金7亿元,拟全部用于偿付到期债务融资工具:【23川高速MTN006(革命老区)】。</t>
+          <t>本期科技创新债券拟发行10.00亿元,发行人拟将本期科技创新债券募集资金扣除发行费用后,全部用于基金出资支持科技创新领域发展相关用途。</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,中信银行股份有限公司</t>
+          <t>兴业银行股份有限公司,成都农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
@@ -6113,7 +6117,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司2026年度第五期中期票据</t>
+          <t>成都先进制造产业投资有限公司2026年度第二期科技创新债券</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6123,60 +6127,60 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK26" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP26" s="3"/>
+      <c r="AQ26" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
           <t>2029-08-31</t>
         </is>
       </c>
-      <c r="AK26" s="3"/>
-      <c r="AL26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AM26" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AO26" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ26" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR26" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AT26" s="3" t="inlineStr">
-        <is>
-          <t>高速公路</t>
-        </is>
-      </c>
-      <c r="AU26" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV26" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -6184,7 +6188,7 @@
       </c>
       <c r="AW26" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX26" s="3" t="inlineStr">
@@ -6202,7 +6206,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26先进制造MTN002(科创债)</t>
+          <t>26顺控发展MTN001(并购)</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6212,7 +6216,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>102683449.IB</t>
+          <t>102683444.IB</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -6221,53 +6225,53 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26先进制造MTN001(科创债)</t>
+          <t>25顺控发展MTN001</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>2.92Y+2.00Y</t>
+          <t>1.65Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.6979</t>
+          <t>1.6401</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>1.8000/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>成都先进制造产业投资有限公司</t>
+          <t>广东顺控发展股份有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 19.13</t>
+          <t>C- 13.64</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6277,7 +6281,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>08-28 11:00</t>
+          <t>08-28 14:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6291,19 +6295,15 @@
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>3.76</v>
+        <v>4.5</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+        <v>3.4</v>
+      </c>
+      <c r="W27" s="3"/>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -6318,17 +6318,17 @@
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>广东省-佛山市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券拟发行10.00亿元,发行人拟将本期科技创新债券募集资金扣除发行费用后,全部用于基金出资支持科技创新领域发展相关用途。</t>
+          <t>发行人本期中期票据拟发行6.00亿元,其中28,300.00万元用于偿还发行人并购贷款;12,682.61万元置换发行人过去一年内并购活动的自有资金出资;19,017.39万元用于补充流动资金。</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,成都农村商业银行股份有限公司</t>
+          <t>中国银河证券股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>成都先进制造产业投资有限公司2026年度第二期科技创新债券</t>
+          <t>广东顺控发展股份有限公司2026年度第一期中期票据(并购)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6384,28 +6384,32 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP27" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6438,7 +6442,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26顺控发展MTN001(并购)</t>
+          <t>26华发科技MTN002(科创债)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6448,7 +6452,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>102683444.IB</t>
+          <t>102683455.IB</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -6457,38 +6461,38 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>25顺控发展MTN001</t>
+          <t>26华发科技MTN001(科创债)</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>1.65Y</t>
+          <t>2.79Y+2.00Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.6401</t>
+          <t>2.2887</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -6498,12 +6502,12 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>广东顺控发展股份有限公司</t>
+          <t>珠海华发科技产业集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C- 13.64</t>
+          <t>C 25.37</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6513,7 +6517,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>08-28 14:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6527,15 +6531,19 @@
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>4.5</v>
+        <v>3.14</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="W28" s="3"/>
+        <v>1.34</v>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>2.23%~2.33%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6543,24 +6551,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>广东省-佛山市</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据拟发行6.00亿元,其中28,300.00万元用于偿还发行人并购贷款;12,682.61万元置换发行人过去一年内并购活动的自有资金出资;19,017.39万元用于补充流动资金。</t>
+          <t>本期中期票据发行金额上限为10亿元,募集资金扣除发行费用后,拟全部用于置换本期债券发行日前12个月内发行人自有资金对现有基金的前期出资</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,招商银行股份有限公司</t>
+          <t>中国建设银行股份有限公司,东莞农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6581,7 +6585,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>广东顺控发展股份有限公司2026年度第一期中期票据(并购)</t>
+          <t>珠海华发科技产业集团有限公司2026年度第二期科技创新债券</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6621,27 +6625,27 @@
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6674,7 +6678,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26华发科技MTN002(科创债)</t>
+          <t>26光明02</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6684,12 +6688,12 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>102683455.IB</t>
+          <t>245992.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
@@ -6700,46 +6704,46 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26华发科技MTN001(科创债)</t>
+          <t>24光明02</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>2.79Y+2.00Y</t>
+          <t>2.86Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>2.2887</t>
+          <t>1.6100</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6500/1.6300</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>珠海华发科技产业集团有限公司</t>
+          <t>光明食品(集团)有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C 25.37</t>
+          <t>B+ 57.27</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6749,7 +6753,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6763,19 +6767,17 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="V29" s="4" t="n">
-        <v>1.34</v>
-      </c>
+        <v>4.13</v>
+      </c>
+      <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>2.23%~2.33%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6786,23 +6788,23 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额上限为10亿元,募集资金扣除发行费用后,拟全部用于置换本期债券发行日前12个月内发行人自有资金对现有基金的前期出资</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将10.00亿元用于偿还到期债务[23光明02]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,东莞农村商业银行股份有限公司</t>
+          <t>中银国际证券股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,平安证券股份有限公司,中泰证券股份有限公司,中国国际金融股份有限公司,申万宏源证券有限公司,光大证券股份有限公司,长城证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6812,12 +6814,12 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>珠海华发科技产业集团有限公司2026年度第二期科技创新债券</t>
+          <t>光明食品(集团)有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6827,17 +6829,13 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK29" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-31</t>
+        </is>
+      </c>
+      <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t/>
         </is>
       </c>
       <c r="AM29" s="3" t="inlineStr">
@@ -6857,32 +6855,32 @@
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>轻工制造</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>食品加工</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t/>
         </is>
       </c>
       <c r="AV29" s="3" t="inlineStr">
@@ -6892,7 +6890,7 @@
       </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX29" s="3" t="inlineStr">
@@ -6910,72 +6908,72 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26光明02</t>
+          <t>26皖担Y1</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>245992.SH</t>
+          <t>245991.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>24光明02</t>
+          <t>25安徽担保PPN001</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.86Y</t>
+          <t>2.14Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.6100</t>
+          <t>1.7477</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>1.6500/1.6300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>光明食品(集团)有限公司</t>
+          <t>安徽省信用融资担保集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>B+ 57.27</t>
+          <t>C 27.50</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6985,7 +6983,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 16:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -6999,17 +6997,17 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>4.13</v>
+        <v>3.92</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -7020,17 +7018,17 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将10.00亿元用于偿还到期债务[23光明02]</t>
+          <t>本期公司债券募集资金扣除发行费用后,发行人拟将15亿元用于置换2026年8月使用自有资金偿付到期的15亿元23皖担Y1[23皖担Y1]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>中银国际证券股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,平安证券股份有限公司,中泰证券股份有限公司,中国国际金融股份有限公司,申万宏源证券有限公司,光大证券股份有限公司,长城证券股份有限公司</t>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,国元证券股份有限公司,华安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -7051,7 +7049,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>光明食品(集团)有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>安徽省信用融资担保集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7082,32 +7080,32 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>轻工制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>担保</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>再担保</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>食品加工</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7122,7 +7120,7 @@
       </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX30" s="3" t="inlineStr">
@@ -7140,33 +7138,33 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26皖担Y1</t>
+          <t>26福州地铁GN002(碳中和债)</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>08-28 19:00</t>
+          <t>08-28 18:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>245991.SH</t>
+          <t>132680091.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
@@ -7175,22 +7173,22 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>25安徽担保PPN001</t>
+          <t>GC榕铁02</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>2.14Y</t>
+          <t>4.80Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.7477</t>
+          <t>1.7951</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -7200,12 +7198,12 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>安徽省信用融资担保集团有限公司</t>
+          <t>福州地铁集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C 27.50</t>
+          <t>C 25.05</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7215,7 +7213,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -7229,12 +7227,14 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="V31" s="3"/>
+        <v>3.1429</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>1.57</v>
+      </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
@@ -7250,23 +7250,23 @@
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,发行人拟将15亿元用于置换2026年8月使用自有资金偿付到期的15亿元23皖担Y1[23皖担Y1]</t>
+          <t>募集资金拟全部用于城市轨道交通建设类绿色低碳产业项目，包括福州地铁1号线、2号线、4号线、5号线、6号线、福州至长乐机场城际铁路(F1线)</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国国际金融股份有限公司,国元证券股份有限公司,华安证券股份有限公司</t>
+          <t>中国银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>安徽省信用融资担保集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
+          <t>福州地铁集团有限公司2026年度第二期绿色中期票据(碳中和债)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7291,60 +7291,64 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
-        </is>
-      </c>
-      <c r="AK31" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK31" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL31" s="3" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>公交</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM31" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AO31" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ31" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR31" s="3" t="inlineStr">
-        <is>
-          <t>担保</t>
-        </is>
-      </c>
-      <c r="AS31" s="3" t="inlineStr">
-        <is>
-          <t>再担保</t>
-        </is>
-      </c>
-      <c r="AT31" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU31" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV31" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7352,7 +7356,7 @@
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
@@ -7370,7 +7374,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26福州地铁GN002(碳中和债)</t>
+          <t>26汤山建设PPN001</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7380,62 +7384,62 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>132680091.IB</t>
+          <t>032680504.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.0</v>
+        <v>7.4</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.0</v>
+        <v>7.4</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>GC榕铁02</t>
+          <t>24汤山04</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>4.80Y</t>
+          <t>3.22Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.7951</t>
+          <t>1.7594</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7100</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>福州地铁集团有限公司</t>
+          <t>南京汤山建设投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C 25.05</t>
+          <t>C- 12.91</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7459,46 +7463,42 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.1429</v>
+        <v>2.7162</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>1.57</v>
+        <v>1.0</v>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t>1.74%~1.84%</t>
-        </is>
-      </c>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X32" s="3"/>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>募集资金拟全部用于城市轨道交通建设类绿色低碳产业项目，包括福州地铁1号线、2号线、4号线、5号线、6号线、福州至长乐机场城际铁路(F1线)</t>
+          <t>发行人本次定向债务融资工具注册金额7.40亿元，本期发行金额7.40亿元，募集资金拟全部用于偿还发行人到期债务融资工具本金[25汤山建设SCP001]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,招商银行股份有限公司</t>
+          <t>南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
@@ -7513,24 +7513,20 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>福州地铁集团有限公司2026年度第二期绿色中期票据(碳中和债)</t>
+          <t>南京汤山建设投资发展集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK32" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-31</t>
+        </is>
+      </c>
+      <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -7548,12 +7544,12 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
@@ -7563,17 +7559,17 @@
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7606,7 +7602,7 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26汤山建设PPN001</t>
+          <t>26遂宁兴业PPN001</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7616,62 +7612,62 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>032680504.IB</t>
+          <t>032690010.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.4</v>
+        <v>4.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7.4</v>
+        <v>4.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>24汤山04</t>
+          <t>26伊犁财通PPN001</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>3.22Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.7594</t>
+          <t>2.0881</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/1.7100</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>南京汤山建设投资发展集团有限公司</t>
+          <t>遂宁兴业投资集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C- 12.91</t>
+          <t>D- 2.50</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7681,7 +7677,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 09:30</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7695,17 +7691,21 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>2.7162</v>
+        <v>3.2</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>1.0</v>
+        <v>1.4</v>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X33" s="3"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>2.26%~2.36%</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -7714,17 +7714,17 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>四川省-遂宁市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>发行人本次定向债务融资工具注册金额7.40亿元，本期发行金额7.40亿元，募集资金拟全部用于偿还发行人到期债务融资工具本金[25汤山建设SCP001]</t>
+          <t>本次定向债务融资工具注册规模为4亿元，本期定向债务融资工具基础发行规模0亿元，发行规模上限4亿元。根据发行人的资金需求，拟用于偿还公司存量债务融资工具本金【25遂宁兴业SCP002】、【26遂宁兴业SCP001】</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司</t>
+          <t>重庆银行股份有限公司,光大证券股份有限公司,天津银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>南京汤山建设投资发展集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>遂宁兴业投资集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7755,10 +7755,14 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
-        </is>
-      </c>
-      <c r="AK33" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK33" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -7781,22 +7785,22 @@
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
@@ -7834,57 +7838,57 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26遂宁兴业PPN001</t>
+          <t>26长沙银行三农债01</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 16:30</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>032690010.IB</t>
+          <t>212680028.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.0</v>
+        <v>20.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.0</v>
+        <v>20.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.25</v>
+        <v>1.59</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26伊犁财通PPN001</t>
+          <t>26长沙银行债02</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2.0881</t>
+          <t>1.6023</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -7894,12 +7898,12 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>遂宁兴业投资集团有限公司</t>
+          <t>长沙银行股份有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>D- 2.50</t>
+          <t>A 72.67</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7909,7 +7913,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:30</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7919,50 +7923,50 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>1.4</v>
-      </c>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U34" s="3"/>
+      <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>2.26%~2.36%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z34" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>四川省-遂宁市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具注册规模为4亿元，本期定向债务融资工具基础发行规模0亿元，发行规模上限4亿元。根据发行人的资金需求，拟用于偿还公司存量债务融资工具本金【25遂宁兴业SCP002】、【26遂宁兴业SCP001】</t>
+          <t>本期债券募集资金将依据适用法律和监管部门的批准,专项用于发放涉农贷款。</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>重庆银行股份有限公司,光大证券股份有限公司,天津银行股份有限公司</t>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,兴业银行股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,广发证券股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -7977,67 +7981,67 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>遂宁兴业投资集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>长沙银行股份有限公司2026年"三农"专项金融债券</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
+          <t>2029-09-01</t>
         </is>
       </c>
       <c r="AK34" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL34" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AM34" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8070,72 +8074,72 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26长沙银行三农债01</t>
+          <t>26平安租赁CP003</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:30</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>212680028.IB</t>
+          <t>042680303.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.97Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.31 ~ 1.51</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26长沙银行债02</t>
+          <t>26平安租赁CP002</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>355D</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.6023</t>
+          <t>1.5665</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1.6050/--</t>
+          <t>--/1.5600</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>长沙银行股份有限公司</t>
+          <t>平安国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>A 72.67</t>
+          <t>C- 20.18</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8162,12 +8166,12 @@
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.55%~1.59%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8175,35 +8179,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将依据适用法律和监管部门的批准,专项用于发放涉农贷款。</t>
+          <t>发行人本次发行短期融资券拟募集资金4亿元，拟全部用于偿还发行人银行借款</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,兴业银行股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,广发证券股份有限公司,中国建设银行股份有限公司</t>
+          <t>渤海银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>长沙银行股份有限公司2026年"三农"专项金融债券</t>
+          <t>平安国际融资租赁有限公司2026年度第三期短期融资券</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>2027-08-21</t>
         </is>
       </c>
       <c r="AK35" s="3" t="inlineStr">
@@ -8233,54 +8233,54 @@
       </c>
       <c r="AL35" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM35" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO35" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ35" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR35" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS35" s="3" t="inlineStr">
-        <is>
-          <t>城商行</t>
-        </is>
-      </c>
-      <c r="AT35" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU35" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV35" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -8298,78 +8298,82 @@
       </c>
       <c r="AY35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AZ35" s="3"/>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AZ35" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26平安租赁CP003</t>
+          <t>26长安汇通MTN003(科创债)</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-28 18:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>042680303.IB</t>
+          <t>102683454.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>0.97Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.51</t>
-        </is>
-      </c>
-      <c r="H36" s="3"/>
+          <t>1.60 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1.87</v>
+      </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26平安租赁CP002</t>
+          <t>26长安汇通MTN002</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>355D</t>
+          <t>4.82Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.5665</t>
+          <t>1.9570</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/1.5600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>平安国际融资租赁有限公司</t>
+          <t>长安汇通集团有限责任公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C- 20.18</t>
+          <t>C+ 32.22</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8389,19 +8393,23 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="U36" s="4" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>1.79</v>
+      </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.55%~1.59%</t>
+          <t>1.89%~1.99%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8412,28 +8420,28 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行短期融资券拟募集资金4亿元，拟全部用于偿还发行人银行借款</t>
+          <t>本期科技创新债券发行规模为6亿元,募集资金拟全部用于置换本期债券发行之日起一年以内科技创新领域基金出资和科技创新领域股权投资[25长安汇通SCP002,23长安汇通PPN001,25长安汇通SCP003,23长安汇通PPN002]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司,招商银行股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
@@ -8443,7 +8451,7 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>平安国际融资租赁有限公司2026年度第三期短期融资券</t>
+          <t>长安汇通集团有限责任公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8453,57 +8461,57 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2027-08-21</t>
+          <t>2031-08-31</t>
         </is>
       </c>
       <c r="AK36" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8528,17 +8536,15 @@
       </c>
       <c r="AY36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AZ36" s="4" t="n">
-        <v>0.0</v>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AZ36" s="3"/>
     </row>
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26长安汇通MTN003(科创债)</t>
+          <t>26中建材集MTN004(科创债)</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8548,47 +8554,47 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>102683454.IB</t>
+          <t>102683447.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.40</t>
+          <t>1.48 ~ 1.68</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26长安汇通MTN002</t>
+          <t>24中建材集MTN001A(科创票据)</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>4.82Y</t>
+          <t>2.95Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.9570</t>
+          <t>1.6800</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -8598,12 +8604,12 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>长安汇通集团有限责任公司</t>
+          <t>中国建材集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.22</t>
+          <t>C+ 32.00</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8626,20 +8632,16 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U37" s="4" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="V37" s="4" t="n">
-        <v>1.79</v>
-      </c>
+      <c r="U37" s="3"/>
+      <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.89%~1.99%</t>
+          <t>1.62%~1.72%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8650,17 +8652,17 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券发行规模为6亿元,募集资金拟全部用于置换本期债券发行之日起一年以内科技创新领域基金出资和科技创新领域股权投资[25长安汇通SCP002,23长安汇通PPN001,25长安汇通SCP003,23长安汇通PPN002]</t>
+          <t>本期债务融资工具发行规模为11亿元,募集资金用于偿还有息债务；本期科技创新债券的募集资金穿透实际用于发行人科技创新业务及主营业务新材料核心板块,主要投向新材料领域项下玻璃纤维、石膏板、风电叶片等的研发设备购置、核心生产装备升级改造及核心物料采购等</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>江苏银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8671,7 +8673,7 @@
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
@@ -8681,7 +8683,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>长安汇通集团有限责任公司2026年度第三期科技创新债券</t>
+          <t>中国建材集团有限公司2026年度第四期科技创新债券</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8691,14 +8693,10 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK37" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-31</t>
+        </is>
+      </c>
+      <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -8721,27 +8719,27 @@
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8774,57 +8772,55 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26中建材集MTN004(科创债)</t>
+          <t>26靖滨01</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>102683447.IB</t>
+          <t>283740.SH</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>11.0</v>
-      </c>
+        <v>6.6</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.48 ~ 1.68</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.58</v>
+        <v>2.19</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>24中建材集MTN001A(科创票据)</t>
+          <t>24靖滨03</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2.95Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.6800</t>
+          <t>1.7952</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -8834,12 +8830,12 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>中国建材集团有限公司</t>
+          <t>靖江市滨江新城投资开发有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.00</t>
+          <t>C- 14.86</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8849,7 +8845,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8859,117 +8855,117 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.62%~1.72%</t>
+          <t>1.97%~2.07%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模为11亿元,募集资金用于偿还有息债务；本期科技创新债券的募集资金穿透实际用于发行人科技创新业务及主营业务新材料核心板块,主要投向新材料领域项下玻璃纤维、石膏板、风电叶片等的研发设备购置、核心生产装备升级改造及核心物料采购等</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还发行人即将到期的公司债券本金；本期债券募集资金中6.6亿元仅用于偿还发行人即将到期的公司债券本金；本期债券为5年期债券,募集资金拟全部用于偿还到期的公司债券本金[23靖滨02]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>天风证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>中国建材集团有限公司2026年度第四期科技创新债券</t>
+          <t>靖江市滨江新城投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AM38" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -9002,7 +8998,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26靖滨01</t>
+          <t>26蓉西01</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -9012,7 +9008,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>283740.SH</t>
+          <t>283832.SH</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -9021,36 +9017,38 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F39" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>24靖滨03</t>
+          <t>25蓉西01</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>3.96Y+2.00Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.7952</t>
+          <t>1.9319</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -9060,12 +9058,12 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司</t>
+          <t>成都温江兴蓉西城市运营集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 14.86</t>
+          <t>D 4.57</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9085,10 +9083,12 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U39" s="3"/>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="U39" s="4" t="n">
+        <v>3.51</v>
+      </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
@@ -9097,28 +9097,28 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.97%~2.07%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还发行人即将到期的公司债券本金；本期债券募集资金中6.6亿元仅用于偿还发行人即将到期的公司债券本金；本期债券为5年期债券,募集资金拟全部用于偿还到期的公司债券本金[23靖滨02]</t>
+          <t>本期公司债券募集资金扣除发行费用后,4亿元用于置换发行人偿还“23蓉西01”公司债券本金的自有资金,6亿元用于偿还即将回售的“23蓉西02”公司债券本金[23蓉西01,23蓉西02]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,中信证券股份有限公司</t>
+          <t>广发证券股份有限公司,国投证券股份有限公司,中天证券股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>成都温江兴蓉西城市运营集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9149,10 +9149,14 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK39" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK39" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL39" s="3" t="inlineStr">
         <is>
           <t/>
@@ -9165,12 +9169,12 @@
       </c>
       <c r="AN39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
@@ -9180,17 +9184,17 @@
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
@@ -9228,7 +9232,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26蓉西01</t>
+          <t>26张高Y1(取消发行)</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9238,62 +9242,58 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>283832.SH</t>
+          <t>DY283797.SH</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>3.0</v>
+      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>1.93</v>
-      </c>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>25蓉西01</t>
+          <t>25张高Y1</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>3.96Y+2.00Y</t>
+          <t>1.65Y+N</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.9319</t>
+          <t>1.6829</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6200</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>成都温江兴蓉西城市运营集团有限公司</t>
+          <t>张家港市高铁投资发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>D 4.57</t>
+          <t>C- 19.06</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9313,21 +9313,19 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="U40" s="4" t="n">
-        <v>3.51</v>
-      </c>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -9338,17 +9336,17 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,4亿元用于置换发行人偿还“23蓉西01”公司债券本金的自有资金,6亿元用于偿还即将回售的“23蓉西02”公司债券本金[23蓉西01,23蓉西02]</t>
+          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金。[23张高Y2]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,国投证券股份有限公司,中天证券股份有限公司</t>
+          <t>东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
@@ -9369,7 +9367,7 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>成都温江兴蓉西城市运营集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9379,12 +9377,12 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
+          <t>2029-09-01</t>
         </is>
       </c>
       <c r="AK40" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL40" s="3" t="inlineStr">
@@ -9399,7 +9397,7 @@
       </c>
       <c r="AN40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO40" s="3" t="inlineStr">
@@ -9414,17 +9412,17 @@
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
@@ -9444,7 +9442,7 @@
       </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX40" s="3" t="inlineStr">
@@ -9462,7 +9460,7 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26张高Y1(取消发行)</t>
+          <t>26XCF14</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9472,111 +9470,115 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>DY283797.SH</t>
+          <t>283838.SH</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5+2+2</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>3.0</v>
+        <v>6.5</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H41" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>1.9</v>
+      </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>26XCF12</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>4.98Y+4.00Y</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>1.9001</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>--/1.8900</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>成都兴城投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>C 28.93</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>08-28 16:00</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>25张高Y1</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>1.65Y+N</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>1.6829</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>--/1.6200</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>张家港市高铁投资发展(集团)有限公司</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t>C- 19.06</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>08-28 15:00</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U41" s="3"/>
+      <c r="U41" s="4" t="n">
+        <v>2.17</v>
+      </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金。[23张高Y2]</t>
+          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途,具体用途根据发行人资金需求情况确定。</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
@@ -9597,7 +9599,7 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)(取消发行)</t>
+          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行公司债券(第七期)(品种二)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9607,7 +9609,7 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>2035-09-01</t>
         </is>
       </c>
       <c r="AK41" s="3" t="inlineStr">
@@ -9632,27 +9634,27 @@
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
@@ -9662,7 +9664,7 @@
       </c>
       <c r="AU41" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AV41" s="3" t="inlineStr">
@@ -9690,70 +9692,72 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26XCF14</t>
+          <t>26海峡环保SCP002</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>08-28 19:00</t>
+          <t>08-28 18:00</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>283838.SH</t>
+          <t>012682173.IB</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>5+2+2</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F42" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>26XCF12</t>
+          <t>26海峡环保SCP001</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>4.98Y+4.00Y</t>
+          <t>159D</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.9001</t>
+          <t>1.5369</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/1.8900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司</t>
+          <t>福建海峡环保集团股份有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C 28.93</t>
+          <t>D- 1.50</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9763,7 +9767,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:00</t>
+          <t>08-28 10:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9773,48 +9777,48 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>2.17</v>
+        <v>2.9333</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.56%~1.60%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途,具体用途根据发行人资金需求情况确定。</t>
+          <t>本期超短期融资券发行金额3.00亿元,拟用于偿还金融机构借款</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,申万宏源证券有限公司</t>
+          <t>兴业银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
@@ -9824,79 +9828,75 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行公司债券(第七期)(品种二)</t>
+          <t>福建海峡环保集团股份有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2035-09-01</t>
-        </is>
-      </c>
-      <c r="AK42" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-05-28</t>
+        </is>
+      </c>
+      <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM42" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO42" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ42" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR42" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS42" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT42" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU42" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
       <c r="AV42" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -9904,7 +9904,7 @@
       </c>
       <c r="AW42" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX42" s="3" t="inlineStr">
@@ -9922,57 +9922,57 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26海峡环保SCP002</t>
+          <t>26嘉产03</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>012682173.IB</t>
+          <t>283739.SH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26海峡环保SCP001</t>
+          <t>26嘉产02</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>159D</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.5369</t>
+          <t>1.8940</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>福建海峡环保集团股份有限公司</t>
+          <t>嘉兴市产业发展集团有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>D- 1.50</t>
+          <t>C- 14.95</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>08-28 10:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -10011,44 +10011,44 @@
         </is>
       </c>
       <c r="U43" s="4" t="n">
-        <v>2.9333</v>
+        <v>4.63</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.60%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额3.00亿元,拟用于偿还金融机构借款</t>
+          <t>本期债券募集资金扣除发行费用后其中6亿元用于偿还公司债券到期本金，剩余募集资金用于偿还其他有息债务[23嘉产02]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>东吴证券股份有限公司,平安证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
@@ -10058,28 +10058,32 @@
       </c>
       <c r="AG43" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>福建海峡环保集团股份有限公司2026年度第二期超短期融资券</t>
+          <t>嘉兴市产业发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2027-05-28</t>
-        </is>
-      </c>
-      <c r="AK43" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK43" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t/>
         </is>
       </c>
       <c r="AM43" s="3" t="inlineStr">
@@ -10094,32 +10098,32 @@
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
@@ -10152,17 +10156,17 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26嘉产03</t>
+          <t>26文登蓝海MTN001</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>08-28 19:00</t>
+          <t>08-28 18:00</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>283739.SH</t>
+          <t>102683453.IB</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -10171,38 +10175,38 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>9.0</v>
+        <v>4.2</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>9.0</v>
+        <v>4.2</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>2.30 ~ 3.30</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1.88</v>
+        <v>2.44</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>26嘉产02</t>
+          <t>22蓝海债</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>2.59Y</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.8940</t>
+          <t>2.1091</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -10212,12 +10216,12 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>嘉兴市产业发展集团有限公司</t>
+          <t>威海市文登区蓝海投资开发有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C- 14.95</t>
+          <t>C+ 33.67</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10227,7 +10231,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -10241,44 +10245,46 @@
         </is>
       </c>
       <c r="U44" s="4" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="V44" s="3"/>
+        <v>3.119</v>
+      </c>
+      <c r="V44" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>2.20%~2.30%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>山东省-威海市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后其中6亿元用于偿还公司债券到期本金，剩余募集资金用于偿还其他有息债务[23嘉产02]</t>
+          <t>本期中期票据发行金额4.20亿元,募集资金用于偿还到期债务融资工具本金[23文登蓝海MTN001]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,平安证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>国投证券股份有限公司,中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF44" s="3" t="inlineStr">
@@ -10288,17 +10294,17 @@
       </c>
       <c r="AG44" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>嘉兴市产业发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>威海市文登区蓝海投资开发有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ44" s="3" t="inlineStr">
@@ -10313,7 +10319,7 @@
       </c>
       <c r="AL44" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM44" s="3" t="inlineStr">
@@ -10328,32 +10334,32 @@
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
@@ -10386,7 +10392,7 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26文登蓝海MTN001</t>
+          <t>26中荆06</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10396,7 +10402,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>102683453.IB</t>
+          <t>283811.SH</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -10405,38 +10411,38 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2.30 ~ 3.30</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>2.44</v>
+        <v>1.99</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>22蓝海债</t>
+          <t>24中荆投资PPN002</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>2.59Y</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>2.1091</t>
+          <t>1.9247</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -10446,12 +10452,12 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>威海市文登区蓝海投资开发有限公司</t>
+          <t>中荆投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.67</t>
+          <t>C- 18.67</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10461,7 +10467,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10475,11 +10481,9 @@
         </is>
       </c>
       <c r="U45" s="4" t="n">
-        <v>3.119</v>
-      </c>
-      <c r="V45" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>3.68</v>
+      </c>
+      <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -10487,7 +10491,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>2.20%~2.30%</t>
+          <t>1.81%~1.91%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -10498,23 +10502,27 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>山东省-威海市</t>
+          <t>湖北省-荆门市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额4.20亿元,募集资金用于偿还到期债务融资工具本金[23文登蓝海MTN001]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券本金。[G23中荆3]</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司,中泰证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD45" s="3"/>
+          <t>国泰海通证券股份有限公司,长江证券股份有限公司,东方证券股份有限公司,国金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr">
+        <is>
+          <t>长江产业投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
@@ -10524,17 +10532,17 @@
       </c>
       <c r="AG45" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>威海市文登区蓝海投资开发有限公司2026年度第一期中期票据</t>
+          <t>中荆投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ45" s="3" t="inlineStr">
@@ -10549,7 +10557,7 @@
       </c>
       <c r="AL45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t/>
         </is>
       </c>
       <c r="AM45" s="3" t="inlineStr">
@@ -10564,32 +10572,32 @@
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
@@ -10599,7 +10607,7 @@
       </c>
       <c r="AV45" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW45" s="3" t="inlineStr">
@@ -10622,37 +10630,37 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26中荆06</t>
+          <t>26商物06</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>283811.SH</t>
+          <t>283775.SH</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.7</v>
+        <v>12.0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1.4</v>
+        <v>12.0</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.70 ~ 2.40</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="inlineStr">
@@ -10662,32 +10670,32 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>24中荆投资PPN002</t>
+          <t>26新疆商贸PPN001</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>2.95Y</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.9247</t>
+          <t>1.9813</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0100/1.9000</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>中荆投资控股集团有限公司</t>
+          <t>新疆商贸物流(集团)有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>C- 18.67</t>
+          <t>C+ 32.69</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10711,45 +10719,41 @@
         </is>
       </c>
       <c r="U46" s="4" t="n">
-        <v>3.68</v>
+        <v>1.425</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>1.81%~1.91%</t>
+          <t>1.91%~2.01%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>湖北省-荆门市</t>
+          <t>新疆维吾尔自治区-乌鲁木齐市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券本金。[G23中荆3]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,长江证券股份有限公司,东方证券股份有限公司,国金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD46" s="3" t="inlineStr">
-        <is>
-          <t>长江产业投资集团有限公司</t>
-        </is>
-      </c>
+          <t>招商证券股份有限公司,光大证券股份有限公司,中国银河证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -10767,7 +10771,7 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>中荆投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)</t>
+          <t>新疆商贸物流(集团)有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10777,14 +10781,10 @@
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK46" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-31</t>
+        </is>
+      </c>
+      <c r="AK46" s="3"/>
       <c r="AL46" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10807,27 +10807,27 @@
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="AV46" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW46" s="3" t="inlineStr">
@@ -10860,72 +10860,72 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26商物06</t>
+          <t>26传化MTN001(科创债)</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>08-28 19:00</t>
+          <t>08-28 18:00</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>283775.SH</t>
+          <t>102683451.IB</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.40</t>
+          <t>1.80 ~ 2.50</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>26新疆商贸PPN001</t>
+          <t>25生产兵团MTN002</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>2.95Y</t>
+          <t>2.30Y</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.9813</t>
+          <t>1.7048</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>2.0100/1.9000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>新疆商贸物流(集团)有限公司</t>
+          <t>传化智联股份有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.69</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
@@ -10949,17 +10949,19 @@
         </is>
       </c>
       <c r="U47" s="4" t="n">
-        <v>1.425</v>
-      </c>
-      <c r="V47" s="3"/>
+        <v>1.6</v>
+      </c>
+      <c r="V47" s="4" t="n">
+        <v>1.33</v>
+      </c>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>1.91%~2.01%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
@@ -10970,54 +10972,54 @@
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区-乌鲁木齐市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还有息债务</t>
+          <t>发行人本期科技创新债券发行规模为2亿元,其中1亿元用于偿还发行人有息负债,1亿元用于子公司浙江传化功能新材料有限公司纺织工业印染助剂、纺织品整理剂、化学试剂和助剂等功能化学品和新材料领域产品的研发和技术突破的投入</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司,光大证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>浙商银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
       <c r="AE47" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF47" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG47" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>新疆商贸物流(集团)有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>传化智联股份有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t>2028-08-31</t>
         </is>
       </c>
       <c r="AK47" s="3"/>
       <c r="AL47" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM47" s="3" t="inlineStr">
@@ -11042,22 +11044,22 @@
       </c>
       <c r="AQ47" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>物流</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
@@ -11090,7 +11092,7 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26传化MTN001(科创债)</t>
+          <t>26南京交建SCP005</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -11100,47 +11102,47 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>102683451.IB</t>
+          <t>012682175.IB</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>2.0</v>
+        <v>4.5</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2.0</v>
+        <v>4.5</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.50</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>25生产兵团MTN002</t>
+          <t>26南京交建SCP004</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2.30Y</t>
+          <t>255D</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.7048</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -11150,12 +11152,12 @@
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>传化智联股份有限公司</t>
+          <t>南京市交通建设投资控股(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C 26.67</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11179,19 +11181,19 @@
         </is>
       </c>
       <c r="U48" s="4" t="n">
-        <v>1.6</v>
+        <v>4.2556</v>
       </c>
       <c r="V48" s="4" t="n">
-        <v>1.33</v>
+        <v>1.0</v>
       </c>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
@@ -11202,28 +11204,28 @@
       <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>发行人本期科技创新债券发行规模为2亿元,其中1亿元用于偿还发行人有息负债,1亿元用于子公司浙江传化功能新材料有限公司纺织工业印染助剂、纺织品整理剂、化学试剂和助剂等功能化学品和新材料领域产品的研发和技术突破的投入</t>
+          <t>本期超短期融资券发行金额4.5亿元,本期发行的募集资金拟用于偿还发行人有息债务[26南京交建SCP002]</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>南京银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF48" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG48" s="3" t="inlineStr">
@@ -11233,7 +11235,7 @@
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>传化智联股份有限公司2026年度第一期科技创新债券</t>
+          <t>南京市交通建设投资控股(集团)有限责任公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
@@ -11243,7 +11245,7 @@
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2028-08-31</t>
+          <t>2027-05-28</t>
         </is>
       </c>
       <c r="AK48" s="3"/>
@@ -11264,32 +11266,32 @@
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP48" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ48" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT48" s="3" t="inlineStr">
         <is>
-          <t>物流</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU48" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-28.xlsx
+++ b/data/credit_bond_all_2026-08-28.xlsx
@@ -1177,7 +1177,9 @@
       <c r="E5" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.50</t>
@@ -9048,70 +9050,72 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26XCF14</t>
+          <t>26海峡环保SCP002</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>08-28 19:00</t>
+          <t>08-28 18:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>283838.SH</t>
+          <t>012682173.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>5+2+2</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F39" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26XCF12</t>
+          <t>26海峡环保SCP001</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>4.98Y+4.00Y</t>
+          <t>159D</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.9001</t>
+          <t>1.5369</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/1.8900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司</t>
+          <t>福建海峡环保集团股份有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.15</t>
+          <t>C- 16.50</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9121,7 +9125,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:00</t>
+          <t>08-28 10:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -9131,48 +9135,48 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>2.17</v>
+        <v>2.9333</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.56%~1.60%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途,具体用途根据发行人资金需求情况确定。</t>
+          <t>本期超短期融资券发行金额3.00亿元,拟用于偿还金融机构借款</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,申万宏源证券有限公司</t>
+          <t>兴业银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9182,79 +9186,75 @@
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行公司债券(第七期)(品种二)</t>
+          <t>福建海峡环保集团股份有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2035-09-01</t>
-        </is>
-      </c>
-      <c r="AK39" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-05-28</t>
+        </is>
+      </c>
+      <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM39" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO39" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ39" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR39" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS39" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT39" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU39" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
       <c r="AV39" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="AW39" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX39" s="3" t="inlineStr">
@@ -9280,57 +9280,57 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26海峡环保SCP002</t>
+          <t>26嘉产03</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>012682173.IB</t>
+          <t>283739.SH</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26海峡环保SCP001</t>
+          <t>26嘉产02</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>159D</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.5369</t>
+          <t>1.8940</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -9340,12 +9340,12 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>福建海峡环保集团股份有限公司</t>
+          <t>嘉兴市产业发展集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 16.50</t>
+          <t>C- 14.95</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>08-28 10:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -9369,44 +9369,44 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>2.9333</v>
+        <v>4.63</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.60%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额3.00亿元,拟用于偿还金融机构借款</t>
+          <t>本期债券募集资金扣除发行费用后其中6亿元用于偿还公司债券到期本金，剩余募集资金用于偿还其他有息债务[23嘉产02]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>东吴证券股份有限公司,平安证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -9416,28 +9416,32 @@
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>福建海峡环保集团股份有限公司2026年度第二期超短期融资券</t>
+          <t>嘉兴市产业发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2027-05-28</t>
-        </is>
-      </c>
-      <c r="AK40" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK40" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AM40" s="3" t="inlineStr">
@@ -9452,32 +9456,32 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9510,17 +9514,17 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26嘉产03</t>
+          <t>26文登蓝海MTN001</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>08-28 19:00</t>
+          <t>08-28 18:00</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>283739.SH</t>
+          <t>102683453.IB</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -9529,38 +9533,38 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>9.0</v>
+        <v>4.2</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>9.0</v>
+        <v>4.2</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>2.30 ~ 3.30</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1.88</v>
+        <v>2.44</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26嘉产02</t>
+          <t>22蓝海债</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>2.59Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.8940</t>
+          <t>2.1091</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -9570,12 +9574,12 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>嘉兴市产业发展集团有限公司</t>
+          <t>威海市文登区蓝海投资开发有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C- 14.95</t>
+          <t>B- 35.69</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9585,7 +9589,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9599,44 +9603,46 @@
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="V41" s="3"/>
+        <v>3.119</v>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>2.20%~2.30%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>山东省-威海市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后其中6亿元用于偿还公司债券到期本金，剩余募集资金用于偿还其他有息债务[23嘉产02]</t>
+          <t>本期中期票据发行金额4.20亿元,募集资金用于偿还到期债务融资工具本金[23文登蓝海MTN001]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,平安证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>国投证券股份有限公司,中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
@@ -9646,17 +9652,17 @@
       </c>
       <c r="AG41" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>嘉兴市产业发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>威海市文登区蓝海投资开发有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ41" s="3" t="inlineStr">
@@ -9671,7 +9677,7 @@
       </c>
       <c r="AL41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM41" s="3" t="inlineStr">
@@ -9686,32 +9692,32 @@
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9744,7 +9750,7 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26文登蓝海MTN001</t>
+          <t>26中荆06</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9754,7 +9760,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>102683453.IB</t>
+          <t>283811.SH</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -9763,38 +9769,38 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2.30 ~ 3.30</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>2.44</v>
+        <v>1.99</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>22蓝海债</t>
+          <t>24中荆投资PPN002</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2.59Y</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>2.1091</t>
+          <t>1.9247</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -9804,12 +9810,12 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>威海市文登区蓝海投资开发有限公司</t>
+          <t>中荆投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>B- 35.69</t>
+          <t>C- 18.67</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9819,7 +9825,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9833,11 +9839,9 @@
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>3.119</v>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>3.68</v>
+      </c>
+      <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -9845,7 +9849,7 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>2.20%~2.30%</t>
+          <t>1.81%~1.91%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -9856,23 +9860,27 @@
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>山东省-威海市</t>
+          <t>湖北省-荆门市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额4.20亿元,募集资金用于偿还到期债务融资工具本金[23文登蓝海MTN001]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券本金。[G23中荆3]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司,中泰证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD42" s="3"/>
+          <t>国泰海通证券股份有限公司,长江证券股份有限公司,东方证券股份有限公司,国金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr">
+        <is>
+          <t>长江产业投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
@@ -9882,17 +9890,17 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>威海市文登区蓝海投资开发有限公司2026年度第一期中期票据</t>
+          <t>中荆投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
@@ -9907,7 +9915,7 @@
       </c>
       <c r="AL42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t/>
         </is>
       </c>
       <c r="AM42" s="3" t="inlineStr">
@@ -9922,32 +9930,32 @@
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
@@ -9957,7 +9965,7 @@
       </c>
       <c r="AV42" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW42" s="3" t="inlineStr">
@@ -9980,37 +9988,37 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26中荆06</t>
+          <t>26商物06</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>283811.SH</t>
+          <t>283775.SH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.7</v>
+        <v>12.0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1.4</v>
+        <v>12.0</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.70 ~ 2.40</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="inlineStr">
@@ -10020,32 +10028,32 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>24中荆投资PPN002</t>
+          <t>26新疆商贸PPN001</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>2.95Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.9247</t>
+          <t>1.9813</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0100/1.9000</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>中荆投资控股集团有限公司</t>
+          <t>新疆商贸物流(集团)有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 18.67</t>
+          <t>C+ 34.80</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10069,45 +10077,41 @@
         </is>
       </c>
       <c r="U43" s="4" t="n">
-        <v>3.68</v>
+        <v>1.425</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>1.81%~1.91%</t>
+          <t>1.91%~2.01%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>湖北省-荆门市</t>
+          <t>新疆维吾尔自治区-乌鲁木齐市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券本金。[G23中荆3]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,长江证券股份有限公司,东方证券股份有限公司,国金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD43" s="3" t="inlineStr">
-        <is>
-          <t>长江产业投资集团有限公司</t>
-        </is>
-      </c>
+          <t>招商证券股份有限公司,光大证券股份有限公司,中国银河证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -10125,7 +10129,7 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>中荆投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)</t>
+          <t>新疆商贸物流(集团)有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
@@ -10135,67 +10139,63 @@
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK43" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-31</t>
+        </is>
+      </c>
+      <c r="AK43" s="3"/>
       <c r="AL43" s="3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr">
+        <is>
+          <t>贸易零售</t>
+        </is>
+      </c>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>其他贸易</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>其他贸易</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>贸易</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM43" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AO43" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ43" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR43" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS43" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV43" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW43" s="3" t="inlineStr">
@@ -10218,72 +10218,72 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26商物06</t>
+          <t>26传化MTN001(科创债)</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>08-28 19:00</t>
+          <t>08-28 18:00</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>283775.SH</t>
+          <t>102683451.IB</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.40</t>
+          <t>1.80 ~ 2.50</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>26新疆商贸PPN001</t>
+          <t>25生产兵团MTN002</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2.95Y</t>
+          <t>2.30Y</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.9813</t>
+          <t>1.7048</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>2.0100/1.9000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>新疆商贸物流(集团)有限公司</t>
+          <t>传化智联股份有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.80</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -10307,17 +10307,19 @@
         </is>
       </c>
       <c r="U44" s="4" t="n">
-        <v>1.425</v>
-      </c>
-      <c r="V44" s="3"/>
+        <v>1.6</v>
+      </c>
+      <c r="V44" s="4" t="n">
+        <v>1.33</v>
+      </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.91%~2.01%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
@@ -10328,54 +10330,54 @@
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区-乌鲁木齐市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还有息债务</t>
+          <t>发行人本期科技创新债券发行规模为2亿元,其中1亿元用于偿还发行人有息负债,1亿元用于子公司浙江传化功能新材料有限公司纺织工业印染助剂、纺织品整理剂、化学试剂和助剂等功能化学品和新材料领域产品的研发和技术突破的投入</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司,光大证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>浙商银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF44" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG44" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>新疆商贸物流(集团)有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>传化智联股份有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t>2028-08-31</t>
         </is>
       </c>
       <c r="AK44" s="3"/>
       <c r="AL44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM44" s="3" t="inlineStr">
@@ -10400,22 +10402,22 @@
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>物流</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
@@ -10448,7 +10450,7 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26传化MTN001(科创债)</t>
+          <t>26南京交建SCP005</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10458,62 +10460,62 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>102683451.IB</t>
+          <t>012682175.IB</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>2.0</v>
+        <v>4.5</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2.0</v>
+        <v>4.5</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.50</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>25生产兵团MTN002</t>
+          <t>26南京交建SCP004</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>2.30Y</t>
+          <t>255D</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.7048</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4090</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>传化智联股份有限公司</t>
+          <t>南京市交通建设投资控股(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C 29.51</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10537,19 +10539,19 @@
         </is>
       </c>
       <c r="U45" s="4" t="n">
-        <v>1.6</v>
+        <v>4.2556</v>
       </c>
       <c r="V45" s="4" t="n">
-        <v>1.33</v>
+        <v>1.0</v>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -10560,28 +10562,28 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>发行人本期科技创新债券发行规模为2亿元,其中1亿元用于偿还发行人有息负债,1亿元用于子公司浙江传化功能新材料有限公司纺织工业印染助剂、纺织品整理剂、化学试剂和助剂等功能化学品和新材料领域产品的研发和技术突破的投入</t>
+          <t>本期超短期融资券发行金额4.5亿元,本期发行的募集资金拟用于偿还发行人有息债务[26南京交建SCP002]</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>南京银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG45" s="3" t="inlineStr">
@@ -10591,7 +10593,7 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>传化智联股份有限公司2026年度第一期科技创新债券</t>
+          <t>南京市交通建设投资控股(集团)有限责任公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10601,7 +10603,7 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2028-08-31</t>
+          <t>2027-05-28</t>
         </is>
       </c>
       <c r="AK45" s="3"/>
@@ -10622,32 +10624,32 @@
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>物流</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
@@ -10680,7 +10682,7 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26南京交建SCP005</t>
+          <t>26中兵物资SCP001</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10690,7 +10692,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>012682175.IB</t>
+          <t>012682171.IB</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -10699,53 +10701,53 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>4.5</v>
+        <v>4.0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>4.5</v>
+        <v>4.0</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.37 ~ 1.57</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>26南京交建SCP004</t>
+          <t>26中拓SCP009</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>255D</t>
+          <t>259D</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.7014</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>--/1.4090</t>
+          <t>1.7500/--</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司</t>
+          <t>中国兵工物资集团有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>C 29.51</t>
+          <t>C- 25.00</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10769,21 +10771,15 @@
         </is>
       </c>
       <c r="U46" s="4" t="n">
-        <v>4.2556</v>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>1.575</v>
+      </c>
+      <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t>1.51%~1.55%</t>
-        </is>
-      </c>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X46" s="3"/>
       <c r="Y46" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -10792,17 +10788,17 @@
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额4.5亿元,本期发行的募集资金拟用于偿还发行人有息债务[26南京交建SCP002]</t>
+          <t>本期债务融资工具发行金额4亿元,募集资金拟用于偿还到期债务及补充流动资金</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,江苏银行股份有限公司</t>
+          <t>平安银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD46" s="3"/>
@@ -10813,7 +10809,7 @@
       </c>
       <c r="AF46" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG46" s="3" t="inlineStr">
@@ -10823,7 +10819,7 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司2026年度第五期超短期融资券</t>
+          <t>中国兵工物资集团有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10854,32 +10850,32 @@
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
@@ -10912,72 +10908,72 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26中兵物资SCP001</t>
+          <t>26靖滨01</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>012682171.IB</t>
+          <t>283740.SH</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>4.0</v>
+        <v>6.6</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>4.0</v>
+        <v>6.6</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.37 ~ 1.57</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>1.43</v>
+        <v>2.19</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>26中拓SCP009</t>
+          <t>24靖滨03</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>259D</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.7014</t>
+          <t>1.7952</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>1.7500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>中国兵工物资集团有限公司</t>
+          <t>靖江市滨江新城投资开发有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C- 25.00</t>
+          <t>C- 14.03</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10987,7 +10983,7 @@
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
@@ -10997,115 +10993,119 @@
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U47" s="4" t="n">
-        <v>1.575</v>
+        <v>2.17</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X47" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>1.97%~2.07%</t>
+        </is>
+      </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额4亿元,募集资金拟用于偿还到期债务及补充流动资金</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还发行人即将到期的公司债券本金；本期债券募集资金中6.6亿元仅用于偿还发行人即将到期的公司债券本金；本期债券为5年期债券,募集资金拟全部用于偿还到期的公司债券本金[23靖滨02]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,招商银行股份有限公司</t>
+          <t>天风证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
       <c r="AE47" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF47" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG47" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>中国兵工物资集团有限公司2026年度第一期超短期融资券</t>
+          <t>靖江市滨江新城投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2027-05-28</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK47" s="3"/>
       <c r="AL47" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AM47" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP47" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ47" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
@@ -11138,7 +11138,7 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26靖滨01</t>
+          <t>26XCF14</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -11148,47 +11148,47 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>283740.SH</t>
+          <t>283838.SH</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+2+2</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>6.6</v>
+        <v>11.0</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>24靖滨03</t>
+          <t>26XCF12</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>4.98Y+4.00Y</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.7952</t>
+          <t>1.9001</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司</t>
+          <t>成都兴城投资集团有限公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>C- 14.03</t>
+          <t>C+ 30.15</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 16:00</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -11232,33 +11232,33 @@
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.97%~2.07%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还发行人即将到期的公司债券本金；本期债券募集资金中6.6亿元仅用于偿还发行人即将到期的公司债券本金；本期债券为5年期债券,募集资金拟全部用于偿还到期的公司债券本金[23靖滨02]</t>
+          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途,具体用途根据发行人资金需求情况确定。</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,中信证券股份有限公司</t>
+          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
@@ -11279,7 +11279,7 @@
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行公司债券(第七期)(品种二)</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
@@ -11289,60 +11289,64 @@
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
+          <t>2035-09-01</t>
+        </is>
+      </c>
+      <c r="AK48" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
           <t>2031-09-01</t>
         </is>
       </c>
-      <c r="AK48" s="3"/>
-      <c r="AL48" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM48" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO48" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ48" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR48" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS48" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV48" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -11350,7 +11354,7 @@
       </c>
       <c r="AW48" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX48" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-28.xlsx
+++ b/data/credit_bond_all_2026-08-28.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-02" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-03" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,9 @@
       <c r="H3" s="4" t="n">
         <v>1.39</v>
       </c>
-      <c r="I3" s="3"/>
+      <c r="I3" s="4" t="n">
+        <v>22.07</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.53</t>
@@ -985,7 +987,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 18.67</t>
+          <t>C- 19.46</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1188,7 +1190,9 @@
       <c r="H5" s="4" t="n">
         <v>1.94</v>
       </c>
-      <c r="I5" s="3"/>
+      <c r="I5" s="4" t="n">
+        <v>24.51</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1.98</t>
@@ -1221,7 +1225,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C- 16.86</t>
+          <t>C- 14.91</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1313,7 +1317,7 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM5" s="3" t="inlineStr">
@@ -1418,7 +1422,9 @@
       <c r="H6" s="4" t="n">
         <v>1.92</v>
       </c>
-      <c r="I6" s="3"/>
+      <c r="I6" s="4" t="n">
+        <v>66.0</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>1.94</t>
@@ -1648,7 +1654,9 @@
       <c r="H7" s="4" t="n">
         <v>1.57</v>
       </c>
-      <c r="I7" s="3"/>
+      <c r="I7" s="4" t="n">
+        <v>31.0</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>1.57</t>
@@ -1681,7 +1689,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>B+ 59.13</t>
+          <t>A- 66.73</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1913,7 +1921,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C- 18.99</t>
+          <t>C- 20.26</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -2112,7 +2120,9 @@
       <c r="H9" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="I9" s="3"/>
+      <c r="I9" s="4" t="n">
+        <v>23.07</v>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>1.48</t>
@@ -2145,7 +2155,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C 29.51</t>
+          <t>C 29.88</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2344,7 +2354,9 @@
       <c r="H10" s="4" t="n">
         <v>2.37</v>
       </c>
-      <c r="I10" s="3"/>
+      <c r="I10" s="4" t="n">
+        <v>111.0</v>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>2.34</t>
@@ -2377,7 +2389,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>B- 37.56</t>
+          <t>B- 36.90</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2576,7 +2588,9 @@
       <c r="H11" s="4" t="n">
         <v>1.8</v>
       </c>
-      <c r="I11" s="3"/>
+      <c r="I11" s="4" t="n">
+        <v>54.0</v>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
           <t>1.91</t>
@@ -2609,7 +2623,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>B- 38.61</t>
+          <t>B- 39.70</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2808,7 +2822,9 @@
       <c r="H12" s="4" t="n">
         <v>2.23</v>
       </c>
-      <c r="I12" s="3"/>
+      <c r="I12" s="4" t="n">
+        <v>81.81</v>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>1.95</t>
@@ -3044,7 +3060,9 @@
       <c r="H13" s="4" t="n">
         <v>2.29</v>
       </c>
-      <c r="I13" s="3"/>
+      <c r="I13" s="4" t="n">
+        <v>59.51</v>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t>2.12</t>
@@ -3280,7 +3298,9 @@
       <c r="H14" s="4" t="n">
         <v>2.05</v>
       </c>
-      <c r="I14" s="3"/>
+      <c r="I14" s="4" t="n">
+        <v>63.81</v>
+      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
           <t>2.02</t>
@@ -3313,7 +3333,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 17.89</t>
+          <t>C- 17.45</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3516,7 +3536,9 @@
       <c r="H15" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="I15" s="3"/>
+      <c r="I15" s="4" t="n">
+        <v>34.0</v>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
           <t>1.70</t>
@@ -3549,7 +3571,7 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 17.44</t>
+          <t>C- 20.17</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3748,7 +3770,9 @@
       <c r="H16" s="4" t="n">
         <v>1.55</v>
       </c>
-      <c r="I16" s="3"/>
+      <c r="I16" s="4" t="n">
+        <v>13.81</v>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t>1.64</t>
@@ -3781,7 +3805,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C 25.58</t>
+          <t>C- 24.21</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3984,7 +4008,9 @@
       <c r="H17" s="4" t="n">
         <v>1.72</v>
       </c>
-      <c r="I17" s="3"/>
+      <c r="I17" s="4" t="n">
+        <v>30.81</v>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>1.70</t>
@@ -4220,7 +4246,9 @@
       <c r="H18" s="4" t="n">
         <v>2.15</v>
       </c>
-      <c r="I18" s="3"/>
+      <c r="I18" s="4" t="n">
+        <v>73.81</v>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
           <t>2.21</t>
@@ -4253,7 +4281,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B- 41.85</t>
+          <t>B- 42.56</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4456,7 +4484,9 @@
       <c r="H19" s="4" t="n">
         <v>1.58</v>
       </c>
-      <c r="I19" s="3"/>
+      <c r="I19" s="4" t="n">
+        <v>32.0</v>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
           <t>1.63</t>
@@ -4489,7 +4519,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B+ 59.09</t>
+          <t>B+ 59.36</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4686,7 +4716,9 @@
       <c r="H20" s="4" t="n">
         <v>1.8</v>
       </c>
-      <c r="I20" s="3"/>
+      <c r="I20" s="4" t="n">
+        <v>54.0</v>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
           <t>1.78</t>
@@ -4916,7 +4948,9 @@
       <c r="H21" s="4" t="n">
         <v>1.8</v>
       </c>
-      <c r="I21" s="3"/>
+      <c r="I21" s="4" t="n">
+        <v>38.81</v>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
           <t>1.81</t>
@@ -4949,7 +4983,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.08</t>
+          <t>C+ 31.20</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -5152,7 +5186,9 @@
       <c r="H22" s="4" t="n">
         <v>1.79</v>
       </c>
-      <c r="I22" s="3"/>
+      <c r="I22" s="4" t="n">
+        <v>53.0</v>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
           <t>1.76</t>
@@ -5382,7 +5418,9 @@
       <c r="H23" s="4" t="n">
         <v>2.25</v>
       </c>
-      <c r="I23" s="3"/>
+      <c r="I23" s="4" t="n">
+        <v>83.81</v>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
           <t>2.11</t>
@@ -5618,7 +5656,9 @@
       <c r="H24" s="4" t="n">
         <v>1.59</v>
       </c>
-      <c r="I24" s="3"/>
+      <c r="I24" s="4" t="n">
+        <v>33.0</v>
+      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
           <t>1.60</t>
@@ -5651,7 +5691,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>A 72.30</t>
+          <t>A 71.97</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5854,7 +5894,9 @@
       <c r="H25" s="4" t="n">
         <v>1.87</v>
       </c>
-      <c r="I25" s="3"/>
+      <c r="I25" s="4" t="n">
+        <v>45.81</v>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
           <t>1.93</t>
@@ -6090,7 +6132,9 @@
       <c r="H26" s="4" t="n">
         <v>2.08</v>
       </c>
-      <c r="I26" s="3"/>
+      <c r="I26" s="4" t="n">
+        <v>66.81</v>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -6123,7 +6167,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 20.03</t>
+          <t>C- 19.70</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6320,7 +6364,9 @@
       <c r="H27" s="4" t="n">
         <v>1.65</v>
       </c>
-      <c r="I27" s="3"/>
+      <c r="I27" s="4" t="n">
+        <v>39.53</v>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
           <t>1.64</t>
@@ -6445,7 +6491,7 @@
       <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6550,7 +6596,9 @@
       <c r="H28" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="I28" s="3"/>
+      <c r="I28" s="4" t="n">
+        <v>108.81</v>
+      </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -6768,7 +6816,9 @@
       <c r="H29" s="4" t="n">
         <v>1.99</v>
       </c>
-      <c r="I29" s="3"/>
+      <c r="I29" s="4" t="n">
+        <v>57.81</v>
+      </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
           <t>1.92</t>
@@ -6801,7 +6851,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 18.99</t>
+          <t>C- 20.26</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6998,7 +7048,9 @@
       <c r="H30" s="4" t="n">
         <v>2.13</v>
       </c>
-      <c r="I30" s="3"/>
+      <c r="I30" s="4" t="n">
+        <v>71.81</v>
+      </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
           <t>1.92</t>
@@ -7031,7 +7083,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 15.75</t>
+          <t>C 27.56</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7123,7 +7175,7 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM30" s="3" t="inlineStr">
@@ -7228,7 +7280,9 @@
       <c r="H31" s="4" t="n">
         <v>1.84</v>
       </c>
-      <c r="I31" s="3"/>
+      <c r="I31" s="4" t="n">
+        <v>58.0</v>
+      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
           <t>1.77</t>
@@ -7462,7 +7516,9 @@
       <c r="H32" s="4" t="n">
         <v>1.75</v>
       </c>
-      <c r="I32" s="3"/>
+      <c r="I32" s="4" t="n">
+        <v>21.46</v>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
           <t>1.75</t>
@@ -7495,7 +7551,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.15</t>
+          <t>C+ 34.25</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7692,7 +7748,9 @@
       <c r="H33" s="4" t="n">
         <v>1.78</v>
       </c>
-      <c r="I33" s="3"/>
+      <c r="I33" s="4" t="n">
+        <v>36.81</v>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
           <t>1.74</t>
@@ -7725,7 +7783,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>B- 36.79</t>
+          <t>B- 38.57</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7922,7 +7980,9 @@
       <c r="H34" s="4" t="n">
         <v>2.38</v>
       </c>
-      <c r="I34" s="3"/>
+      <c r="I34" s="4" t="n">
+        <v>96.81</v>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
           <t>2.53</t>
@@ -7955,7 +8015,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 16.50</t>
+          <t>C+ 32.50</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8156,7 +8216,9 @@
       <c r="H35" s="4" t="n">
         <v>1.51</v>
       </c>
-      <c r="I35" s="3"/>
+      <c r="I35" s="4" t="n">
+        <v>28.68</v>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
           <t>1.51</t>
@@ -8189,7 +8251,7 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C- 20.67</t>
+          <t>C- 18.80</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8212,7 +8274,9 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U35" s="3"/>
+      <c r="U35" s="4" t="n">
+        <v>0.6</v>
+      </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
@@ -8390,7 +8454,9 @@
       <c r="H36" s="4" t="n">
         <v>1.58</v>
       </c>
-      <c r="I36" s="3"/>
+      <c r="I36" s="4" t="n">
+        <v>32.0</v>
+      </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
           <t>1.68</t>
@@ -8423,7 +8489,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>B- 39.11</t>
+          <t>B- 44.78</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8620,7 +8686,9 @@
       <c r="H37" s="4" t="n">
         <v>1.93</v>
       </c>
-      <c r="I37" s="3"/>
+      <c r="I37" s="4" t="n">
+        <v>51.81</v>
+      </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
           <t>2.05</t>
@@ -8653,7 +8721,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>D 4.57</t>
+          <t>C- 10.04</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8883,7 +8951,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C- 15.75</t>
+          <t>C 27.56</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -9082,7 +9150,9 @@
       <c r="H39" s="4" t="n">
         <v>1.45</v>
       </c>
-      <c r="I39" s="3"/>
+      <c r="I39" s="4" t="n">
+        <v>28.07</v>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -9115,7 +9185,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 16.50</t>
+          <t>C 29.00</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9312,7 +9382,9 @@
       <c r="H40" s="4" t="n">
         <v>1.88</v>
       </c>
-      <c r="I40" s="3"/>
+      <c r="I40" s="4" t="n">
+        <v>46.81</v>
+      </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
           <t>1.90</t>
@@ -9345,7 +9417,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 14.95</t>
+          <t>C- 12.71</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9546,7 +9618,9 @@
       <c r="H41" s="4" t="n">
         <v>2.44</v>
       </c>
-      <c r="I41" s="3"/>
+      <c r="I41" s="4" t="n">
+        <v>102.81</v>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
           <t>2.37</t>
@@ -9579,7 +9653,7 @@
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>B- 35.69</t>
+          <t>C+ 34.33</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9782,7 +9856,9 @@
       <c r="H42" s="4" t="n">
         <v>1.99</v>
       </c>
-      <c r="I42" s="3"/>
+      <c r="I42" s="4" t="n">
+        <v>57.81</v>
+      </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
           <t>1.99</t>
@@ -9815,7 +9891,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C- 18.67</t>
+          <t>C- 19.46</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9915,7 +9991,7 @@
       </c>
       <c r="AL42" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM42" s="3" t="inlineStr">
@@ -10020,7 +10096,9 @@
       <c r="H43" s="4" t="n">
         <v>2.02</v>
       </c>
-      <c r="I43" s="3"/>
+      <c r="I43" s="4" t="n">
+        <v>76.0</v>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
           <t>1.99</t>
@@ -10250,7 +10328,9 @@
       <c r="H44" s="4" t="n">
         <v>2.05</v>
       </c>
-      <c r="I44" s="3"/>
+      <c r="I44" s="4" t="n">
+        <v>79.53</v>
+      </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
           <t>1.80</t>
@@ -10482,7 +10562,9 @@
       <c r="H45" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="I45" s="3"/>
+      <c r="I45" s="4" t="n">
+        <v>23.07</v>
+      </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
           <t>1.48</t>
@@ -10515,7 +10597,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C 29.51</t>
+          <t>C 29.88</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10714,7 +10796,9 @@
       <c r="H46" s="4" t="n">
         <v>1.43</v>
       </c>
-      <c r="I46" s="3"/>
+      <c r="I46" s="4" t="n">
+        <v>26.07</v>
+      </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
           <t>1.57</t>
@@ -10747,7 +10831,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>C- 25.00</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10940,7 +11024,9 @@
       <c r="H47" s="4" t="n">
         <v>2.19</v>
       </c>
-      <c r="I47" s="3"/>
+      <c r="I47" s="4" t="n">
+        <v>77.81</v>
+      </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
           <t>1.99</t>
@@ -10973,7 +11059,7 @@
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C- 14.03</t>
+          <t>C- 11.20</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -11065,7 +11151,7 @@
       <c r="AK47" s="3"/>
       <c r="AL47" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM47" s="3" t="inlineStr">
@@ -11170,7 +11256,9 @@
       <c r="H48" s="4" t="n">
         <v>1.9</v>
       </c>
-      <c r="I48" s="3"/>
+      <c r="I48" s="4" t="n">
+        <v>25.7</v>
+      </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
           <t>1.90</t>
@@ -11193,7 +11281,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8900</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
@@ -11203,7 +11291,7 @@
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.15</t>
+          <t>C+ 34.25</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-28.xlsx
+++ b/data/credit_bond_all_2026-08-28.xlsx
@@ -1622,17 +1622,17 @@
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26苏州银行01</t>
+          <t>26淮联06(取消发行)</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2620007.IB</t>
+          <t>DY283830.SH</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1641,40 +1641,34 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>30.0</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>31.0</v>
-      </c>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>25苏州银行科创债01(柜台)</t>
+          <t>24淮安国联PPN003</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>4.04Y</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.6308</t>
+          <t>1.7748</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1684,12 +1678,12 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>苏州银行股份有限公司</t>
+          <t>淮安市国有联合投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>A- 66.73</t>
+          <t>C- 20.26</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1699,7 +1693,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
@@ -1716,12 +1710,12 @@
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1729,50 +1723,46 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+          <t>本期债券募集资金扣除发行费用后,拟将全部用于偿还公司债券本金[23淮发V2]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国银行股份有限公司,中国邮政储蓄银行股份有限公司,中国工商银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国光大银行股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,国信证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,东吴证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG7" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>苏州银行股份有限公司2026年第一期金融债券</t>
+          <t>淮安市国有联合投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="inlineStr">
@@ -1787,12 +1777,12 @@
       </c>
       <c r="AL7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t/>
         </is>
       </c>
       <c r="AM7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN7" s="3" t="inlineStr">
@@ -1802,32 +1792,32 @@
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1860,68 +1850,74 @@
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26淮联06(取消发行)</t>
+          <t>26南京交建SCP006</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>08-28 19:00</t>
+          <t>08-28 18:00</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>DY283830.SH</t>
+          <t>012682174.IB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F8" s="3"/>
+        <v>3.5</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>3.5</v>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+          <t>1.30 ~ 1.70</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>23.07</v>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>24淮安国联PPN003</t>
+          <t>26南京交建SCP004</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>255D</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.7748</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4090</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司</t>
+          <t>南京市交通建设投资控股(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C- 20.26</t>
+          <t>C 29.88</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1931,7 +1927,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
@@ -1941,19 +1937,23 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>1.01</v>
+      </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -1964,23 +1964,23 @@
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将全部用于偿还公司债券本金[23淮发V2]</t>
+          <t>本期超短期融资券发行金额3.5亿元,本期发行的募集资金扣除发行费用后用于偿还发行人本级及子公司有息债务</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,东吴证券股份有限公司,招商证券股份有限公司</t>
+          <t>中信银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
@@ -1990,32 +1990,28 @@
       </c>
       <c r="AG8" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种一)(取消发行)</t>
+          <t>南京市交通建设投资控股(集团)有限责任公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK8" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-05-28</t>
+        </is>
+      </c>
+      <c r="AK8" s="3"/>
       <c r="AL8" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM8" s="3" t="inlineStr">
@@ -2025,17 +2021,17 @@
       </c>
       <c r="AN8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
@@ -2045,17 +2041,17 @@
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
@@ -2088,7 +2084,7 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26南京交建SCP006</t>
+          <t>26西安高新MTN009</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2098,64 +2094,64 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>012682174.IB</t>
+          <t>102683452.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.5</v>
+        <v>10.0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.5</v>
+        <v>10.0</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.75 ~ 2.75</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.4</v>
+        <v>2.37</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>23.07</v>
+        <v>111.0</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26南京交建SCP004</t>
+          <t>24西安高新MTN015</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>255D</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>2.3383</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/1.4090</t>
+          <t>2.3500/--</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司</t>
+          <t>西安高新控股有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C 29.88</t>
+          <t>B- 36.90</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2179,19 +2175,19 @@
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>2.26%~2.36%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -2202,23 +2198,23 @@
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额3.5亿元,本期发行的募集资金扣除发行费用后用于偿还发行人本级及子公司有息债务</t>
+          <t>发行人本期中期票据基础发行金额人民币0亿元，发行金额上限人民币10亿元，募集资金全部拟用于偿还发行人到期债务[25西安高新CP010,25西安高新CP011]</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,南京银行股份有限公司</t>
+          <t>中信银行股份有限公司,西安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
@@ -2233,7 +2229,7 @@
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司2026年度第六期超短期融资券</t>
+          <t>西安高新控股有限公司2026年度第九期中期票据</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2243,7 +2239,7 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2027-05-28</t>
+          <t>2029-08-31</t>
         </is>
       </c>
       <c r="AK9" s="3"/>
@@ -2269,7 +2265,7 @@
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
@@ -2279,17 +2275,17 @@
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
@@ -2322,7 +2318,7 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26西安高新MTN009</t>
+          <t>26海发国资MTN003</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2332,7 +2328,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>102683452.IB</t>
+          <t>102683445.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -2348,48 +2344,48 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.75 ~ 2.75</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.37</v>
+        <v>1.8</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>111.0</v>
+        <v>54.0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>24西安高新MTN015</t>
+          <t>24海发国资MTN004</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>2.3383</t>
+          <t>1.9062</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>2.3500/--</t>
+          <t>1.9200/1.8800</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>西安高新控股有限公司</t>
+          <t>青岛海发国有资本投资运营集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>B- 36.90</t>
+          <t>B- 39.70</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2413,19 +2409,19 @@
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.57</v>
+        <v>3.3</v>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>2.26%~2.36%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -2436,17 +2432,17 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行金额人民币0亿元，发行金额上限人民币10亿元，募集资金全部拟用于偿还发行人到期债务[25西安高新CP010,25西安高新CP011]</t>
+          <t>本期发行规模为人民币10亿元，本期债务融资工具募集资金将用于偿还发行人合并范围内有息债务本金。[25海发国资SCP006,26海发国资SCP001,23海发国资MTN003]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,西安银行股份有限公司</t>
+          <t>中信银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
@@ -2467,7 +2463,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>西安高新控股有限公司2026年度第九期中期票据</t>
+          <t>青岛海发国有资本投资运营集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2503,7 +2499,7 @@
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
@@ -2513,12 +2509,12 @@
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
@@ -2556,7 +2552,7 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26海发国资MTN003</t>
+          <t>26宜都国通MTN001</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2566,64 +2562,64 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>102683445.IB</t>
+          <t>102683456.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>54.0</v>
+        <v>81.81</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>24海发国资MTN004</t>
+          <t>26宜都国通CP001</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>203D</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.9062</t>
+          <t>1.6759</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>1.9200/1.8800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>青岛海发国有资本投资运营集团有限公司</t>
+          <t>宜都市国通投资开发有限责任公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>B- 39.70</t>
+          <t>D+ 5.27</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2647,40 +2643,40 @@
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>3.3</v>
+        <v>1.15</v>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>2.11%~2.21%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>湖北省-宜昌市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期发行规模为人民币10亿元，本期债务融资工具募集资金将用于偿还发行人合并范围内有息债务本金。[25海发国资SCP006,26海发国资SCP001,23海发国资MTN003]</t>
+          <t>本期基础发行规模0.00亿元，发行金额上限4.00亿元，募集资金拟用于偿还接续“25宜都国通CP002”的专项过桥贷款；本期募集资金拟用于偿还“25宜都国通CP002”本金4.00亿元</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,渤海银行股份有限公司</t>
+          <t>广发证券股份有限公司,汉口银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
@@ -2701,7 +2697,7 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>青岛海发国有资本投资运营集团有限公司2026年度第三期中期票据</t>
+          <t>宜都市国通投资开发有限责任公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2711,10 +2707,14 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
-        </is>
-      </c>
-      <c r="AK11" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK11" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL11" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
@@ -2790,7 +2790,7 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26宜都国通MTN001</t>
+          <t>26金川MTN002</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2800,64 +2800,64 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>102683456.IB</t>
+          <t>102683450.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.90 ~ 2.29</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>81.81</v>
+        <v>59.51</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26宜都国通CP001</t>
+          <t>26金川MTN001</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>203D</t>
+          <t>4.83Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.6759</t>
+          <t>1.8772</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9000/1.7800</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>宜都市国通投资开发有限责任公司</t>
+          <t>金川集团股份有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.27</t>
+          <t>C+ 30.90</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2881,40 +2881,40 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>3.1</v>
+        <v>1.08</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>2.11%~2.21%</t>
+          <t>2.10%~2.20%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>湖北省-宜昌市</t>
+          <t>甘肃省-金昌市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期基础发行规模0.00亿元，发行金额上限4.00亿元，募集资金拟用于偿还接续“25宜都国通CP002”的专项过桥贷款；本期募集资金拟用于偿还“25宜都国通CP002”本金4.00亿元</t>
+          <t>发行人本期拟发行5亿元中期票据,拟全部用于偿还发行人有息负债。</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,汉口银行股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>宜都市国通投资开发有限责任公司2026年度第一期中期票据</t>
+          <t>金川集团股份有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
+          <t>2036-08-31</t>
         </is>
       </c>
       <c r="AK12" s="3" t="inlineStr">
@@ -2970,32 +2970,32 @@
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他有色金属</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -3028,7 +3028,7 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26金川MTN002</t>
+          <t>26盛裕投资MTN001</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>102683450.IB</t>
+          <t>102690019.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
@@ -3054,48 +3054,48 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.29</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>59.51</v>
+        <v>63.81</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26金川MTN001</t>
+          <t>25盛裕投资MTN003</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>4.83Y</t>
+          <t>1.58Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.8772</t>
+          <t>1.7538</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>1.9000/1.7800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>金川集团股份有限公司</t>
+          <t>扬州盛裕投资发展有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.90</t>
+          <t>C- 17.45</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 14:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3119,40 +3119,40 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.08</v>
+        <v>2.86</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>1.1</v>
+        <v>1.0</v>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>2.10%~2.20%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>甘肃省-金昌市</t>
+          <t>江苏省-扬州市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>发行人本期拟发行5亿元中期票据,拟全部用于偿还发行人有息负债。</t>
+          <t>发行人承诺本期中期票据5.00亿元用于偿还含回售选择权的中期票据“23盛裕投资MTN001”回售本金部分,金额5.00亿元[23盛裕投资MTN001]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>中国银河证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>金川集团股份有限公司2026年度第二期中期票据</t>
+          <t>扬州盛裕投资发展有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2036-08-31</t>
+          <t>2031-08-31</t>
         </is>
       </c>
       <c r="AK13" s="3" t="inlineStr">
@@ -3208,32 +3208,32 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5*无效</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>其他有色金属</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>金属非金属新材料</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3266,7 +3266,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26盛裕投资MTN001</t>
+          <t>26川高速MTN005</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3276,64 +3276,64 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>102690019.IB</t>
+          <t>102683446.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 1.80</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>63.81</v>
+        <v>34.0</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>25盛裕投资MTN003</t>
+          <t>24川高速MTN006</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>1.58Y</t>
+          <t>2.64Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7538</t>
+          <t>1.6868</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>扬州盛裕投资发展有限公司</t>
+          <t>四川高速公路建设开发集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 17.45</t>
+          <t>C- 20.17</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>08-28 14:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3357,40 +3357,40 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.86</v>
+        <v>4.8429</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.0</v>
+        <v>1.11</v>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>江苏省-扬州市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>发行人承诺本期中期票据5.00亿元用于偿还含回售选择权的中期票据“23盛裕投资MTN001”回售本金部分,金额5.00亿元[23盛裕投资MTN001]</t>
+          <t>发行人本期债务融资工具拟募集资金7亿元,拟全部用于偿付到期债务融资工具:【23川高速MTN006(革命老区)】。</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>中国民生银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>扬州盛裕投资发展有限公司2026年度第一期中期票据</t>
+          <t>四川高速公路建设开发集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3421,14 +3421,10 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK14" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-31</t>
+        </is>
+      </c>
+      <c r="AK14" s="3"/>
       <c r="AL14" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -3446,12 +3442,12 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>6.5*无效</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
@@ -3461,17 +3457,17 @@
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3504,7 +3500,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26川高速MTN005</t>
+          <t>26先进制造MTN002(科创债)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3514,64 +3510,64 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>102683446.IB</t>
+          <t>102683449.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.80</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>34.0</v>
+        <v>13.81</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>24川高速MTN006</t>
+          <t>26先进制造MTN001(科创债)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>2.64Y</t>
+          <t>2.92Y+2.00Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.6868</t>
+          <t>1.6979</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>1.8000/1.7000</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司</t>
+          <t>成都先进制造产业投资有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 20.17</t>
+          <t>C- 24.21</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3581,7 +3577,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 11:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3595,19 +3591,19 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.8429</v>
+        <v>3.76</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -3615,20 +3611,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z15" s="3"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具拟募集资金7亿元,拟全部用于偿付到期债务融资工具:【23川高速MTN006(革命老区)】。</t>
+          <t>本期科技创新债券拟发行10.00亿元,发行人拟将本期科技创新债券募集资金扣除发行费用后,全部用于基金出资支持科技创新领域发展相关用途。</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,中信银行股份有限公司</t>
+          <t>兴业银行股份有限公司,成都农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司2026年度第五期中期票据</t>
+          <t>成都先进制造产业投资有限公司2026年度第二期科技创新债券</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3659,60 +3659,60 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK15" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP15" s="3"/>
+      <c r="AQ15" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
           <t>2029-08-31</t>
         </is>
       </c>
-      <c r="AK15" s="3"/>
-      <c r="AL15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AM15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AO15" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ15" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR15" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>高速公路</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX15" s="3" t="inlineStr">
@@ -3738,7 +3738,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26先进制造MTN002(科创债)</t>
+          <t>26顺控发展MTN001(并购)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>102683449.IB</t>
+          <t>102683444.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3757,55 +3757,55 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>13.81</v>
+        <v>30.81</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26先进制造MTN001(科创债)</t>
+          <t>25顺控发展MTN001</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2.92Y+2.00Y</t>
+          <t>1.65Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.6979</t>
+          <t>1.6401</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1.8000/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>成都先进制造产业投资有限公司</t>
+          <t>广东顺控发展股份有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C- 24.21</t>
+          <t>B- 43.64</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>08-28 11:00</t>
+          <t>08-28 14:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3829,19 +3829,15 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>3.76</v>
+        <v>4.5</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W16" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+        <v>3.4</v>
+      </c>
+      <c r="W16" s="3"/>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -3856,17 +3852,17 @@
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>广东省-佛山市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券拟发行10.00亿元,发行人拟将本期科技创新债券募集资金扣除发行费用后,全部用于基金出资支持科技创新领域发展相关用途。</t>
+          <t>发行人本期中期票据拟发行6.00亿元,其中28,300.00万元用于偿还发行人并购贷款;12,682.61万元置换发行人过去一年内并购活动的自有资金出资;19,017.39万元用于补充流动资金。</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,成都农村商业银行股份有限公司</t>
+          <t>中国银河证券股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
@@ -3887,7 +3883,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>成都先进制造产业投资有限公司2026年度第二期科技创新债券</t>
+          <t>广东顺控发展股份有限公司2026年度第一期中期票据(并购)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3922,28 +3918,32 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP16" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3976,7 +3976,7 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26顺控发展MTN001(并购)</t>
+          <t>26华发科技MTN002(科创债)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>102683444.IB</t>
+          <t>102683455.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3995,40 +3995,40 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>30.81</v>
+        <v>73.81</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>25顺控发展MTN001</t>
+          <t>26华发科技MTN001(科创债)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>1.65Y</t>
+          <t>2.79Y+2.00Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.6401</t>
+          <t>2.2887</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>广东顺控发展股份有限公司</t>
+          <t>珠海华发科技产业集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B- 43.64</t>
+          <t>B- 42.56</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>08-28 14:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -4067,15 +4067,19 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>4.5</v>
+        <v>3.14</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="W17" s="3"/>
+        <v>1.34</v>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>2.23%~2.33%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -4083,24 +4087,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z17" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>广东省-佛山市</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据拟发行6.00亿元,其中28,300.00万元用于偿还发行人并购贷款;12,682.61万元置换发行人过去一年内并购活动的自有资金出资;19,017.39万元用于补充流动资金。</t>
+          <t>本期中期票据发行金额上限为10亿元,募集资金扣除发行费用后,拟全部用于置换本期债券发行日前12个月内发行人自有资金对现有基金的前期出资</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,招商银行股份有限公司</t>
+          <t>中国建设银行股份有限公司,东莞农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>广东顺控发展股份有限公司2026年度第一期中期票据(并购)</t>
+          <t>珠海华发科技产业集团有限公司2026年度第二期科技创新债券</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4161,27 +4161,27 @@
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4214,7 +4214,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26华发科技MTN002(科创债)</t>
+          <t>26光明02</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102683455.IB</t>
+          <t>245992.SH</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -4240,48 +4240,48 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>73.81</v>
+        <v>32.0</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26华发科技MTN001(科创债)</t>
+          <t>24光明02</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2.79Y+2.00Y</t>
+          <t>2.86Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>2.2887</t>
+          <t>1.6100</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6500/1.6300</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>珠海华发科技产业集团有限公司</t>
+          <t>光明食品(集团)有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B- 42.56</t>
+          <t>B+ 59.36</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -4305,19 +4305,17 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="V18" s="4" t="n">
-        <v>1.34</v>
-      </c>
+        <v>4.13</v>
+      </c>
+      <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>2.23%~2.33%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4328,23 +4326,23 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额上限为10亿元,募集资金扣除发行费用后,拟全部用于置换本期债券发行日前12个月内发行人自有资金对现有基金的前期出资</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将10.00亿元用于偿还到期债务[23光明02]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,东莞农村商业银行股份有限公司</t>
+          <t>中银国际证券股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,平安证券股份有限公司,中泰证券股份有限公司,中国国际金融股份有限公司,申万宏源证券有限公司,光大证券股份有限公司,长城证券股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4354,12 +4352,12 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>珠海华发科技产业集团有限公司2026年度第二期科技创新债券</t>
+          <t>光明食品(集团)有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4369,17 +4367,13 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK18" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-31</t>
+        </is>
+      </c>
+      <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AM18" s="3" t="inlineStr">
@@ -4399,32 +4393,32 @@
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>轻工制造</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>食品加工</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t/>
         </is>
       </c>
       <c r="AV18" s="3" t="inlineStr">
@@ -4434,7 +4428,7 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4452,74 +4446,74 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26光明02</t>
+          <t>26皖担Y1</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>245992.SH</t>
+          <t>245991.SH</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>32.0</v>
+        <v>54.0</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>24光明02</t>
+          <t>25安徽担保PPN001</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>2.86Y</t>
+          <t>2.14Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.6100</t>
+          <t>1.7477</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>1.6500/1.6300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>光明食品(集团)有限公司</t>
+          <t>安徽省信用融资担保集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B+ 59.36</t>
+          <t>C 27.50</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4529,7 +4523,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 16:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4543,17 +4537,17 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>4.13</v>
+        <v>3.92</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -4564,17 +4558,17 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将10.00亿元用于偿还到期债务[23光明02]</t>
+          <t>本期公司债券募集资金扣除发行费用后,发行人拟将15亿元用于置换2026年8月使用自有资金偿付到期的15亿元23皖担Y1[23皖担Y1]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>中银国际证券股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,平安证券股份有限公司,中泰证券股份有限公司,中国国际金融股份有限公司,申万宏源证券有限公司,光大证券股份有限公司,长城证券股份有限公司</t>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,国元证券股份有限公司,华安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
@@ -4595,7 +4589,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>光明食品(集团)有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>安徽省信用融资担保集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4626,32 +4620,32 @@
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>轻工制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>担保</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>再担保</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>食品加工</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4666,7 +4660,7 @@
       </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX19" s="3" t="inlineStr">
@@ -4684,59 +4678,59 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26皖担Y1</t>
+          <t>26福州地铁GN002(碳中和债)</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>08-28 19:00</t>
+          <t>08-28 18:00</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>245991.SH</t>
+          <t>132680091.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>54.0</v>
+        <v>38.81</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>25安徽担保PPN001</t>
+          <t>GC榕铁02</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.14Y</t>
+          <t>4.80Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.7477</t>
+          <t>1.7951</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4746,12 +4740,12 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>安徽省信用融资担保集团有限公司</t>
+          <t>福州地铁集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C 27.50</t>
+          <t>C+ 31.20</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4761,7 +4755,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -4775,12 +4769,14 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="V20" s="3"/>
+        <v>3.1429</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>1.57</v>
+      </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
@@ -4796,23 +4792,23 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,发行人拟将15亿元用于置换2026年8月使用自有资金偿付到期的15亿元23皖担Y1[23皖担Y1]</t>
+          <t>募集资金拟全部用于城市轨道交通建设类绿色低碳产业项目，包括福州地铁1号线、2号线、4号线、5号线、6号线、福州至长乐机场城际铁路(F1线)</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国国际金融股份有限公司,国元证券股份有限公司,华安证券股份有限公司</t>
+          <t>中国银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4822,12 +4818,12 @@
       </c>
       <c r="AG20" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>安徽省信用融资担保集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
+          <t>福州地铁集团有限公司2026年度第二期绿色中期票据(碳中和债)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4837,13 +4833,17 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
-        </is>
-      </c>
-      <c r="AK20" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK20" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM20" s="3" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
@@ -4868,22 +4868,22 @@
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>担保</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>再担保</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AW20" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX20" s="3" t="inlineStr">
@@ -4916,7 +4916,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26福州地铁GN002(碳中和债)</t>
+          <t>26汤山建设PPN001</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4926,64 +4926,64 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>132680091.IB</t>
+          <t>032680504.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>7.0</v>
+        <v>7.4</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>7.0</v>
+        <v>7.4</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>38.81</v>
+        <v>53.0</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>GC榕铁02</t>
+          <t>24汤山04</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>4.80Y</t>
+          <t>3.22Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.7951</t>
+          <t>1.7594</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7100</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>福州地铁集团有限公司</t>
+          <t>南京汤山建设投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.20</t>
+          <t>C- 19.65</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -5007,46 +5007,42 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>3.1429</v>
+        <v>2.7162</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.57</v>
+        <v>1.0</v>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t>1.74%~1.84%</t>
-        </is>
-      </c>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X21" s="3"/>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>募集资金拟全部用于城市轨道交通建设类绿色低碳产业项目，包括福州地铁1号线、2号线、4号线、5号线、6号线、福州至长乐机场城际铁路(F1线)</t>
+          <t>发行人本次定向债务融资工具注册金额7.40亿元，本期发行金额7.40亿元，募集资金拟全部用于偿还发行人到期债务融资工具本金[25汤山建设SCP001]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,招商银行股份有限公司</t>
+          <t>南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -5061,24 +5057,20 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>福州地铁集团有限公司2026年度第二期绿色中期票据(碳中和债)</t>
+          <t>南京汤山建设投资发展集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK21" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-31</t>
+        </is>
+      </c>
+      <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -5096,12 +5088,12 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
@@ -5111,17 +5103,17 @@
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -5149,12 +5141,14 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ21" s="3"/>
+      <c r="AZ21" s="4" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26汤山建设PPN001</t>
+          <t>26遂宁兴业PPN001</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5164,64 +5158,64 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>032680504.IB</t>
+          <t>032690010.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>7.4</v>
+        <v>4.0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>7.4</v>
+        <v>4.0</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>53.0</v>
+        <v>83.81</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>24汤山04</t>
+          <t>26伊犁财通PPN001</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>3.22Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.7594</t>
+          <t>2.0881</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/1.7100</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>南京汤山建设投资发展集团有限公司</t>
+          <t>遂宁兴业投资集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C- 19.65</t>
+          <t>C- 15.00</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5231,7 +5225,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 09:30</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5245,17 +5239,21 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.7162</v>
+        <v>3.2</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.0</v>
+        <v>1.4</v>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X22" s="3"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>2.26%~2.36%</t>
+        </is>
+      </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -5264,17 +5262,17 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>四川省-遂宁市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>发行人本次定向债务融资工具注册金额7.40亿元，本期发行金额7.40亿元，募集资金拟全部用于偿还发行人到期债务融资工具本金[25汤山建设SCP001]</t>
+          <t>本次定向债务融资工具注册规模为4亿元，本期定向债务融资工具基础发行规模0亿元，发行规模上限4亿元。根据发行人的资金需求，拟用于偿还公司存量债务融资工具本金【25遂宁兴业SCP002】、【26遂宁兴业SCP001】</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司</t>
+          <t>重庆银行股份有限公司,光大证券股份有限公司,天津银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
@@ -5295,7 +5293,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>南京汤山建设投资发展集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>遂宁兴业投资集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5305,10 +5303,14 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
-        </is>
-      </c>
-      <c r="AK22" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK22" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL22" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -5331,22 +5333,22 @@
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
@@ -5379,81 +5381,79 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ22" s="4" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="AZ22" s="3"/>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26遂宁兴业PPN001</t>
+          <t>26长沙银行三农债01</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 16:30</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>032690010.IB</t>
+          <t>212680028.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.0</v>
+        <v>20.0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.0</v>
+        <v>20.0</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.25</v>
+        <v>1.59</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>83.81</v>
+        <v>33.0</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26伊犁财通PPN001</t>
+          <t>26长沙银行债02</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>2.0881</t>
+          <t>1.6023</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6050/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>遂宁兴业投资集团有限公司</t>
+          <t>长沙银行股份有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C- 15.00</t>
+          <t>A 71.97</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:30</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -5473,50 +5473,50 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="U23" s="4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V23" s="4" t="n">
-        <v>1.4</v>
-      </c>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>2.26%~2.36%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z23" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>四川省-遂宁市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具注册规模为4亿元，本期定向债务融资工具基础发行规模0亿元，发行规模上限4亿元。根据发行人的资金需求，拟用于偿还公司存量债务融资工具本金【25遂宁兴业SCP002】、【26遂宁兴业SCP001】</t>
+          <t>本期债券募集资金将依据适用法律和监管部门的批准,专项用于发放涉农贷款。</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>重庆银行股份有限公司,光大证券股份有限公司,天津银行股份有限公司</t>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,兴业银行股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,广发证券股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5531,67 +5531,67 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>遂宁兴业投资集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>长沙银行股份有限公司2026年"三农"专项金融债券</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
+          <t>2029-09-01</t>
         </is>
       </c>
       <c r="AK23" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL23" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AM23" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5624,74 +5624,74 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26长沙银行三农债01</t>
+          <t>26长安汇通MTN003(科创债)</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:30</t>
+          <t>08-28 18:00</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>212680028.IB</t>
+          <t>102683454.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.60 ~ 2.40</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.59</v>
+        <v>1.87</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>33.0</v>
+        <v>45.81</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26长沙银行债02</t>
+          <t>26长安汇通MTN002</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>4.82Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.6023</t>
+          <t>1.9570</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>1.6050/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>长沙银行股份有限公司</t>
+          <t>长安汇通集团有限责任公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>A 71.97</t>
+          <t>B- 47.13</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5711,11 +5711,15 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>3.4667</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>1.79</v>
+      </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -5723,7 +5727,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.89%~1.99%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -5731,30 +5735,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将依据适用法律和监管部门的批准,专项用于发放涉农贷款。</t>
+          <t>本期科技创新债券发行规模为6亿元,募集资金拟全部用于置换本期债券发行之日起一年以内科技创新领域基金出资和科技创新领域股权投资[25长安汇通SCP002,23长安汇通PPN001,25长安汇通SCP003,23长安汇通PPN002]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,兴业银行股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,广发证券股份有限公司,中国建设银行股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>长沙银行股份有限公司2026年"三农"专项金融债券</t>
+          <t>长安汇通集团有限责任公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5779,57 +5779,57 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>2031-08-31</t>
         </is>
       </c>
       <c r="AK24" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5862,17 +5862,17 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26长安汇通MTN003(科创债)</t>
+          <t>26堰控01</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>102683454.IB</t>
+          <t>520442.SZ</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -5881,40 +5881,40 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.40</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>45.81</v>
+        <v>66.81</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26长安汇通MTN002</t>
+          <t>26十堰城控PPN001</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>4.82Y</t>
+          <t>4.89Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.9570</t>
+          <t>2.0561</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>长安汇通集团有限责任公司</t>
+          <t>十堰市城市发展控股集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>B- 47.13</t>
+          <t>C- 19.70</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5949,50 +5949,48 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.4667</v>
-      </c>
-      <c r="V25" s="4" t="n">
-        <v>1.79</v>
-      </c>
+        <v>4.46</v>
+      </c>
+      <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.89%~1.99%</t>
+          <t>1.96%~2.06%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>湖北省-十堰市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券发行规模为6亿元,募集资金拟全部用于置换本期债券发行之日起一年以内科技创新领域基金出资和科技创新领域股权投资[25长安汇通SCP002,23长安汇通PPN001,25长安汇通SCP003,23长安汇通PPN002]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还即将回售的公司债券本金[23堰控03]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>长江证券股份有限公司,华鑫证券有限责任公司,中国国际金融股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
@@ -6002,52 +6000,48 @@
       </c>
       <c r="AG25" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>长安汇通集团有限责任公司2026年度第三期科技创新债券</t>
+          <t>十堰市城市发展控股集团有限公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK25" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AM25" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
@@ -6057,17 +6051,17 @@
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -6100,17 +6094,17 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26堰控01</t>
+          <t>26惠众01</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>08-28 19:00</t>
+          <t>08-28 18:30</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>520442.SZ</t>
+          <t>283826.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -6119,40 +6113,32 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>2.20 ~ 3.50</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>66.81</v>
+        <v>108.81</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>26十堰城控PPN001</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>4.89Y</t>
-        </is>
-      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>2.0561</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -6162,12 +6148,12 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>十堰市城市发展控股集团有限公司</t>
+          <t>山东惠众民生发展集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 19.70</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6191,17 +6177,17 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>4.46</v>
+        <v>2.95</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.96%~2.06%</t>
+          <t>2.35%~2.45%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -6212,17 +6198,17 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>湖北省-十堰市</t>
+          <t>山东省-枣庄市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还即将回售的公司债券本金[23堰控03]</t>
+          <t>本期债券募集资金扣除发行费用后,全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,华鑫证券有限责任公司,中国国际金融股份有限公司,招商证券股份有限公司</t>
+          <t>浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
@@ -6238,12 +6224,12 @@
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>十堰市城市发展控股集团有限公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>山东惠众民生发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6274,32 +6260,28 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP26" s="3"/>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>供热</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>供热</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>生物制品</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6332,7 +6314,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26港口Y2</t>
+          <t>26淮联07</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6342,64 +6324,64 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>245965.SH</t>
+          <t>283831.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>2+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>10.0</v>
+        <v>2.5</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.65</v>
+        <v>1.99</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>39.53</v>
+        <v>57.81</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26港口Y1</t>
+          <t>25淮发03</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>1.74Y+N</t>
+          <t>3.94Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.6633</t>
+          <t>1.8585</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/1.6200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>福建省港口集团有限责任公司</t>
+          <t>淮安市国有联合投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.99</t>
+          <t>C- 20.26</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6423,17 +6405,17 @@
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2.92</v>
+        <v>2.04</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -6444,17 +6426,17 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还公司债务</t>
+          <t>本期债券募集资金扣除发行费用后,拟将全部用于偿还公司债券本金[23淮发V2]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,华福证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,招商证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
@@ -6475,23 +6457,23 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>福建省港口集团有限责任公司2026年面向专业投资者公开发行可续期公司债券(第二期)</t>
+          <t>淮安市国有联合投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种二)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2028-09-01</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6506,12 +6488,12 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
@@ -6521,17 +6503,17 @@
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6546,12 +6528,12 @@
       </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX27" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY27" s="3" t="inlineStr">
@@ -6564,121 +6546,129 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26惠众01</t>
+          <t>26盛泽G1</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:30</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>283826.SH</t>
+          <t>245734.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 3.50</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>108.81</v>
+        <v>58.0</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>24盛泽G1</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>2.81Y</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>1.7543</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>江苏盛泽投资有限公司</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>C- 10.83</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>08-28 15:00</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>山东惠众民生发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>08-28 15:00</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.95</v>
+        <v>2.46</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>2.35%~2.45%</t>
+          <t>1.70%~1.80%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>山东省-枣庄市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,全部用于偿还有息债务</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换到期公司债券本金的偿债资金[23盛泽G1]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司</t>
+          <t>华安证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6699,20 +6689,24 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>山东惠众民生发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>江苏盛泽投资有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK28" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK28" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL28" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6720,7 +6714,7 @@
       </c>
       <c r="AM28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AN28" s="3" t="inlineStr">
@@ -6730,28 +6724,32 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP28" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>供热</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>供热</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>生物制品</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6784,7 +6782,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26淮联07</t>
+          <t>26XCF13</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6794,64 +6792,64 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>283831.SH</t>
+          <t>283837.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2+2</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>57.81</v>
+        <v>21.46</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>25淮发03</t>
+          <t>26XCF11</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>3.94Y</t>
+          <t>2.98Y+4.00Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.8585</t>
+          <t>1.7657</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7300</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司</t>
+          <t>成都兴城投资集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 20.26</t>
+          <t>C+ 34.25</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6861,7 +6859,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 16:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6875,17 +6873,17 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.04</v>
+        <v>4.05</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6896,17 +6894,17 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将全部用于偿还公司债券本金[23淮发V2]</t>
+          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途,具体用途根据发行人资金需求情况确定。</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,招商证券股份有限公司,东吴证券股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,华泰联合证券有限责任公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6927,7 +6925,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>淮安市国有联合投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种二)</t>
+          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行公司债券(第七期)(品种一)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6937,7 +6935,7 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
+          <t>2033-09-01</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
@@ -6958,7 +6956,7 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
@@ -6968,17 +6966,17 @@
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
@@ -6988,7 +6986,7 @@
       </c>
       <c r="AU29" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-01</t>
         </is>
       </c>
       <c r="AV29" s="3" t="inlineStr">
@@ -6998,7 +6996,7 @@
       </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX29" s="3" t="inlineStr">
@@ -7016,7 +7014,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26张高Y2</t>
+          <t>26金义03</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -7026,64 +7024,64 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>283798.SH</t>
+          <t>283806.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.35 ~ 2.35</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>71.81</v>
+        <v>36.81</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>25张高Y1</t>
+          <t>26金义02</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>1.65Y+N</t>
+          <t>2.79Y+2.00Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.6829</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/1.6200</t>
+          <t>1.7800/1.7600</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>张家港市高铁投资发展(集团)有限公司</t>
+          <t>浙江金义控股集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C 27.56</t>
+          <t>B- 38.57</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7093,7 +7091,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 16:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -7107,38 +7105,38 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.75</v>
+        <v>3.19</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.90%~2.00%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金。[23张高Y2]</t>
+          <t>本期债券的募集资金扣除发行费用后,拟全部用于偿还到期的公司债券“23金义03”。[23金义03]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,国金证券股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -7159,7 +7157,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
+          <t>浙江金义控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7175,7 +7173,7 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="AM30" s="3" t="inlineStr">
@@ -7195,7 +7193,7 @@
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
@@ -7205,22 +7203,22 @@
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-01</t>
         </is>
       </c>
       <c r="AV30" s="3" t="inlineStr">
@@ -7230,7 +7228,7 @@
       </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX30" s="3" t="inlineStr">
@@ -7248,22 +7246,22 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26盛泽G1</t>
+          <t>26宝鸡工发PPN002</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>08-28 19:00</t>
+          <t>08-28 18:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>245734.SH</t>
+          <t>032680503.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
@@ -7274,48 +7272,48 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.90 ~ 3.00</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.84</v>
+        <v>2.38</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>58.0</v>
+        <v>96.81</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>24盛泽G1</t>
+          <t>26宝鸡工发PPN001</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>2.81Y</t>
+          <t>2.58Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.7543</t>
+          <t>2.1288</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.1400</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>江苏盛泽投资有限公司</t>
+          <t>宝鸡市工业发展集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C- 10.83</t>
+          <t>C+ 32.50</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7325,7 +7323,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 14:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -7335,48 +7333,50 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="V31" s="3"/>
+        <v>3.06</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>3.33</v>
+      </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.70%~1.80%</t>
-        </is>
-      </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
+          <t>2.54%~2.64%</t>
+        </is>
+      </c>
+      <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>陕西省-宝鸡市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换到期公司债券本金的偿债资金[23盛泽G1]</t>
+          <t>发行人本期定向债务融资工具基础发行规模0.00 亿元，发行金额上限5.00亿元，募集资金拟用于偿还公司有息负债、补充流动资金。其中，3亿元用于偿还公司有息负债，2亿元用于补充流动资金</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>华安证券股份有限公司,东吴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD31" s="3"/>
+          <t>光大证券股份有限公司,华夏银行股份有限公司,重庆银行股份有限公司,兴业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr">
+        <is>
+          <t>西安投融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -7386,82 +7386,78 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>江苏盛泽投资有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>宝鸡市工业发展集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>2031-08-31</t>
         </is>
       </c>
       <c r="AK31" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL31" s="3" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP31" s="3"/>
+      <c r="AQ31" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM31" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO31" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ31" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR31" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS31" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT31" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU31" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV31" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW31" s="3" t="inlineStr">
@@ -7479,79 +7475,81 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ31" s="3"/>
+      <c r="AZ31" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26XCF13</t>
+          <t>26平安租赁CP003</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>08-28 19:00</t>
+          <t>08-31 18:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>283837.SH</t>
+          <t>042680303.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3+2+2</t>
+          <t>0.97Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.5</v>
+        <v>4.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.31 ~ 1.51</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>21.46</v>
+        <v>28.68</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26XCF11</t>
+          <t>26平安租赁CP002</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2.98Y+4.00Y</t>
+          <t>355D</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.7657</t>
+          <t>1.5665</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/1.7300</t>
+          <t>--/1.5600</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司</t>
+          <t>平安国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.25</t>
+          <t>C- 18.80</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7561,7 +7559,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7575,17 +7573,17 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>4.05</v>
+        <v>0.6</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.55%~1.59%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7596,101 +7594,105 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途,具体用途根据发行人资金需求情况确定。</t>
+          <t>发行人本次发行短期融资券拟募集资金4亿元，拟全部用于偿还发行人银行借款</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,华泰联合证券有限责任公司,申万宏源证券有限公司</t>
+          <t>渤海银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行公司债券(第七期)(品种一)</t>
+          <t>平安国际融资租赁有限公司2026年度第三期短期融资券</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2033-09-01</t>
-        </is>
-      </c>
-      <c r="AK32" s="3"/>
+          <t>2027-08-21</t>
+        </is>
+      </c>
+      <c r="AK32" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL32" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM32" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO32" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ32" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR32" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
       <c r="AV32" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7698,7 +7700,7 @@
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
@@ -7708,82 +7710,84 @@
       </c>
       <c r="AY32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AZ32" s="3"/>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AZ32" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26金义03</t>
+          <t>26苏州银行01</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>08-28 19:00</t>
+          <t>08-28 16:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>283806.SH</t>
+          <t>2620007.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 2.35</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>36.81</v>
+        <v>31.0</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26金义02</t>
+          <t>25苏州银行科创债01(柜台)</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>2.79Y+2.00Y</t>
+          <t>4.04Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.6308</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>1.7800/1.7600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>浙江金义控股集团有限公司</t>
+          <t>苏州银行股份有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>B- 38.57</t>
+          <t>A- 66.73</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7793,7 +7797,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7806,18 +7810,16 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U33" s="4" t="n">
-        <v>3.19</v>
-      </c>
+      <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7825,104 +7827,112 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z33" s="3"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除发行费用后,拟全部用于偿还到期的公司债券“23金义03”。[23金义03]</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,国金证券股份有限公司,光大证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中国银行股份有限公司,中国邮政储蓄银行股份有限公司,中国工商银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,中国光大银行股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>浙江金义控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>苏州银行股份有限公司2026年第一期金融债券</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="AK33" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK33" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>城商行</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO33" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ33" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR33" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7930,7 +7940,7 @@
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
@@ -7948,7 +7958,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26宝鸡工发PPN002</t>
+          <t>26中建材集MTN004(科创债)</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7958,64 +7968,64 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>032680503.IB</t>
+          <t>102683447.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 3.00</t>
+          <t>1.48 ~ 1.68</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.38</v>
+        <v>1.58</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>96.81</v>
+        <v>32.0</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26宝鸡工发PPN001</t>
+          <t>24中建材集MTN001A(科创票据)</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2.58Y</t>
+          <t>2.95Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2.1288</t>
+          <t>1.6800</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/2.1400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>宝鸡市工业发展集团有限公司</t>
+          <t>中国建材集团有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.50</t>
+          <t>B- 44.78</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8025,7 +8035,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>08-28 14:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -8039,51 +8049,49 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>3.33</v>
-      </c>
+        <v>1.5909</v>
+      </c>
+      <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>2.54%~2.64%</t>
-        </is>
-      </c>
-      <c r="Y34" s="3"/>
+          <t>1.62%~1.72%</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>陕西省-宝鸡市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具基础发行规模0.00 亿元，发行金额上限5.00亿元，募集资金拟用于偿还公司有息负债、补充流动资金。其中，3亿元用于偿还公司有息负债，2亿元用于补充流动资金</t>
+          <t>本期债务融资工具发行规模为11亿元,募集资金用于偿还有息债务；本期科技创新债券的募集资金穿透实际用于发行人科技创新业务及主营业务新材料核心板块,主要投向新材料领域项下玻璃纤维、石膏板、风电叶片等的研发设备购置、核心生产装备升级改造及核心物料采购等</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,华夏银行股份有限公司,重庆银行股份有限公司,兴业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD34" s="3" t="inlineStr">
-        <is>
-          <t>西安投融资担保有限公司</t>
-        </is>
-      </c>
+          <t>江苏银行股份有限公司,中国光大银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr">
@@ -8093,24 +8101,20 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>宝鸡市工业发展集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>中国建材集团有限公司2026年度第四期科技创新债券</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-31</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -8128,28 +8132,32 @@
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP34" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8159,7 +8167,7 @@
       </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW34" s="3" t="inlineStr">
@@ -8177,81 +8185,79 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="AZ34" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ34" s="3"/>
     </row>
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26平安租赁CP003</t>
+          <t>26蓉西01</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>08-31 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>042680303.IB</t>
+          <t>283832.SH</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>0.97Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.51</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.51</v>
+        <v>1.93</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>28.68</v>
+        <v>51.81</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26平安租赁CP002</t>
+          <t>25蓉西01</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>355D</t>
+          <t>3.96Y+2.00Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.5665</t>
+          <t>1.9319</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/1.5600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>平安国际融资租赁有限公司</t>
+          <t>成都温江兴蓉西城市运营集团有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C- 18.80</t>
+          <t>C- 10.04</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8261,7 +8267,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -8271,123 +8277,123 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>0.6</v>
+        <v>3.51</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.55%~1.59%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行短期融资券拟募集资金4亿元，拟全部用于偿还发行人银行借款</t>
+          <t>本期公司债券募集资金扣除发行费用后,4亿元用于置换发行人偿还“23蓉西01”公司债券本金的自有资金,6亿元用于偿还即将回售的“23蓉西02”公司债券本金[23蓉西01,23蓉西02]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司,招商银行股份有限公司</t>
+          <t>广发证券股份有限公司,国投证券股份有限公司,中天证券股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>平安国际融资租赁有限公司2026年度第三期短期融资券</t>
+          <t>成都温江兴蓉西城市运营集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2027-08-21</t>
+          <t>2031-08-31</t>
         </is>
       </c>
       <c r="AK35" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AM35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8412,84 +8418,76 @@
       </c>
       <c r="AY35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AZ35" s="4" t="n">
-        <v>0.0</v>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AZ35" s="3"/>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26中建材集MTN004(科创债)</t>
+          <t>26张高Y1(取消发行)</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>102683447.IB</t>
+          <t>DY283797.SH</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>11.0</v>
-      </c>
+        <v>3.0</v>
+      </c>
+      <c r="F36" s="3"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.48 ~ 1.68</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>32.0</v>
-      </c>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>24中建材集MTN001A(科创票据)</t>
+          <t>25张高Y1</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2.95Y</t>
+          <t>1.65Y+N</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.6800</t>
+          <t>1.6829</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6200</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>中国建材集团有限公司</t>
+          <t>张家港市高铁投资发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>B- 44.78</t>
+          <t>C 27.56</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8499,7 +8497,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8509,119 +8507,121 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="U36" s="4" t="n">
-        <v>1.5909</v>
-      </c>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.62%~1.72%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模为11亿元,募集资金用于偿还有息债务；本期科技创新债券的募集资金穿透实际用于发行人科技创新业务及主营业务新材料核心板块,主要投向新材料领域项下玻璃纤维、石膏板、风电叶片等的研发设备购置、核心生产装备升级改造及核心物料采购等</t>
+          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金。[23张高Y2]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>中国建材集团有限公司2026年度第四期科技创新债券</t>
+          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
-        </is>
-      </c>
-      <c r="AK36" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK36" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL36" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AM36" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="AW36" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX36" s="3" t="inlineStr">
@@ -8654,59 +8654,59 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26蓉西01</t>
+          <t>26海峡环保SCP002</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>08-28 19:00</t>
+          <t>08-28 18:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>283832.SH</t>
+          <t>012682173.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.93</v>
+        <v>1.45</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>51.81</v>
+        <v>28.07</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>25蓉西01</t>
+          <t>26海峡环保SCP001</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>3.96Y+2.00Y</t>
+          <t>159D</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.9319</t>
+          <t>1.5369</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -8716,12 +8716,12 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>成都温江兴蓉西城市运营集团有限公司</t>
+          <t>福建海峡环保集团股份有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C- 10.04</t>
+          <t>C 29.00</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 10:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -8745,17 +8745,17 @@
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>3.51</v>
+        <v>2.9333</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.56%~1.60%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8766,23 +8766,23 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,4亿元用于置换发行人偿还“23蓉西01”公司债券本金的自有资金,6亿元用于偿还即将回售的“23蓉西02”公司债券本金[23蓉西01,23蓉西02]</t>
+          <t>本期超短期融资券发行金额3.00亿元,拟用于偿还金融机构借款</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,国投证券股份有限公司,中天证券股份有限公司</t>
+          <t>兴业银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
@@ -8792,32 +8792,28 @@
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>成都温江兴蓉西城市运营集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>福建海峡环保集团股份有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK37" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-05-28</t>
+        </is>
+      </c>
+      <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM37" s="3" t="inlineStr">
@@ -8832,32 +8828,32 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8890,7 +8886,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26张高Y1(取消发行)</t>
+          <t>26嘉产03</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8900,111 +8896,119 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>DY283797.SH</t>
+          <t>283739.SH</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>9.0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>9.0</v>
+      </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
           <t>1.70 ~ 2.70</t>
         </is>
       </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+      <c r="H38" s="4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>46.81</v>
+      </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>26嘉产02</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>4.77Y</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>1.8940</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>嘉兴市产业发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>C- 12.71</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>08-28 15:00</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>25张高Y1</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>1.65Y+N</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>1.6829</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>--/1.6200</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>张家港市高铁投资发展(集团)有限公司</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t>C 27.56</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t>08-28 15:00</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="U38" s="3"/>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="U38" s="4" t="n">
+        <v>4.63</v>
+      </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金。[23张高Y2]</t>
+          <t>本期债券募集资金扣除发行费用后其中6亿元用于偿还公司债券到期本金，剩余募集资金用于偿还其他有息债务[23嘉产02]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>东吴证券股份有限公司,平安证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
@@ -9025,7 +9029,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)(取消发行)</t>
+          <t>嘉兴市产业发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -9035,64 +9039,64 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>2031-08-31</t>
         </is>
       </c>
       <c r="AK38" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL38" s="3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM38" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO38" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ38" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR38" s="3" t="inlineStr">
-        <is>
-          <t>综合基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS38" s="3" t="inlineStr">
-        <is>
-          <t>综合基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT38" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU38" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV38" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -9100,7 +9104,7 @@
       </c>
       <c r="AW38" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX38" s="3" t="inlineStr">
@@ -9118,7 +9122,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26海峡环保SCP002</t>
+          <t>26文登蓝海MTN001</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -9128,49 +9132,49 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>012682173.IB</t>
+          <t>102683453.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>3.0</v>
+        <v>4.2</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>3.0</v>
+        <v>4.2</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>2.30 ~ 3.30</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.45</v>
+        <v>2.44</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>28.07</v>
+        <v>102.81</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26海峡环保SCP001</t>
+          <t>22蓝海债</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>159D</t>
+          <t>2.59Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.5369</t>
+          <t>2.1091</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -9180,12 +9184,12 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>福建海峡环保集团股份有限公司</t>
+          <t>威海市文登区蓝海投资开发有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C 29.00</t>
+          <t>C+ 34.33</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9195,7 +9199,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>08-28 10:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -9209,17 +9213,19 @@
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>2.9333</v>
-      </c>
-      <c r="V39" s="3"/>
+        <v>3.119</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.60%</t>
+          <t>2.20%~2.30%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -9230,23 +9236,23 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>山东省-威海市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额3.00亿元,拟用于偿还金融机构借款</t>
+          <t>本期中期票据发行金额4.20亿元,募集资金用于偿还到期债务融资工具本金[23文登蓝海MTN001]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>国投证券股份有限公司,中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9261,7 +9267,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>福建海峡环保集团股份有限公司2026年度第二期超短期融资券</t>
+          <t>威海市文登区蓝海投资开发有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9271,10 +9277,14 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2027-05-28</t>
-        </is>
-      </c>
-      <c r="AK39" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK39" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL39" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -9292,32 +9302,32 @@
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9350,7 +9360,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26嘉产03</t>
+          <t>26商物06</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9360,64 +9370,64 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>283739.SH</t>
+          <t>283775.SH</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.70 ~ 2.40</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>46.81</v>
+        <v>76.0</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26嘉产02</t>
+          <t>26新疆商贸PPN001</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>2.95Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.8940</t>
+          <t>1.9813</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0100/1.9000</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>嘉兴市产业发展集团有限公司</t>
+          <t>新疆商贸物流(集团)有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 12.71</t>
+          <t>C+ 34.80</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9441,17 +9451,17 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>4.63</v>
+        <v>1.425</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.91%~2.01%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -9462,17 +9472,17 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>新疆维吾尔自治区-乌鲁木齐市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后其中6亿元用于偿还公司债券到期本金，剩余募集资金用于偿还其他有息债务[23嘉产02]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,平安证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>招商证券股份有限公司,光大证券股份有限公司,中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
@@ -9493,7 +9503,7 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>嘉兴市产业发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>新疆商贸物流(集团)有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9503,14 +9513,10 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK40" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-31</t>
+        </is>
+      </c>
+      <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -9528,32 +9534,32 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9586,7 +9592,7 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26文登蓝海MTN001</t>
+          <t>26传化MTN001(科创债)</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9596,49 +9602,49 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>102683453.IB</t>
+          <t>102683451.IB</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>4.2</v>
+        <v>2.0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>4.2</v>
+        <v>2.0</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2.30 ~ 3.30</t>
+          <t>1.80 ~ 2.50</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>102.81</v>
+        <v>79.53</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>22蓝海债</t>
+          <t>25生产兵团MTN002</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>2.59Y</t>
+          <t>2.30Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>2.1091</t>
+          <t>1.7048</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -9648,12 +9654,12 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>威海市文登区蓝海投资开发有限公司</t>
+          <t>传化智联股份有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.33</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9677,10 +9683,10 @@
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>3.119</v>
+        <v>1.6</v>
       </c>
       <c r="V41" s="4" t="n">
-        <v>1.0</v>
+        <v>1.33</v>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
@@ -9689,28 +9695,28 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>2.20%~2.30%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>山东省-威海市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额4.20亿元,募集资金用于偿还到期债务融资工具本金[23文登蓝海MTN001]</t>
+          <t>发行人本期科技创新债券发行规模为2亿元,其中1亿元用于偿还发行人有息负债,1亿元用于子公司浙江传化功能新材料有限公司纺织工业印染助剂、纺织品整理剂、化学试剂和助剂等功能化学品和新材料领域产品的研发和技术突破的投入</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司,中泰证券股份有限公司</t>
+          <t>浙商银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
@@ -9721,7 +9727,7 @@
       </c>
       <c r="AF41" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG41" s="3" t="inlineStr">
@@ -9731,7 +9737,7 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>威海市文登区蓝海投资开发有限公司2026年度第一期中期票据</t>
+          <t>传化智联股份有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9741,14 +9747,10 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK41" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2028-08-31</t>
+        </is>
+      </c>
+      <c r="AK41" s="3"/>
       <c r="AL41" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -9766,32 +9768,32 @@
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>物流</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9824,7 +9826,7 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26中荆06</t>
+          <t>26南京交建SCP005</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9834,64 +9836,64 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>283811.SH</t>
+          <t>012682175.IB</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F42" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 1.70</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>1.99</v>
-      </c>
       <c r="I42" s="4" t="n">
-        <v>57.81</v>
+        <v>23.07</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>24中荆投资PPN002</t>
+          <t>26南京交建SCP004</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>255D</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.9247</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4090</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>中荆投资控股集团有限公司</t>
+          <t>南京市交通建设投资控股(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C- 19.46</t>
+          <t>C 29.88</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9901,7 +9903,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9915,48 +9917,46 @@
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="V42" s="3"/>
+        <v>4.2556</v>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.81%~1.91%</t>
+          <t>1.51%~1.55%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>湖北省-荆门市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券本金。[G23中荆3]</t>
+          <t>本期超短期融资券发行金额4.5亿元,本期发行的募集资金拟用于偿还发行人有息债务[26南京交建SCP002]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,长江证券股份有限公司,东方证券股份有限公司,国金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD42" s="3" t="inlineStr">
-        <is>
-          <t>长江产业投资集团有限公司</t>
-        </is>
-      </c>
+          <t>南京银行股份有限公司,江苏银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
@@ -9966,32 +9966,28 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>中荆投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)</t>
+          <t>南京市交通建设投资控股(集团)有限责任公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK42" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-05-28</t>
+        </is>
+      </c>
+      <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM42" s="3" t="inlineStr">
@@ -10006,32 +10002,32 @@
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
@@ -10041,7 +10037,7 @@
       </c>
       <c r="AV42" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW42" s="3" t="inlineStr">
@@ -10064,74 +10060,74 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26商物06</t>
+          <t>26中兵物资SCP001</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>08-28 19:00</t>
+          <t>08-28 18:00</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>283775.SH</t>
+          <t>012682171.IB</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.40</t>
+          <t>1.37 ~ 1.57</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>2.02</v>
+        <v>1.43</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>76.0</v>
+        <v>26.07</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26新疆商贸PPN001</t>
+          <t>26中拓SCP009</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>2.95Y</t>
+          <t>259D</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.9813</t>
+          <t>1.7014</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>2.0100/1.9000</t>
+          <t>1.7500/--</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>新疆商贸物流(集团)有限公司</t>
+          <t>中国兵工物资集团有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.80</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10141,7 +10137,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>08-28 15:00</t>
+          <t>08-28 09:00</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -10155,7 +10151,7 @@
         </is>
       </c>
       <c r="U43" s="4" t="n">
-        <v>1.425</v>
+        <v>1.575</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
@@ -10163,11 +10159,7 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t>1.91%~2.01%</t>
-        </is>
-      </c>
+      <c r="X43" s="3"/>
       <c r="Y43" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -10176,54 +10168,54 @@
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区-乌鲁木齐市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还有息债务</t>
+          <t>本期债务融资工具发行金额4亿元,募集资金拟用于偿还到期债务及补充流动资金</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司,光大证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>平安银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG43" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>新疆商贸物流(集团)有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>中国兵工物资集团有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t>2027-05-28</t>
         </is>
       </c>
       <c r="AK43" s="3"/>
       <c r="AL43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM43" s="3" t="inlineStr">
@@ -10243,7 +10235,7 @@
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
@@ -10296,59 +10288,59 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26传化MTN001(科创债)</t>
+          <t>26靖滨01</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>102683451.IB</t>
+          <t>283740.SH</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>2.0</v>
+        <v>6.6</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2.0</v>
+        <v>6.6</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>79.53</v>
+        <v>77.81</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>25生产兵团MTN002</t>
+          <t>24靖滨03</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2.30Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.7048</t>
+          <t>1.7952</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -10358,12 +10350,12 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>传化智联股份有限公司</t>
+          <t>靖江市滨江新城投资开发有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C- 11.20</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10373,7 +10365,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -10383,121 +10375,119 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U44" s="4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V44" s="4" t="n">
-        <v>1.33</v>
-      </c>
+        <v>2.17</v>
+      </c>
+      <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.97%~2.07%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>发行人本期科技创新债券发行规模为2亿元,其中1亿元用于偿还发行人有息负债,1亿元用于子公司浙江传化功能新材料有限公司纺织工业印染助剂、纺织品整理剂、化学试剂和助剂等功能化学品和新材料领域产品的研发和技术突破的投入</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还发行人即将到期的公司债券本金；本期债券募集资金中6.6亿元仅用于偿还发行人即将到期的公司债券本金；本期债券为5年期债券,募集资金拟全部用于偿还到期的公司债券本金[23靖滨02]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>天风证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF44" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG44" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>传化智联股份有限公司2026年度第一期科技创新债券</t>
+          <t>靖江市滨江新城投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2028-08-31</t>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AK44" s="3"/>
       <c r="AL44" s="3" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AM44" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>物流</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
@@ -10530,74 +10520,74 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26南京交建SCP005</t>
+          <t>26XCF14</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-28 19:00</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>012682175.IB</t>
+          <t>283838.SH</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5+2+2</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4.5</v>
+        <v>11.0</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>23.07</v>
+        <v>25.7</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26南京交建SCP004</t>
+          <t>26XCF12</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>255D</t>
+          <t>4.98Y+4.00Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.9001</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>--/1.4090</t>
+          <t>--/1.8900</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司</t>
+          <t>成都兴城投资集团有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C 29.88</t>
+          <t>C+ 34.25</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10607,7 +10597,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 16:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10617,23 +10607,21 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U45" s="4" t="n">
-        <v>4.2556</v>
-      </c>
-      <c r="V45" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>2.17</v>
+      </c>
+      <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.55%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -10644,23 +10632,23 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额4.5亿元,本期发行的募集资金拟用于偿还发行人有息债务[26南京交建SCP002]</t>
+          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途,具体用途根据发行人资金需求情况确定。</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,江苏银行股份有限公司</t>
+          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
@@ -10670,73 +10658,77 @@
       </c>
       <c r="AG45" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司2026年度第五期超短期融资券</t>
+          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行公司债券(第七期)(品种二)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2027-05-28</t>
-        </is>
-      </c>
-      <c r="AK45" s="3"/>
+          <t>2035-09-01</t>
+        </is>
+      </c>
+      <c r="AK45" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL45" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="AM45" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-01</t>
         </is>
       </c>
       <c r="AV45" s="3" t="inlineStr">
@@ -10746,7 +10738,7 @@
       </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX45" s="3" t="inlineStr">
@@ -10764,7 +10756,7 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26中兵物资SCP001</t>
+          <t>26中荆06</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10774,64 +10766,64 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>012682171.IB</t>
+          <t>283811.SH</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>4.0</v>
+        <v>0.7</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>4.0</v>
+        <v>1.4</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.37 ~ 1.57</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1.43</v>
+        <v>1.99</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>26.07</v>
+        <v>57.81</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>26中拓SCP009</t>
+          <t>24中荆投资PPN002</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>259D</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.7014</t>
+          <t>1.9247</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>1.7500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>中国兵工物资集团有限公司</t>
+          <t>中荆投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C- 19.46</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10841,7 +10833,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>08-28 09:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -10855,71 +10847,83 @@
         </is>
       </c>
       <c r="U46" s="4" t="n">
-        <v>1.575</v>
+        <v>3.68</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X46" s="3"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>1.81%~1.91%</t>
+        </is>
+      </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>湖北省-荆门市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额4亿元,募集资金拟用于偿还到期债务及补充流动资金</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券本金。[G23中荆3]</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,招商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD46" s="3"/>
+          <t>国泰海通证券股份有限公司,长江证券股份有限公司,东方证券股份有限公司,国金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr">
+        <is>
+          <t>长江产业投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE46" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF46" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG46" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>中国兵工物资集团有限公司2026年度第一期超短期融资券</t>
+          <t>中荆投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2027-05-28</t>
-        </is>
-      </c>
-      <c r="AK46" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK46" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM46" s="3" t="inlineStr">
@@ -10939,27 +10943,27 @@
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
@@ -10969,7 +10973,7 @@
       </c>
       <c r="AV46" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW46" s="3" t="inlineStr">
@@ -10992,7 +10996,7 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26靖滨01</t>
+          <t>26张高Y2</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -11002,49 +11006,49 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>283740.SH</t>
+          <t>283798.SH</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>6.6</v>
+        <v>3.0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>6.6</v>
+        <v>6.0</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>77.81</v>
+        <v>71.81</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>24靖滨03</t>
+          <t>25张高Y1</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>1.65Y+N</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.7952</t>
+          <t>1.6829</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -11054,12 +11058,12 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司</t>
+          <t>张家港市高铁投资发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C- 11.20</t>
+          <t>C 27.56</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -11083,38 +11087,38 @@
         </is>
       </c>
       <c r="U47" s="4" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>1.97%~2.07%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还发行人即将到期的公司债券本金；本期债券募集资金中6.6亿元仅用于偿还发行人即将到期的公司债券本金；本期债券为5年期债券,募集资金拟全部用于偿还到期的公司债券本金[23靖滨02]</t>
+          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金。[23张高Y2]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,中信证券股份有限公司</t>
+          <t>东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
@@ -11135,7 +11139,7 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -11166,7 +11170,7 @@
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP47" s="3" t="inlineStr">
@@ -11181,12 +11185,12 @@
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
@@ -11206,7 +11210,7 @@
       </c>
       <c r="AW47" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX47" s="3" t="inlineStr">
@@ -11224,7 +11228,7 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26XCF14</t>
+          <t>26港口Y2</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -11234,64 +11238,64 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>283838.SH</t>
+          <t>245965.SH</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>5+2+2</t>
+          <t>2+N</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>6.5</v>
+        <v>10.0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>25.7</v>
+        <v>39.53</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>26XCF12</t>
+          <t>26港口Y1</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>4.98Y+4.00Y</t>
+          <t>1.74Y+N</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.9001</t>
+          <t>1.6633</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>--/1.8900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司</t>
+          <t>福建省港口集团有限责任公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.25</t>
+          <t>C+ 32.99</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11301,7 +11305,7 @@
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>08-28 16:00</t>
+          <t>08-28 15:00</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -11315,7 +11319,7 @@
         </is>
       </c>
       <c r="U48" s="4" t="n">
-        <v>2.17</v>
+        <v>2.92</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
@@ -11325,7 +11329,7 @@
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
@@ -11336,17 +11340,17 @@
       <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将用于生产性支出,具体包括偿还债务、补充流动资金、项目投资、股权投资等符合国家法律法规要求的用途,具体用途根据发行人资金需求情况确定。</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还公司债务</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,申万宏源证券有限公司</t>
+          <t>兴业证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
@@ -11367,74 +11371,70 @@
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>成都兴城投资集团有限公司2026年面向专业投资者非公开发行公司债券(第七期)(品种二)</t>
+          <t>福建省港口集团有限责任公司2026年面向专业投资者公开发行可续期公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2035-09-01</t>
-        </is>
-      </c>
-      <c r="AK48" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-09-01</t>
+        </is>
+      </c>
+      <c r="AK48" s="3"/>
       <c r="AL48" s="3" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM48" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO48" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ48" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR48" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS48" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
       <c r="AV48" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -11442,12 +11442,12 @@
       </c>
       <c r="AW48" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX48" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY48" s="3" t="inlineStr">
